--- a/inst/extdata/wyoming_criteria_crosswalk.xlsx
+++ b/inst/extdata/wyoming_criteria_crosswalk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F7499B-0740-4D42-BF54-D7874D60F7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5488785B-B760-40DF-9AF3-98EAB806655B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{254103FA-C5D3-4049-B135-21AE92C6DC6D}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="20710" windowHeight="11020" xr2:uid="{254103FA-C5D3-4049-B135-21AE92C6DC6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2734" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2734" uniqueCount="176">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -213,9 +213,6 @@
   </si>
   <si>
     <t>Modified aquatic life</t>
-  </si>
-  <si>
-    <t>Effluent-dependent aquatic life</t>
   </si>
   <si>
     <t>Chronic</t>
@@ -528,9 +525,6 @@
     <t>Based on taste and odor effects and is more stringent than if based solely on toxic or carcinogenic effects.  See Chapter 1 Table 9, footnote k - this criterion does not apply to the Belle Fourche River above the confluence with Donkey Creek, mainstem of the Belle Fourche River, tributaries to Antelope Creek in the Cheyenne River watershed, Little Thunder Creek and all of its tributaries below the confluence with North Prong Creek in the Cheyenne River watershed, the Little Powder River watershed, the mainstem of Clear Creek and its tributaries upstream of Clearmont, WY in the Powder River watershed, the mainstem of Crazy Woman Creek and its tributaries in the Powder River watershed, the North Fork of the Powder River and all its tributaries in the Powder River watershed, and the Middle Fork of the Powder River and all its tributaries in the Powder River watershed.</t>
   </si>
   <si>
-    <t>Full body contact water recreation</t>
-  </si>
-  <si>
     <t>ESCHERICHIA COLI</t>
   </si>
   <si>
@@ -543,21 +537,12 @@
     <t>For waters designated for full-body contact water recreation, the criterion 630 organisms/100 mL applies October 1 - April 30.</t>
   </si>
   <si>
-    <t>Human Consumption of Fish</t>
-  </si>
-  <si>
     <t>Industry</t>
   </si>
   <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>Limited body contact water recreation</t>
-  </si>
-  <si>
-    <t>Terrestrial wildlife</t>
-  </si>
-  <si>
     <t>0.411/(1+107.204-pH) + 58.4/(1+ 10pH-7.204)</t>
   </si>
   <si>
@@ -573,9 +558,6 @@
     <t>When ambient temperature is &gt;15.6 degrees, exceedance occurs if pollution increases temperature &gt;2.2 degrees than existing temperatures</t>
   </si>
   <si>
-    <t>Human Consumption of Effluent-Dependent Fish</t>
-  </si>
-  <si>
     <t>CHROMIUM, TRIVALENT, TOTAL</t>
   </si>
   <si>
@@ -595,6 +577,15 @@
   </si>
   <si>
     <t>FLUORANTHENE IN FISH TISSUE</t>
+  </si>
+  <si>
+    <t>Recreation</t>
+  </si>
+  <si>
+    <t>Fish Consumption</t>
+  </si>
+  <si>
+    <t>Wildlife</t>
   </si>
 </sst>
 </file>
@@ -1153,7 +1144,7 @@
         <v>43</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>44</v>
@@ -1234,7 +1225,7 @@
         <v>43</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>56</v>
@@ -1315,7 +1306,7 @@
         <v>43</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>57</v>
@@ -1396,7 +1387,7 @@
         <v>43</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>58</v>
@@ -1477,10 +1468,10 @@
         <v>43</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>59</v>
+        <v>173</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>45</v>
@@ -1558,10 +1549,10 @@
         <v>43</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>59</v>
+        <v>173</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>45</v>
@@ -1571,7 +1562,7 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5" t="s">
@@ -1612,13 +1603,13 @@
       <c r="AC7" s="5"/>
       <c r="AD7" s="5"/>
       <c r="AE7" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AF7" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG7" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
@@ -1639,7 +1630,7 @@
         <v>43</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>44</v>
@@ -1652,7 +1643,7 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
@@ -1693,13 +1684,13 @@
       <c r="AC8" s="5"/>
       <c r="AD8" s="5"/>
       <c r="AE8" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AF8" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG8" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AH8" s="5"/>
       <c r="AI8" s="5"/>
@@ -1720,7 +1711,7 @@
         <v>43</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>56</v>
@@ -1733,7 +1724,7 @@
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5" t="s">
@@ -1774,13 +1765,13 @@
       <c r="AC9" s="5"/>
       <c r="AD9" s="5"/>
       <c r="AE9" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AF9" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG9" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
@@ -1801,7 +1792,7 @@
         <v>43</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>57</v>
@@ -1814,7 +1805,7 @@
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5" t="s">
@@ -1855,13 +1846,13 @@
       <c r="AC10" s="5"/>
       <c r="AD10" s="5"/>
       <c r="AE10" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AF10" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG10" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
@@ -1882,7 +1873,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>58</v>
@@ -1895,7 +1886,7 @@
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
@@ -1936,13 +1927,13 @@
       <c r="AC11" s="5"/>
       <c r="AD11" s="5"/>
       <c r="AE11" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AF11" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG11" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
@@ -1963,13 +1954,13 @@
         <v>43</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>46</v>
@@ -1985,7 +1976,7 @@
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5">
@@ -2019,7 +2010,7 @@
       <c r="AC12" s="5"/>
       <c r="AD12" s="5"/>
       <c r="AE12" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AF12" s="5"/>
       <c r="AG12" s="5"/>
@@ -2036,13 +2027,13 @@
         <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>46</v>
@@ -2058,7 +2049,7 @@
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5">
@@ -2092,7 +2083,7 @@
       <c r="AC13" s="5"/>
       <c r="AD13" s="5"/>
       <c r="AE13" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AF13" s="5"/>
       <c r="AG13" s="5"/>
@@ -2109,20 +2100,20 @@
         <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5" t="s">
@@ -2131,7 +2122,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5">
@@ -2165,7 +2156,7 @@
       <c r="AC14" s="5"/>
       <c r="AD14" s="5"/>
       <c r="AE14" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AF14" s="5"/>
       <c r="AG14" s="5"/>
@@ -2182,16 +2173,16 @@
         <v>43</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
@@ -2209,7 +2200,7 @@
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
       <c r="P15" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q15" s="5">
         <v>1</v>
@@ -2236,13 +2227,13 @@
       <c r="AC15" s="5"/>
       <c r="AD15" s="5"/>
       <c r="AE15" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF15" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="AF15" s="5" t="s">
+      <c r="AG15" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="AG15" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="AH15" s="5"/>
       <c r="AI15" s="5"/>
@@ -2269,20 +2260,20 @@
         <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5" t="s">
@@ -2296,7 +2287,7 @@
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q16" s="5">
         <v>30</v>
@@ -2323,13 +2314,13 @@
       <c r="AC16" s="5"/>
       <c r="AD16" s="5"/>
       <c r="AE16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF16" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="AF16" s="5" t="s">
+      <c r="AG16" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="AG16" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="AH16" s="5"/>
       <c r="AI16" s="5"/>
@@ -2344,20 +2335,20 @@
         <v>43</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5" t="s">
@@ -2371,7 +2362,7 @@
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
       <c r="P17" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q17" s="5">
         <v>30</v>
@@ -2398,13 +2389,13 @@
       <c r="AC17" s="5"/>
       <c r="AD17" s="5"/>
       <c r="AE17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF17" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG17" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="AF17" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG17" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="AH17" s="5"/>
       <c r="AI17" s="5"/>
@@ -2419,13 +2410,13 @@
         <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>46</v>
@@ -2441,7 +2432,7 @@
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5">
@@ -2490,20 +2481,20 @@
         <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5" t="s">
@@ -2512,7 +2503,7 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5">
@@ -2561,13 +2552,13 @@
         <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>46</v>
@@ -2615,13 +2606,13 @@
       <c r="AC20" s="5"/>
       <c r="AD20" s="5"/>
       <c r="AE20" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF20" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG20" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH20" s="5">
         <v>1.1366719999999999</v>
@@ -2646,20 +2637,20 @@
         <v>43</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5" t="s">
@@ -2700,13 +2691,13 @@
       <c r="AC21" s="5"/>
       <c r="AD21" s="5"/>
       <c r="AE21" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF21" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG21" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH21" s="5">
         <v>1.101672</v>
@@ -2731,13 +2722,13 @@
         <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>46</v>
@@ -2753,7 +2744,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5">
@@ -2787,7 +2778,7 @@
       <c r="AC22" s="5"/>
       <c r="AD22" s="5"/>
       <c r="AE22" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AF22" s="5"/>
       <c r="AG22" s="5"/>
@@ -2804,20 +2795,20 @@
         <v>43</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5" t="s">
@@ -2826,7 +2817,7 @@
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5">
@@ -2860,7 +2851,7 @@
       <c r="AC23" s="5"/>
       <c r="AD23" s="5"/>
       <c r="AE23" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AF23" s="5"/>
       <c r="AG23" s="5"/>
@@ -2877,13 +2868,13 @@
         <v>43</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>46</v>
@@ -2899,7 +2890,7 @@
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
       <c r="M24" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N24" s="5"/>
       <c r="O24" s="5">
@@ -2948,20 +2939,20 @@
         <v>43</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5" t="s">
@@ -2970,7 +2961,7 @@
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
       <c r="M25" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5">
@@ -3019,13 +3010,13 @@
         <v>43</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>46</v>
@@ -3073,13 +3064,13 @@
       <c r="AC26" s="5"/>
       <c r="AD26" s="5"/>
       <c r="AE26" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AF26" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG26" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AH26" s="5"/>
       <c r="AI26" s="5"/>
@@ -3100,20 +3091,20 @@
         <v>43</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5" t="s">
@@ -3154,13 +3145,13 @@
       <c r="AC27" s="5"/>
       <c r="AD27" s="5"/>
       <c r="AE27" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AF27" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG27" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH27" s="5"/>
       <c r="AI27" s="5"/>
@@ -3181,13 +3172,13 @@
         <v>43</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>46</v>
@@ -3201,7 +3192,7 @@
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
       <c r="M28" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5">
@@ -3214,16 +3205,16 @@
         <v>30</v>
       </c>
       <c r="R28" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S28" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T28" s="5">
+        <v>1</v>
+      </c>
+      <c r="U28" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S28" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T28" s="5">
-        <v>1</v>
-      </c>
-      <c r="U28" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V28" s="5"/>
       <c r="W28" s="5"/>
@@ -3250,20 +3241,20 @@
         <v>43</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5" t="s">
@@ -3272,7 +3263,7 @@
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
       <c r="M29" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5">
@@ -3321,13 +3312,13 @@
         <v>43</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>46</v>
@@ -3375,13 +3366,13 @@
       <c r="AC30" s="5"/>
       <c r="AD30" s="5"/>
       <c r="AE30" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AF30" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG30" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AH30" s="5">
         <v>1.4620299999999999</v>
@@ -3406,20 +3397,20 @@
         <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5" t="s">
@@ -3460,13 +3451,13 @@
       <c r="AC31" s="5"/>
       <c r="AD31" s="5"/>
       <c r="AE31" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AF31" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG31" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AH31" s="5">
         <v>1.4620299999999999</v>
@@ -3491,13 +3482,13 @@
         <v>43</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>46</v>
@@ -3545,13 +3536,13 @@
       <c r="AC32" s="5"/>
       <c r="AD32" s="5"/>
       <c r="AE32" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF32" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG32" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AH32" s="5"/>
       <c r="AI32" s="5"/>
@@ -3572,20 +3563,20 @@
         <v>43</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5" t="s">
@@ -3626,13 +3617,13 @@
       <c r="AC33" s="5"/>
       <c r="AD33" s="5"/>
       <c r="AE33" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AF33" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG33" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AH33" s="5"/>
       <c r="AI33" s="5"/>
@@ -3653,13 +3644,13 @@
         <v>43</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>46</v>
@@ -3675,7 +3666,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="5">
@@ -3724,20 +3715,20 @@
         <v>43</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5" t="s">
@@ -3746,7 +3737,7 @@
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
       <c r="M35" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N35" s="5"/>
       <c r="O35" s="5">
@@ -3795,13 +3786,13 @@
         <v>43</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>46</v>
@@ -3849,13 +3840,13 @@
       <c r="AC36" s="5"/>
       <c r="AD36" s="5"/>
       <c r="AE36" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF36" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG36" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AH36" s="5"/>
       <c r="AI36" s="5"/>
@@ -3876,20 +3867,20 @@
         <v>43</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5" t="s">
@@ -3930,13 +3921,13 @@
       <c r="AC37" s="5"/>
       <c r="AD37" s="5"/>
       <c r="AE37" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF37" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG37" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AH37" s="5"/>
       <c r="AI37" s="5"/>
@@ -3957,13 +3948,13 @@
         <v>43</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>46</v>
@@ -3977,20 +3968,20 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N38" s="5">
         <v>6.5</v>
       </c>
       <c r="O38" s="5"/>
       <c r="P38" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q38" s="5">
         <v>30</v>
       </c>
       <c r="R38" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S38" s="5" t="s">
         <v>52</v>
@@ -4011,7 +4002,7 @@
       <c r="AC38" s="5"/>
       <c r="AD38" s="5"/>
       <c r="AE38" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AF38" s="5"/>
       <c r="AG38" s="5"/>
@@ -4028,13 +4019,13 @@
         <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>46</v>
@@ -4048,20 +4039,20 @@
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
       <c r="M39" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N39" s="5">
         <v>6.5</v>
       </c>
       <c r="O39" s="5"/>
       <c r="P39" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q39" s="5">
         <v>7</v>
       </c>
       <c r="R39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S39" s="5" t="s">
         <v>52</v>
@@ -4082,7 +4073,7 @@
       <c r="AC39" s="5"/>
       <c r="AD39" s="5"/>
       <c r="AE39" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AF39" s="5"/>
       <c r="AG39" s="5"/>
@@ -4099,13 +4090,13 @@
         <v>43</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>46</v>
@@ -4119,20 +4110,20 @@
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N40" s="5">
         <v>5</v>
       </c>
       <c r="O40" s="5"/>
       <c r="P40" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q40" s="5">
         <v>7</v>
       </c>
       <c r="R40" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S40" s="5" t="s">
         <v>52</v>
@@ -4153,7 +4144,7 @@
       <c r="AC40" s="5"/>
       <c r="AD40" s="5"/>
       <c r="AE40" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AF40" s="5"/>
       <c r="AG40" s="5"/>
@@ -4170,13 +4161,13 @@
         <v>43</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>46</v>
@@ -4190,23 +4181,23 @@
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N41" s="5">
         <v>5</v>
       </c>
       <c r="O41" s="5"/>
       <c r="P41" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q41" s="5">
         <v>1</v>
       </c>
       <c r="R41" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S41" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="T41" s="5">
         <v>1</v>
@@ -4224,7 +4215,7 @@
       <c r="AC41" s="5"/>
       <c r="AD41" s="5"/>
       <c r="AE41" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AF41" s="5"/>
       <c r="AG41" s="5"/>
@@ -4241,13 +4232,13 @@
         <v>43</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>46</v>
@@ -4261,23 +4252,23 @@
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N42" s="5">
         <v>4</v>
       </c>
       <c r="O42" s="5"/>
       <c r="P42" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q42" s="5">
         <v>1</v>
       </c>
       <c r="R42" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S42" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="T42" s="5">
         <v>1</v>
@@ -4295,7 +4286,7 @@
       <c r="AC42" s="5"/>
       <c r="AD42" s="5"/>
       <c r="AE42" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AF42" s="5"/>
       <c r="AG42" s="5"/>
@@ -4312,13 +4303,13 @@
         <v>43</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -4330,7 +4321,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N43" s="5">
         <v>6.5</v>
@@ -4339,16 +4330,16 @@
         <v>9</v>
       </c>
       <c r="P43" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q43" s="5">
+        <v>1</v>
+      </c>
+      <c r="R43" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S43" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="Q43" s="5">
-        <v>1</v>
-      </c>
-      <c r="R43" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="S43" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="T43" s="5">
         <v>1</v>
@@ -4381,16 +4372,16 @@
         <v>43</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5" t="s">
@@ -4403,7 +4394,7 @@
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
       <c r="M44" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N44" s="5"/>
       <c r="O44" s="5">
@@ -4437,7 +4428,7 @@
       <c r="AC44" s="5"/>
       <c r="AD44" s="5"/>
       <c r="AE44" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AF44" s="5"/>
       <c r="AG44" s="5"/>
@@ -4454,20 +4445,20 @@
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="5" t="s">
@@ -4476,7 +4467,7 @@
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N45" s="5"/>
       <c r="O45" s="5">
@@ -4489,7 +4480,7 @@
         <v>96</v>
       </c>
       <c r="R45" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S45" s="5" t="s">
         <v>52</v>
@@ -4510,7 +4501,7 @@
       <c r="AC45" s="5"/>
       <c r="AD45" s="5"/>
       <c r="AE45" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AF45" s="5"/>
       <c r="AG45" s="5"/>
@@ -4527,13 +4518,13 @@
         <v>43</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>46</v>
@@ -4581,13 +4572,13 @@
       <c r="AC46" s="5"/>
       <c r="AD46" s="5"/>
       <c r="AE46" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AF46" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG46" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AH46" s="5"/>
       <c r="AI46" s="5"/>
@@ -4608,13 +4599,13 @@
         <v>43</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -4626,21 +4617,21 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
       <c r="P47" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q47" s="5">
+        <v>1</v>
+      </c>
+      <c r="R47" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S47" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="Q47" s="5">
-        <v>1</v>
-      </c>
-      <c r="R47" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="S47" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="T47" s="5">
         <v>1</v>
@@ -4658,7 +4649,7 @@
       <c r="AC47" s="5"/>
       <c r="AD47" s="5"/>
       <c r="AE47" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AF47" s="5"/>
       <c r="AG47" s="5"/>
@@ -4675,13 +4666,13 @@
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -4693,14 +4684,14 @@
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N48" s="5"/>
       <c r="O48" s="5">
         <v>20</v>
       </c>
       <c r="P48" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q48" s="5">
         <v>2</v>
@@ -4742,13 +4733,13 @@
         <v>43</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>46</v>
@@ -4796,13 +4787,13 @@
       <c r="AC49" s="5"/>
       <c r="AD49" s="5"/>
       <c r="AE49" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AF49" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG49" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AH49" s="5"/>
       <c r="AI49" s="5"/>
@@ -4823,20 +4814,20 @@
         <v>43</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I50" s="5"/>
       <c r="J50" s="5" t="s">
@@ -4877,13 +4868,13 @@
       <c r="AC50" s="5"/>
       <c r="AD50" s="5"/>
       <c r="AE50" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF50" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG50" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AH50" s="5"/>
       <c r="AI50" s="5"/>
@@ -4904,16 +4895,16 @@
         <v>43</v>
       </c>
       <c r="C51" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="F51" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
@@ -4924,7 +4915,7 @@
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N51" s="5"/>
       <c r="O51" s="5">
@@ -4937,7 +4928,7 @@
         <v>30</v>
       </c>
       <c r="R51" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S51" s="5" t="s">
         <v>52</v>
@@ -4973,16 +4964,16 @@
         <v>43</v>
       </c>
       <c r="C52" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="F52" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -4993,7 +4984,7 @@
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N52" s="5"/>
       <c r="O52" s="5">
@@ -5006,7 +4997,7 @@
         <v>30</v>
       </c>
       <c r="R52" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S52" s="5" t="s">
         <v>52</v>
@@ -5027,7 +5018,7 @@
       <c r="AC52" s="5"/>
       <c r="AD52" s="5"/>
       <c r="AE52" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF52" s="5"/>
       <c r="AG52" s="5"/>
@@ -5044,16 +5035,16 @@
         <v>43</v>
       </c>
       <c r="C53" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D53" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>142</v>
-      </c>
       <c r="F53" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -5064,7 +5055,7 @@
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N53" s="5"/>
       <c r="O53" s="5">
@@ -5077,7 +5068,7 @@
         <v>30</v>
       </c>
       <c r="R53" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S53" s="5" t="s">
         <v>52</v>
@@ -5113,16 +5104,16 @@
         <v>43</v>
       </c>
       <c r="C54" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E54" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>144</v>
-      </c>
       <c r="F54" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -5133,7 +5124,7 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N54" s="5"/>
       <c r="O54" s="5">
@@ -5146,7 +5137,7 @@
         <v>30</v>
       </c>
       <c r="R54" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S54" s="5" t="s">
         <v>52</v>
@@ -5182,16 +5173,16 @@
         <v>43</v>
       </c>
       <c r="C55" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D55" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="F55" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -5202,7 +5193,7 @@
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N55" s="5"/>
       <c r="O55" s="5">
@@ -5215,7 +5206,7 @@
         <v>30</v>
       </c>
       <c r="R55" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S55" s="5" t="s">
         <v>52</v>
@@ -5251,16 +5242,16 @@
         <v>43</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -5271,7 +5262,7 @@
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N56" s="5"/>
       <c r="O56" s="5">
@@ -5284,7 +5275,7 @@
         <v>30</v>
       </c>
       <c r="R56" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S56" s="5" t="s">
         <v>52</v>
@@ -5320,13 +5311,13 @@
         <v>43</v>
       </c>
       <c r="C57" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>46</v>
@@ -5340,7 +5331,7 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N57" s="5"/>
       <c r="O57" s="5">
@@ -5353,7 +5344,7 @@
         <v>30</v>
       </c>
       <c r="R57" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S57" s="5" t="s">
         <v>52</v>
@@ -5374,7 +5365,7 @@
       <c r="AC57" s="5"/>
       <c r="AD57" s="5"/>
       <c r="AE57" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AF57" s="5"/>
       <c r="AG57" s="5"/>
@@ -5391,16 +5382,16 @@
         <v>43</v>
       </c>
       <c r="C58" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>101</v>
-      </c>
       <c r="F58" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -5411,7 +5402,7 @@
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
       <c r="M58" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N58" s="5"/>
       <c r="O58" s="5">
@@ -5424,7 +5415,7 @@
         <v>30</v>
       </c>
       <c r="R58" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S58" s="5" t="s">
         <v>52</v>
@@ -5460,16 +5451,16 @@
         <v>43</v>
       </c>
       <c r="C59" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D59" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>109</v>
-      </c>
       <c r="F59" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -5480,7 +5471,7 @@
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N59" s="5"/>
       <c r="O59" s="5">
@@ -5493,7 +5484,7 @@
         <v>30</v>
       </c>
       <c r="R59" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S59" s="5" t="s">
         <v>52</v>
@@ -5529,16 +5520,16 @@
         <v>43</v>
       </c>
       <c r="C60" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D60" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="F60" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -5549,7 +5540,7 @@
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N60" s="5"/>
       <c r="O60" s="5">
@@ -5562,7 +5553,7 @@
         <v>30</v>
       </c>
       <c r="R60" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S60" s="5" t="s">
         <v>52</v>
@@ -5598,16 +5589,16 @@
         <v>43</v>
       </c>
       <c r="C61" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D61" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>124</v>
-      </c>
       <c r="F61" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -5618,7 +5609,7 @@
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
       <c r="M61" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N61" s="5"/>
       <c r="O61" s="5">
@@ -5631,7 +5622,7 @@
         <v>30</v>
       </c>
       <c r="R61" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S61" s="5" t="s">
         <v>52</v>
@@ -5667,13 +5658,13 @@
         <v>43</v>
       </c>
       <c r="C62" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E62" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>46</v>
@@ -5687,7 +5678,7 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N62" s="5"/>
       <c r="O62" s="5">
@@ -5700,7 +5691,7 @@
         <v>30</v>
       </c>
       <c r="R62" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S62" s="5" t="s">
         <v>52</v>
@@ -5736,16 +5727,16 @@
         <v>43</v>
       </c>
       <c r="C63" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E63" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D63" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="F63" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -5756,7 +5747,7 @@
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N63" s="5"/>
       <c r="O63" s="5">
@@ -5769,7 +5760,7 @@
         <v>30</v>
       </c>
       <c r="R63" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S63" s="5" t="s">
         <v>52</v>
@@ -5805,16 +5796,16 @@
         <v>43</v>
       </c>
       <c r="C64" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E64" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D64" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>135</v>
-      </c>
       <c r="F64" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -5825,7 +5816,7 @@
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
       <c r="M64" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N64" s="5"/>
       <c r="O64" s="5">
@@ -5838,7 +5829,7 @@
         <v>30</v>
       </c>
       <c r="R64" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S64" s="5" t="s">
         <v>52</v>
@@ -5874,13 +5865,13 @@
         <v>43</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -5892,7 +5883,7 @@
       <c r="K65" s="5"/>
       <c r="L65" s="5"/>
       <c r="M65" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N65" s="5">
         <v>6.5</v>
@@ -5901,22 +5892,22 @@
         <v>9</v>
       </c>
       <c r="P65" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q65" s="5">
+        <v>1</v>
+      </c>
+      <c r="R65" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S65" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="Q65" s="5">
-        <v>1</v>
-      </c>
-      <c r="R65" s="5" t="s">
+      <c r="T65" s="5">
+        <v>1</v>
+      </c>
+      <c r="U65" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S65" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="T65" s="5">
-        <v>1</v>
-      </c>
-      <c r="U65" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V65" s="5"/>
       <c r="W65" s="5"/>
@@ -5943,13 +5934,13 @@
         <v>43</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -5961,20 +5952,20 @@
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
       <c r="M66" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N66" s="5"/>
       <c r="O66" s="5">
         <v>5</v>
       </c>
       <c r="P66" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q66" s="5">
         <v>30</v>
       </c>
       <c r="R66" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S66" s="5" t="s">
         <v>52</v>
@@ -6010,13 +6001,13 @@
         <v>43</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -6028,20 +6019,20 @@
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N67" s="5"/>
       <c r="O67" s="5">
         <v>15</v>
       </c>
       <c r="P67" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q67" s="5">
         <v>30</v>
       </c>
       <c r="R67" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S67" s="5" t="s">
         <v>52</v>
@@ -6077,13 +6068,13 @@
         <v>43</v>
       </c>
       <c r="C68" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E68" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -6095,7 +6086,7 @@
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N68" s="5"/>
       <c r="O68" s="5">
@@ -6108,7 +6099,7 @@
         <v>30</v>
       </c>
       <c r="R68" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S68" s="5" t="s">
         <v>52</v>
@@ -6144,13 +6135,13 @@
         <v>43</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -6162,20 +6153,20 @@
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
       <c r="M69" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N69" s="5"/>
       <c r="O69" s="5">
         <v>0.01</v>
       </c>
       <c r="P69" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q69" s="5">
         <v>30</v>
       </c>
       <c r="R69" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S69" s="5" t="s">
         <v>52</v>
@@ -6211,13 +6202,13 @@
         <v>43</v>
       </c>
       <c r="C70" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E70" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>105</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>46</v>
@@ -6231,7 +6222,7 @@
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
       <c r="M70" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N70" s="5"/>
       <c r="O70" s="5">
@@ -6244,7 +6235,7 @@
         <v>30</v>
       </c>
       <c r="R70" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S70" s="5" t="s">
         <v>52</v>
@@ -6265,7 +6256,7 @@
       <c r="AC70" s="5"/>
       <c r="AD70" s="5"/>
       <c r="AE70" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AF70" s="5"/>
       <c r="AG70" s="5"/>
@@ -6282,16 +6273,16 @@
         <v>43</v>
       </c>
       <c r="C71" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E71" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D71" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="F71" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -6302,7 +6293,7 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N71" s="5"/>
       <c r="O71" s="5">
@@ -6315,7 +6306,7 @@
         <v>30</v>
       </c>
       <c r="R71" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S71" s="5" t="s">
         <v>52</v>
@@ -6351,20 +6342,20 @@
         <v>43</v>
       </c>
       <c r="C72" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E72" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I72" s="5"/>
       <c r="J72" s="5" t="s">
@@ -6373,7 +6364,7 @@
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N72" s="5"/>
       <c r="O72" s="5">
@@ -6386,7 +6377,7 @@
         <v>96</v>
       </c>
       <c r="R72" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S72" s="5" t="s">
         <v>52</v>
@@ -6407,7 +6398,7 @@
       <c r="AC72" s="5"/>
       <c r="AD72" s="5"/>
       <c r="AE72" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AF72" s="5"/>
       <c r="AG72" s="5"/>
@@ -6424,13 +6415,13 @@
         <v>43</v>
       </c>
       <c r="C73" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E73" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>46</v>
@@ -6446,7 +6437,7 @@
       <c r="K73" s="5"/>
       <c r="L73" s="5"/>
       <c r="M73" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N73" s="5"/>
       <c r="O73" s="5">
@@ -6495,20 +6486,20 @@
         <v>43</v>
       </c>
       <c r="C74" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E74" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I74" s="5"/>
       <c r="J74" s="5" t="s">
@@ -6517,7 +6508,7 @@
       <c r="K74" s="5"/>
       <c r="L74" s="5"/>
       <c r="M74" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N74" s="5"/>
       <c r="O74" s="5">
@@ -6566,13 +6557,13 @@
         <v>43</v>
       </c>
       <c r="C75" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E75" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>82</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>46</v>
@@ -6620,13 +6611,13 @@
       <c r="AC75" s="5"/>
       <c r="AD75" s="5"/>
       <c r="AE75" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF75" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG75" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH75" s="5">
         <v>1.1366719999999999</v>
@@ -6651,20 +6642,20 @@
         <v>43</v>
       </c>
       <c r="C76" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E76" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>82</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I76" s="5"/>
       <c r="J76" s="5" t="s">
@@ -6705,13 +6696,13 @@
       <c r="AC76" s="5"/>
       <c r="AD76" s="5"/>
       <c r="AE76" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF76" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG76" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH76" s="5">
         <v>1.101672</v>
@@ -6736,13 +6727,13 @@
         <v>43</v>
       </c>
       <c r="C77" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D77" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D77" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="E77" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>46</v>
@@ -6758,7 +6749,7 @@
       <c r="K77" s="5"/>
       <c r="L77" s="5"/>
       <c r="M77" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N77" s="5"/>
       <c r="O77" s="5">
@@ -6807,20 +6798,20 @@
         <v>43</v>
       </c>
       <c r="C78" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D78" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D78" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="E78" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I78" s="5"/>
       <c r="J78" s="5" t="s">
@@ -6829,7 +6820,7 @@
       <c r="K78" s="5"/>
       <c r="L78" s="5"/>
       <c r="M78" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N78" s="5"/>
       <c r="O78" s="5">
@@ -6878,13 +6869,13 @@
         <v>43</v>
       </c>
       <c r="C79" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E79" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>46</v>
@@ -6932,13 +6923,13 @@
       <c r="AC79" s="5"/>
       <c r="AD79" s="5"/>
       <c r="AE79" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AF79" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG79" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AH79" s="5"/>
       <c r="AI79" s="5"/>
@@ -6959,20 +6950,20 @@
         <v>43</v>
       </c>
       <c r="C80" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5" t="s">
@@ -7013,13 +7004,13 @@
       <c r="AC80" s="5"/>
       <c r="AD80" s="5"/>
       <c r="AE80" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AF80" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG80" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH80" s="5"/>
       <c r="AI80" s="5"/>
@@ -7040,20 +7031,20 @@
         <v>43</v>
       </c>
       <c r="C81" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E81" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I81" s="5"/>
       <c r="J81" s="5" t="s">
@@ -7062,7 +7053,7 @@
       <c r="K81" s="5"/>
       <c r="L81" s="5"/>
       <c r="M81" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N81" s="5"/>
       <c r="O81" s="5">
@@ -7111,13 +7102,13 @@
         <v>43</v>
       </c>
       <c r="C82" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E82" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>46</v>
@@ -7165,13 +7156,13 @@
       <c r="AC82" s="5"/>
       <c r="AD82" s="5"/>
       <c r="AE82" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AF82" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG82" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AH82" s="5">
         <v>1.4620299999999999</v>
@@ -7196,20 +7187,20 @@
         <v>43</v>
       </c>
       <c r="C83" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E83" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I83" s="5"/>
       <c r="J83" s="5" t="s">
@@ -7250,13 +7241,13 @@
       <c r="AC83" s="5"/>
       <c r="AD83" s="5"/>
       <c r="AE83" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AF83" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG83" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AH83" s="5">
         <v>1.4620299999999999</v>
@@ -7281,13 +7272,13 @@
         <v>43</v>
       </c>
       <c r="C84" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E84" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>105</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>46</v>
@@ -7335,13 +7326,13 @@
       <c r="AC84" s="5"/>
       <c r="AD84" s="5"/>
       <c r="AE84" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF84" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG84" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AH84" s="5"/>
       <c r="AI84" s="5"/>
@@ -7362,20 +7353,20 @@
         <v>43</v>
       </c>
       <c r="C85" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E85" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>105</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I85" s="5"/>
       <c r="J85" s="5" t="s">
@@ -7416,13 +7407,13 @@
       <c r="AC85" s="5"/>
       <c r="AD85" s="5"/>
       <c r="AE85" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AF85" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG85" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AH85" s="5"/>
       <c r="AI85" s="5"/>
@@ -7443,13 +7434,13 @@
         <v>43</v>
       </c>
       <c r="C86" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E86" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>46</v>
@@ -7465,7 +7456,7 @@
       <c r="K86" s="5"/>
       <c r="L86" s="5"/>
       <c r="M86" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N86" s="5"/>
       <c r="O86" s="5">
@@ -7514,20 +7505,20 @@
         <v>43</v>
       </c>
       <c r="C87" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E87" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I87" s="5"/>
       <c r="J87" s="5" t="s">
@@ -7536,7 +7527,7 @@
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
       <c r="M87" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N87" s="5"/>
       <c r="O87" s="5">
@@ -7585,13 +7576,13 @@
         <v>43</v>
       </c>
       <c r="C88" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>111</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>46</v>
@@ -7639,13 +7630,13 @@
       <c r="AC88" s="5"/>
       <c r="AD88" s="5"/>
       <c r="AE88" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF88" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG88" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AH88" s="5"/>
       <c r="AI88" s="5"/>
@@ -7666,20 +7657,20 @@
         <v>43</v>
       </c>
       <c r="C89" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>111</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I89" s="5"/>
       <c r="J89" s="5" t="s">
@@ -7720,13 +7711,13 @@
       <c r="AC89" s="5"/>
       <c r="AD89" s="5"/>
       <c r="AE89" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF89" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG89" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AH89" s="5"/>
       <c r="AI89" s="5"/>
@@ -7747,13 +7738,13 @@
         <v>43</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>59</v>
+        <v>173</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
@@ -7765,7 +7756,7 @@
       <c r="K90" s="5"/>
       <c r="L90" s="5"/>
       <c r="M90" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N90" s="5">
         <v>6.5</v>
@@ -7774,16 +7765,16 @@
         <v>9</v>
       </c>
       <c r="P90" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q90" s="5">
+        <v>1</v>
+      </c>
+      <c r="R90" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S90" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="Q90" s="5">
-        <v>1</v>
-      </c>
-      <c r="R90" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="S90" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="T90" s="5">
         <v>1</v>
@@ -7816,16 +7807,16 @@
         <v>43</v>
       </c>
       <c r="C91" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D91" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>124</v>
-      </c>
       <c r="F91" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5" t="s">
@@ -7838,7 +7829,7 @@
       <c r="K91" s="5"/>
       <c r="L91" s="5"/>
       <c r="M91" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N91" s="5"/>
       <c r="O91" s="5">
@@ -7872,7 +7863,7 @@
       <c r="AC91" s="5"/>
       <c r="AD91" s="5"/>
       <c r="AE91" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AF91" s="5"/>
       <c r="AG91" s="5"/>
@@ -7889,20 +7880,20 @@
         <v>43</v>
       </c>
       <c r="C92" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E92" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D92" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>124</v>
-      </c>
       <c r="F92" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I92" s="5"/>
       <c r="J92" s="5" t="s">
@@ -7911,7 +7902,7 @@
       <c r="K92" s="5"/>
       <c r="L92" s="5"/>
       <c r="M92" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N92" s="5"/>
       <c r="O92" s="5">
@@ -7924,7 +7915,7 @@
         <v>96</v>
       </c>
       <c r="R92" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S92" s="5" t="s">
         <v>52</v>
@@ -7945,7 +7936,7 @@
       <c r="AC92" s="5"/>
       <c r="AD92" s="5"/>
       <c r="AE92" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AF92" s="5"/>
       <c r="AG92" s="5"/>
@@ -7962,13 +7953,13 @@
         <v>43</v>
       </c>
       <c r="C93" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>46</v>
@@ -8016,13 +8007,13 @@
       <c r="AC93" s="5"/>
       <c r="AD93" s="5"/>
       <c r="AE93" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AF93" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG93" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AH93" s="5"/>
       <c r="AI93" s="5"/>
@@ -8043,13 +8034,13 @@
         <v>43</v>
       </c>
       <c r="C94" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E94" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>135</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>46</v>
@@ -8097,13 +8088,13 @@
       <c r="AC94" s="5"/>
       <c r="AD94" s="5"/>
       <c r="AE94" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AF94" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG94" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AH94" s="5"/>
       <c r="AI94" s="5"/>
@@ -8124,20 +8115,20 @@
         <v>43</v>
       </c>
       <c r="C95" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E95" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>135</v>
       </c>
       <c r="F95" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I95" s="5"/>
       <c r="J95" s="5" t="s">
@@ -8157,7 +8148,7 @@
         <v>96</v>
       </c>
       <c r="R95" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S95" s="5" t="s">
         <v>52</v>
@@ -8178,13 +8169,13 @@
       <c r="AC95" s="5"/>
       <c r="AD95" s="5"/>
       <c r="AE95" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF95" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG95" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AH95" s="5"/>
       <c r="AI95" s="5"/>
@@ -8205,13 +8196,13 @@
         <v>43</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
@@ -8223,29 +8214,29 @@
       <c r="K96" s="5"/>
       <c r="L96" s="5"/>
       <c r="M96" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N96" s="5"/>
       <c r="O96" s="5">
         <v>126</v>
       </c>
       <c r="P96" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q96" s="5">
         <v>60</v>
       </c>
       <c r="R96" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S96" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="T96" s="5">
+        <v>1</v>
+      </c>
+      <c r="U96" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S96" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="T96" s="5">
-        <v>1</v>
-      </c>
-      <c r="U96" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V96" s="5"/>
       <c r="W96" s="5"/>
@@ -8257,7 +8248,7 @@
       <c r="AC96" s="5"/>
       <c r="AD96" s="5"/>
       <c r="AE96" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AF96" s="5"/>
       <c r="AG96" s="5"/>
@@ -8274,13 +8265,13 @@
         <v>43</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
@@ -8292,7 +8283,7 @@
       <c r="K97" s="5"/>
       <c r="L97" s="5"/>
       <c r="M97" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N97" s="5">
         <v>6.5</v>
@@ -8301,22 +8292,22 @@
         <v>9</v>
       </c>
       <c r="P97" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q97" s="5">
+        <v>1</v>
+      </c>
+      <c r="R97" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S97" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="Q97" s="5">
-        <v>1</v>
-      </c>
-      <c r="R97" s="5" t="s">
+      <c r="T97" s="5">
+        <v>1</v>
+      </c>
+      <c r="U97" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S97" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="T97" s="5">
-        <v>1</v>
-      </c>
-      <c r="U97" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V97" s="5"/>
       <c r="W97" s="5"/>
@@ -8343,16 +8334,16 @@
         <v>43</v>
       </c>
       <c r="C98" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E98" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D98" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="F98" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
@@ -8363,7 +8354,7 @@
       <c r="K98" s="5"/>
       <c r="L98" s="5"/>
       <c r="M98" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N98" s="5"/>
       <c r="O98" s="5">
@@ -8376,16 +8367,16 @@
         <v>30</v>
       </c>
       <c r="R98" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S98" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T98" s="5">
+        <v>1</v>
+      </c>
+      <c r="U98" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S98" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T98" s="5">
-        <v>1</v>
-      </c>
-      <c r="U98" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V98" s="5"/>
       <c r="W98" s="5"/>
@@ -8412,16 +8403,16 @@
         <v>43</v>
       </c>
       <c r="C99" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E99" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D99" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="F99" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
@@ -8432,7 +8423,7 @@
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
       <c r="M99" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N99" s="5"/>
       <c r="O99" s="5">
@@ -8445,16 +8436,16 @@
         <v>30</v>
       </c>
       <c r="R99" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S99" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T99" s="5">
+        <v>1</v>
+      </c>
+      <c r="U99" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S99" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T99" s="5">
-        <v>1</v>
-      </c>
-      <c r="U99" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V99" s="5"/>
       <c r="W99" s="5"/>
@@ -8481,16 +8472,16 @@
         <v>43</v>
       </c>
       <c r="C100" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E100" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D100" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>109</v>
-      </c>
       <c r="F100" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
@@ -8501,7 +8492,7 @@
       <c r="K100" s="5"/>
       <c r="L100" s="5"/>
       <c r="M100" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N100" s="5"/>
       <c r="O100" s="5">
@@ -8514,16 +8505,16 @@
         <v>30</v>
       </c>
       <c r="R100" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S100" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T100" s="5">
+        <v>1</v>
+      </c>
+      <c r="U100" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S100" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T100" s="5">
-        <v>1</v>
-      </c>
-      <c r="U100" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V100" s="5"/>
       <c r="W100" s="5"/>
@@ -8550,16 +8541,16 @@
         <v>43</v>
       </c>
       <c r="C101" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E101" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="F101" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
@@ -8570,7 +8561,7 @@
       <c r="K101" s="5"/>
       <c r="L101" s="5"/>
       <c r="M101" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N101" s="5"/>
       <c r="O101" s="5">
@@ -8583,16 +8574,16 @@
         <v>30</v>
       </c>
       <c r="R101" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S101" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T101" s="5">
+        <v>1</v>
+      </c>
+      <c r="U101" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S101" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T101" s="5">
-        <v>1</v>
-      </c>
-      <c r="U101" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V101" s="5"/>
       <c r="W101" s="5"/>
@@ -8619,16 +8610,16 @@
         <v>43</v>
       </c>
       <c r="C102" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E102" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D102" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>124</v>
-      </c>
       <c r="F102" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5"/>
@@ -8639,7 +8630,7 @@
       <c r="K102" s="5"/>
       <c r="L102" s="5"/>
       <c r="M102" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N102" s="5"/>
       <c r="O102" s="5">
@@ -8652,16 +8643,16 @@
         <v>30</v>
       </c>
       <c r="R102" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S102" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T102" s="5">
+        <v>1</v>
+      </c>
+      <c r="U102" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S102" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T102" s="5">
-        <v>1</v>
-      </c>
-      <c r="U102" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V102" s="5"/>
       <c r="W102" s="5"/>
@@ -8688,16 +8679,16 @@
         <v>43</v>
       </c>
       <c r="C103" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E103" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D103" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="F103" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
@@ -8708,7 +8699,7 @@
       <c r="K103" s="5"/>
       <c r="L103" s="5"/>
       <c r="M103" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N103" s="5"/>
       <c r="O103" s="5">
@@ -8721,16 +8712,16 @@
         <v>30</v>
       </c>
       <c r="R103" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S103" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T103" s="5">
+        <v>1</v>
+      </c>
+      <c r="U103" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S103" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T103" s="5">
-        <v>1</v>
-      </c>
-      <c r="U103" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V103" s="5"/>
       <c r="W103" s="5"/>
@@ -8757,16 +8748,16 @@
         <v>43</v>
       </c>
       <c r="C104" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E104" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D104" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>135</v>
-      </c>
       <c r="F104" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
@@ -8777,7 +8768,7 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N104" s="5"/>
       <c r="O104" s="5">
@@ -8790,16 +8781,16 @@
         <v>30</v>
       </c>
       <c r="R104" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S104" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T104" s="5">
+        <v>1</v>
+      </c>
+      <c r="U104" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S104" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T104" s="5">
-        <v>1</v>
-      </c>
-      <c r="U104" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V104" s="5"/>
       <c r="W104" s="5"/>
@@ -8826,13 +8817,13 @@
         <v>43</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F105" s="5"/>
       <c r="G105" s="5"/>
@@ -8844,7 +8835,7 @@
       <c r="K105" s="5"/>
       <c r="L105" s="5"/>
       <c r="M105" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N105" s="5">
         <v>6.5</v>
@@ -8853,22 +8844,22 @@
         <v>9</v>
       </c>
       <c r="P105" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q105" s="5">
         <v>30</v>
       </c>
       <c r="R105" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S105" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="T105" s="5">
+        <v>1</v>
+      </c>
+      <c r="U105" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S105" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="T105" s="5">
-        <v>1</v>
-      </c>
-      <c r="U105" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V105" s="5"/>
       <c r="W105" s="5"/>
@@ -8895,16 +8886,16 @@
         <v>43</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E106" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
@@ -8915,7 +8906,7 @@
       <c r="K106" s="5"/>
       <c r="L106" s="5"/>
       <c r="M106" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N106" s="5"/>
       <c r="O106" s="5">
@@ -8928,16 +8919,16 @@
         <v>30</v>
       </c>
       <c r="R106" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S106" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T106" s="5">
+        <v>1</v>
+      </c>
+      <c r="U106" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S106" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T106" s="5">
-        <v>1</v>
-      </c>
-      <c r="U106" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V106" s="5"/>
       <c r="W106" s="5"/>
@@ -8964,13 +8955,13 @@
         <v>43</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F107" s="5"/>
       <c r="G107" s="5"/>
@@ -8982,7 +8973,7 @@
       <c r="K107" s="5"/>
       <c r="L107" s="5"/>
       <c r="M107" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N107" s="5">
         <v>6.5</v>
@@ -8991,22 +8982,22 @@
         <v>9</v>
       </c>
       <c r="P107" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q107" s="5">
+        <v>1</v>
+      </c>
+      <c r="R107" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S107" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="Q107" s="5">
-        <v>1</v>
-      </c>
-      <c r="R107" s="5" t="s">
+      <c r="T107" s="5">
+        <v>1</v>
+      </c>
+      <c r="U107" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S107" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="T107" s="5">
-        <v>1</v>
-      </c>
-      <c r="U107" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V107" s="5"/>
       <c r="W107" s="5"/>
@@ -9033,13 +9024,13 @@
         <v>43</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F108" s="5"/>
       <c r="G108" s="5"/>
@@ -9051,7 +9042,7 @@
       <c r="K108" s="5"/>
       <c r="L108" s="5"/>
       <c r="M108" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N108" s="5">
         <v>6.5</v>
@@ -9060,22 +9051,22 @@
         <v>9</v>
       </c>
       <c r="P108" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q108" s="5">
+        <v>1</v>
+      </c>
+      <c r="R108" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S108" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="Q108" s="5">
-        <v>1</v>
-      </c>
-      <c r="R108" s="5" t="s">
+      <c r="T108" s="5">
+        <v>1</v>
+      </c>
+      <c r="U108" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S108" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="T108" s="5">
-        <v>1</v>
-      </c>
-      <c r="U108" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V108" s="5"/>
       <c r="W108" s="5"/>
@@ -9102,13 +9093,13 @@
         <v>43</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>46</v>
@@ -9124,7 +9115,7 @@
       <c r="K109" s="5"/>
       <c r="L109" s="5"/>
       <c r="M109" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N109" s="5"/>
       <c r="O109" s="5">
@@ -9158,7 +9149,7 @@
       <c r="AC109" s="5"/>
       <c r="AD109" s="5"/>
       <c r="AE109" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AF109" s="5"/>
       <c r="AG109" s="5"/>
@@ -9175,20 +9166,20 @@
         <v>43</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I110" s="5"/>
       <c r="J110" s="5" t="s">
@@ -9197,7 +9188,7 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N110" s="5"/>
       <c r="O110" s="5">
@@ -9210,7 +9201,7 @@
         <v>96</v>
       </c>
       <c r="R110" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S110" s="5" t="s">
         <v>52</v>
@@ -9231,7 +9222,7 @@
       <c r="AC110" s="5"/>
       <c r="AD110" s="5"/>
       <c r="AE110" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AF110" s="5"/>
       <c r="AG110" s="5"/>
@@ -9248,13 +9239,13 @@
         <v>43</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>46</v>
@@ -9270,7 +9261,7 @@
       <c r="K111" s="5"/>
       <c r="L111" s="5"/>
       <c r="M111" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N111" s="5"/>
       <c r="O111" s="5">
@@ -9319,20 +9310,20 @@
         <v>43</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I112" s="5"/>
       <c r="J112" s="5" t="s">
@@ -9341,7 +9332,7 @@
       <c r="K112" s="5"/>
       <c r="L112" s="5"/>
       <c r="M112" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N112" s="5"/>
       <c r="O112" s="5">
@@ -9354,7 +9345,7 @@
         <v>96</v>
       </c>
       <c r="R112" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S112" s="5" t="s">
         <v>52</v>
@@ -9390,13 +9381,13 @@
         <v>43</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>46</v>
@@ -9444,13 +9435,13 @@
       <c r="AC113" s="5"/>
       <c r="AD113" s="5"/>
       <c r="AE113" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF113" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG113" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH113" s="5">
         <v>1.1366719999999999</v>
@@ -9475,20 +9466,20 @@
         <v>43</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I114" s="5"/>
       <c r="J114" s="5" t="s">
@@ -9508,7 +9499,7 @@
         <v>96</v>
       </c>
       <c r="R114" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S114" s="5" t="s">
         <v>52</v>
@@ -9529,13 +9520,13 @@
       <c r="AC114" s="5"/>
       <c r="AD114" s="5"/>
       <c r="AE114" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF114" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG114" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH114" s="5">
         <v>1.101672</v>
@@ -9560,13 +9551,13 @@
         <v>43</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F115" s="5" t="s">
         <v>46</v>
@@ -9582,7 +9573,7 @@
       <c r="K115" s="5"/>
       <c r="L115" s="5"/>
       <c r="M115" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N115" s="5"/>
       <c r="O115" s="5">
@@ -9631,20 +9622,20 @@
         <v>43</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F116" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I116" s="5"/>
       <c r="J116" s="5" t="s">
@@ -9653,7 +9644,7 @@
       <c r="K116" s="5"/>
       <c r="L116" s="5"/>
       <c r="M116" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N116" s="5"/>
       <c r="O116" s="5">
@@ -9666,7 +9657,7 @@
         <v>96</v>
       </c>
       <c r="R116" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S116" s="5" t="s">
         <v>52</v>
@@ -9702,13 +9693,13 @@
         <v>43</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>46</v>
@@ -9756,13 +9747,13 @@
       <c r="AC117" s="5"/>
       <c r="AD117" s="5"/>
       <c r="AE117" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AF117" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG117" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AH117" s="5"/>
       <c r="AI117" s="5"/>
@@ -9783,20 +9774,20 @@
         <v>43</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I118" s="5"/>
       <c r="J118" s="5" t="s">
@@ -9816,7 +9807,7 @@
         <v>96</v>
       </c>
       <c r="R118" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S118" s="5" t="s">
         <v>52</v>
@@ -9837,13 +9828,13 @@
       <c r="AC118" s="5"/>
       <c r="AD118" s="5"/>
       <c r="AE118" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AF118" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG118" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH118" s="5"/>
       <c r="AI118" s="5"/>
@@ -9864,20 +9855,20 @@
         <v>43</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I119" s="5"/>
       <c r="J119" s="5" t="s">
@@ -9886,7 +9877,7 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N119" s="5"/>
       <c r="O119" s="5">
@@ -9899,7 +9890,7 @@
         <v>96</v>
       </c>
       <c r="R119" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S119" s="5" t="s">
         <v>52</v>
@@ -9935,13 +9926,13 @@
         <v>43</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F120" s="5" t="s">
         <v>46</v>
@@ -9989,13 +9980,13 @@
       <c r="AC120" s="5"/>
       <c r="AD120" s="5"/>
       <c r="AE120" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AF120" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG120" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AH120" s="5">
         <v>1.4620299999999999</v>
@@ -10020,20 +10011,20 @@
         <v>43</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G121" s="5"/>
       <c r="H121" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I121" s="5"/>
       <c r="J121" s="5" t="s">
@@ -10053,7 +10044,7 @@
         <v>96</v>
       </c>
       <c r="R121" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S121" s="5" t="s">
         <v>52</v>
@@ -10074,13 +10065,13 @@
       <c r="AC121" s="5"/>
       <c r="AD121" s="5"/>
       <c r="AE121" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AF121" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG121" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AH121" s="5">
         <v>1.4620299999999999</v>
@@ -10105,13 +10096,13 @@
         <v>43</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>46</v>
@@ -10159,13 +10150,13 @@
       <c r="AC122" s="5"/>
       <c r="AD122" s="5"/>
       <c r="AE122" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF122" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG122" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AH122" s="5"/>
       <c r="AI122" s="5"/>
@@ -10186,20 +10177,20 @@
         <v>43</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I123" s="5"/>
       <c r="J123" s="5" t="s">
@@ -10219,7 +10210,7 @@
         <v>96</v>
       </c>
       <c r="R123" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S123" s="5" t="s">
         <v>52</v>
@@ -10240,13 +10231,13 @@
       <c r="AC123" s="5"/>
       <c r="AD123" s="5"/>
       <c r="AE123" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AF123" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG123" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AH123" s="5"/>
       <c r="AI123" s="5"/>
@@ -10267,13 +10258,13 @@
         <v>43</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>46</v>
@@ -10289,7 +10280,7 @@
       <c r="K124" s="5"/>
       <c r="L124" s="5"/>
       <c r="M124" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N124" s="5"/>
       <c r="O124" s="5">
@@ -10338,20 +10329,20 @@
         <v>43</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I125" s="5"/>
       <c r="J125" s="5" t="s">
@@ -10360,7 +10351,7 @@
       <c r="K125" s="5"/>
       <c r="L125" s="5"/>
       <c r="M125" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N125" s="5"/>
       <c r="O125" s="5">
@@ -10373,7 +10364,7 @@
         <v>96</v>
       </c>
       <c r="R125" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S125" s="5" t="s">
         <v>52</v>
@@ -10409,13 +10400,13 @@
         <v>43</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>46</v>
@@ -10463,13 +10454,13 @@
       <c r="AC126" s="5"/>
       <c r="AD126" s="5"/>
       <c r="AE126" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF126" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG126" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AH126" s="5"/>
       <c r="AI126" s="5"/>
@@ -10490,20 +10481,20 @@
         <v>43</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I127" s="5"/>
       <c r="J127" s="5" t="s">
@@ -10523,7 +10514,7 @@
         <v>96</v>
       </c>
       <c r="R127" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S127" s="5" t="s">
         <v>52</v>
@@ -10544,13 +10535,13 @@
       <c r="AC127" s="5"/>
       <c r="AD127" s="5"/>
       <c r="AE127" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF127" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG127" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AH127" s="5"/>
       <c r="AI127" s="5"/>
@@ -10571,13 +10562,13 @@
         <v>43</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F128" s="5"/>
       <c r="G128" s="5"/>
@@ -10589,7 +10580,7 @@
       <c r="K128" s="5"/>
       <c r="L128" s="5"/>
       <c r="M128" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N128" s="5">
         <v>6.5</v>
@@ -10598,16 +10589,16 @@
         <v>9</v>
       </c>
       <c r="P128" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q128" s="5">
+        <v>1</v>
+      </c>
+      <c r="R128" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S128" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="Q128" s="5">
-        <v>1</v>
-      </c>
-      <c r="R128" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="S128" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="T128" s="5">
         <v>1</v>
@@ -10640,16 +10631,16 @@
         <v>43</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5" t="s">
@@ -10662,7 +10653,7 @@
       <c r="K129" s="5"/>
       <c r="L129" s="5"/>
       <c r="M129" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N129" s="5"/>
       <c r="O129" s="5">
@@ -10696,7 +10687,7 @@
       <c r="AC129" s="5"/>
       <c r="AD129" s="5"/>
       <c r="AE129" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AF129" s="5"/>
       <c r="AG129" s="5"/>
@@ -10713,20 +10704,20 @@
         <v>43</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G130" s="5"/>
       <c r="H130" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I130" s="5"/>
       <c r="J130" s="5" t="s">
@@ -10735,7 +10726,7 @@
       <c r="K130" s="5"/>
       <c r="L130" s="5"/>
       <c r="M130" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N130" s="5"/>
       <c r="O130" s="5">
@@ -10748,7 +10739,7 @@
         <v>96</v>
       </c>
       <c r="R130" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S130" s="5" t="s">
         <v>52</v>
@@ -10769,7 +10760,7 @@
       <c r="AC130" s="5"/>
       <c r="AD130" s="5"/>
       <c r="AE130" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AF130" s="5"/>
       <c r="AG130" s="5"/>
@@ -10786,13 +10777,13 @@
         <v>43</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>46</v>
@@ -10840,13 +10831,13 @@
       <c r="AC131" s="5"/>
       <c r="AD131" s="5"/>
       <c r="AE131" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AF131" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG131" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AH131" s="5"/>
       <c r="AI131" s="5"/>
@@ -10867,13 +10858,13 @@
         <v>43</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>46</v>
@@ -10921,13 +10912,13 @@
       <c r="AC132" s="5"/>
       <c r="AD132" s="5"/>
       <c r="AE132" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AF132" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG132" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AH132" s="5"/>
       <c r="AI132" s="5"/>
@@ -10948,20 +10939,20 @@
         <v>43</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G133" s="5"/>
       <c r="H133" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I133" s="5"/>
       <c r="J133" s="5" t="s">
@@ -10981,7 +10972,7 @@
         <v>96</v>
       </c>
       <c r="R133" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S133" s="5" t="s">
         <v>52</v>
@@ -11002,13 +10993,13 @@
       <c r="AC133" s="5"/>
       <c r="AD133" s="5"/>
       <c r="AE133" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF133" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG133" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AH133" s="5"/>
       <c r="AI133" s="5"/>
@@ -11029,13 +11020,13 @@
         <v>43</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F134" s="5"/>
       <c r="G134" s="5"/>
@@ -11047,29 +11038,29 @@
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
       <c r="M134" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N134" s="5"/>
       <c r="O134" s="5">
         <v>630</v>
       </c>
       <c r="P134" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q134" s="5">
         <v>60</v>
       </c>
       <c r="R134" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S134" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="T134" s="5">
+        <v>1</v>
+      </c>
+      <c r="U134" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S134" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="T134" s="5">
-        <v>1</v>
-      </c>
-      <c r="U134" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V134" s="5"/>
       <c r="W134" s="5"/>
@@ -11096,13 +11087,13 @@
         <v>43</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F135" s="5"/>
       <c r="G135" s="5"/>
@@ -11114,7 +11105,7 @@
       <c r="K135" s="5"/>
       <c r="L135" s="5"/>
       <c r="M135" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N135" s="5">
         <v>6.5</v>
@@ -11123,22 +11114,22 @@
         <v>9</v>
       </c>
       <c r="P135" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q135" s="5">
+        <v>1</v>
+      </c>
+      <c r="R135" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S135" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="Q135" s="5">
-        <v>1</v>
-      </c>
-      <c r="R135" s="5" t="s">
+      <c r="T135" s="5">
+        <v>1</v>
+      </c>
+      <c r="U135" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S135" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="T135" s="5">
-        <v>1</v>
-      </c>
-      <c r="U135" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V135" s="5"/>
       <c r="W135" s="5"/>
@@ -11165,13 +11156,13 @@
         <v>43</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F136" s="5"/>
       <c r="G136" s="5"/>
@@ -11183,7 +11174,7 @@
       <c r="K136" s="5"/>
       <c r="L136" s="5"/>
       <c r="M136" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N136" s="5">
         <v>6.5</v>
@@ -11192,22 +11183,22 @@
         <v>9</v>
       </c>
       <c r="P136" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q136" s="5">
+        <v>1</v>
+      </c>
+      <c r="R136" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S136" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="Q136" s="5">
-        <v>1</v>
-      </c>
-      <c r="R136" s="5" t="s">
+      <c r="T136" s="5">
+        <v>1</v>
+      </c>
+      <c r="U136" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S136" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="T136" s="5">
-        <v>1</v>
-      </c>
-      <c r="U136" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V136" s="5"/>
       <c r="W136" s="5"/>
@@ -11234,13 +11225,13 @@
         <v>43</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>46</v>
@@ -11256,7 +11247,7 @@
       <c r="K137" s="5"/>
       <c r="L137" s="5"/>
       <c r="M137" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N137" s="5"/>
       <c r="O137" s="5">
@@ -11290,7 +11281,7 @@
       <c r="AC137" s="5"/>
       <c r="AD137" s="5"/>
       <c r="AE137" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AF137" s="5"/>
       <c r="AG137" s="5"/>
@@ -11307,20 +11298,20 @@
         <v>43</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I138" s="5"/>
       <c r="J138" s="5" t="s">
@@ -11329,7 +11320,7 @@
       <c r="K138" s="5"/>
       <c r="L138" s="5"/>
       <c r="M138" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N138" s="5"/>
       <c r="O138" s="5">
@@ -11342,7 +11333,7 @@
         <v>96</v>
       </c>
       <c r="R138" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S138" s="5" t="s">
         <v>52</v>
@@ -11363,7 +11354,7 @@
       <c r="AC138" s="5"/>
       <c r="AD138" s="5"/>
       <c r="AE138" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AF138" s="5"/>
       <c r="AG138" s="5"/>
@@ -11380,13 +11371,13 @@
         <v>43</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>46</v>
@@ -11402,7 +11393,7 @@
       <c r="K139" s="5"/>
       <c r="L139" s="5"/>
       <c r="M139" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N139" s="5"/>
       <c r="O139" s="5">
@@ -11451,20 +11442,20 @@
         <v>43</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I140" s="5"/>
       <c r="J140" s="5" t="s">
@@ -11473,7 +11464,7 @@
       <c r="K140" s="5"/>
       <c r="L140" s="5"/>
       <c r="M140" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N140" s="5"/>
       <c r="O140" s="5">
@@ -11486,7 +11477,7 @@
         <v>96</v>
       </c>
       <c r="R140" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S140" s="5" t="s">
         <v>52</v>
@@ -11522,13 +11513,13 @@
         <v>43</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>46</v>
@@ -11576,13 +11567,13 @@
       <c r="AC141" s="5"/>
       <c r="AD141" s="5"/>
       <c r="AE141" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF141" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG141" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH141" s="5">
         <v>1.1366719999999999</v>
@@ -11607,20 +11598,20 @@
         <v>43</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I142" s="5"/>
       <c r="J142" s="5" t="s">
@@ -11640,7 +11631,7 @@
         <v>96</v>
       </c>
       <c r="R142" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S142" s="5" t="s">
         <v>52</v>
@@ -11661,13 +11652,13 @@
       <c r="AC142" s="5"/>
       <c r="AD142" s="5"/>
       <c r="AE142" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF142" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG142" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH142" s="5">
         <v>1.101672</v>
@@ -11692,13 +11683,13 @@
         <v>43</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>46</v>
@@ -11714,7 +11705,7 @@
       <c r="K143" s="5"/>
       <c r="L143" s="5"/>
       <c r="M143" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N143" s="5"/>
       <c r="O143" s="5">
@@ -11748,7 +11739,7 @@
       <c r="AC143" s="5"/>
       <c r="AD143" s="5"/>
       <c r="AE143" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AF143" s="5"/>
       <c r="AG143" s="5"/>
@@ -11765,20 +11756,20 @@
         <v>43</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I144" s="5"/>
       <c r="J144" s="5" t="s">
@@ -11787,7 +11778,7 @@
       <c r="K144" s="5"/>
       <c r="L144" s="5"/>
       <c r="M144" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N144" s="5"/>
       <c r="O144" s="5">
@@ -11800,7 +11791,7 @@
         <v>96</v>
       </c>
       <c r="R144" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S144" s="5" t="s">
         <v>52</v>
@@ -11821,7 +11812,7 @@
       <c r="AC144" s="5"/>
       <c r="AD144" s="5"/>
       <c r="AE144" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AF144" s="5"/>
       <c r="AG144" s="5"/>
@@ -11838,13 +11829,13 @@
         <v>43</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>46</v>
@@ -11860,7 +11851,7 @@
       <c r="K145" s="5"/>
       <c r="L145" s="5"/>
       <c r="M145" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N145" s="5"/>
       <c r="O145" s="5">
@@ -11909,20 +11900,20 @@
         <v>43</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I146" s="5"/>
       <c r="J146" s="5" t="s">
@@ -11931,7 +11922,7 @@
       <c r="K146" s="5"/>
       <c r="L146" s="5"/>
       <c r="M146" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N146" s="5"/>
       <c r="O146" s="5">
@@ -11944,7 +11935,7 @@
         <v>96</v>
       </c>
       <c r="R146" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S146" s="5" t="s">
         <v>52</v>
@@ -11980,13 +11971,13 @@
         <v>43</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>46</v>
@@ -12034,13 +12025,13 @@
       <c r="AC147" s="5"/>
       <c r="AD147" s="5"/>
       <c r="AE147" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AF147" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG147" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AH147" s="5"/>
       <c r="AI147" s="5"/>
@@ -12061,20 +12052,20 @@
         <v>43</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I148" s="5"/>
       <c r="J148" s="5" t="s">
@@ -12094,7 +12085,7 @@
         <v>96</v>
       </c>
       <c r="R148" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S148" s="5" t="s">
         <v>52</v>
@@ -12115,13 +12106,13 @@
       <c r="AC148" s="5"/>
       <c r="AD148" s="5"/>
       <c r="AE148" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AF148" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG148" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH148" s="5"/>
       <c r="AI148" s="5"/>
@@ -12142,20 +12133,20 @@
         <v>43</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I149" s="5"/>
       <c r="J149" s="5" t="s">
@@ -12164,7 +12155,7 @@
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
       <c r="M149" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N149" s="5"/>
       <c r="O149" s="5">
@@ -12177,7 +12168,7 @@
         <v>96</v>
       </c>
       <c r="R149" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S149" s="5" t="s">
         <v>52</v>
@@ -12213,13 +12204,13 @@
         <v>43</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>46</v>
@@ -12267,13 +12258,13 @@
       <c r="AC150" s="5"/>
       <c r="AD150" s="5"/>
       <c r="AE150" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AF150" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG150" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AH150" s="5">
         <v>1.4620299999999999</v>
@@ -12298,20 +12289,20 @@
         <v>43</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G151" s="5"/>
       <c r="H151" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I151" s="5"/>
       <c r="J151" s="5" t="s">
@@ -12331,7 +12322,7 @@
         <v>96</v>
       </c>
       <c r="R151" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S151" s="5" t="s">
         <v>52</v>
@@ -12352,13 +12343,13 @@
       <c r="AC151" s="5"/>
       <c r="AD151" s="5"/>
       <c r="AE151" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AF151" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG151" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AH151" s="5">
         <v>1.4620299999999999</v>
@@ -12383,13 +12374,13 @@
         <v>43</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>46</v>
@@ -12437,13 +12428,13 @@
       <c r="AC152" s="5"/>
       <c r="AD152" s="5"/>
       <c r="AE152" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF152" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG152" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AH152" s="5"/>
       <c r="AI152" s="5"/>
@@ -12464,20 +12455,20 @@
         <v>43</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G153" s="5"/>
       <c r="H153" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I153" s="5"/>
       <c r="J153" s="5" t="s">
@@ -12497,7 +12488,7 @@
         <v>96</v>
       </c>
       <c r="R153" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S153" s="5" t="s">
         <v>52</v>
@@ -12518,13 +12509,13 @@
       <c r="AC153" s="5"/>
       <c r="AD153" s="5"/>
       <c r="AE153" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AF153" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG153" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AH153" s="5"/>
       <c r="AI153" s="5"/>
@@ -12545,13 +12536,13 @@
         <v>43</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>46</v>
@@ -12567,7 +12558,7 @@
       <c r="K154" s="5"/>
       <c r="L154" s="5"/>
       <c r="M154" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N154" s="5"/>
       <c r="O154" s="5">
@@ -12616,20 +12607,20 @@
         <v>43</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G155" s="5"/>
       <c r="H155" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I155" s="5"/>
       <c r="J155" s="5" t="s">
@@ -12638,7 +12629,7 @@
       <c r="K155" s="5"/>
       <c r="L155" s="5"/>
       <c r="M155" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N155" s="5"/>
       <c r="O155" s="5">
@@ -12651,7 +12642,7 @@
         <v>96</v>
       </c>
       <c r="R155" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S155" s="5" t="s">
         <v>52</v>
@@ -12687,13 +12678,13 @@
         <v>43</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>46</v>
@@ -12741,13 +12732,13 @@
       <c r="AC156" s="5"/>
       <c r="AD156" s="5"/>
       <c r="AE156" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF156" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG156" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AH156" s="5"/>
       <c r="AI156" s="5"/>
@@ -12768,20 +12759,20 @@
         <v>43</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G157" s="5"/>
       <c r="H157" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I157" s="5"/>
       <c r="J157" s="5" t="s">
@@ -12801,7 +12792,7 @@
         <v>96</v>
       </c>
       <c r="R157" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S157" s="5" t="s">
         <v>52</v>
@@ -12822,13 +12813,13 @@
       <c r="AC157" s="5"/>
       <c r="AD157" s="5"/>
       <c r="AE157" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF157" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG157" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AH157" s="5"/>
       <c r="AI157" s="5"/>
@@ -12849,13 +12840,13 @@
         <v>43</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D158" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F158" s="5"/>
       <c r="G158" s="5"/>
@@ -12867,7 +12858,7 @@
       <c r="K158" s="5"/>
       <c r="L158" s="5"/>
       <c r="M158" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N158" s="5">
         <v>6.5</v>
@@ -12876,16 +12867,16 @@
         <v>9</v>
       </c>
       <c r="P158" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q158" s="5">
+        <v>1</v>
+      </c>
+      <c r="R158" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S158" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="Q158" s="5">
-        <v>1</v>
-      </c>
-      <c r="R158" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="S158" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="T158" s="5">
         <v>1</v>
@@ -12918,16 +12909,16 @@
         <v>43</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G159" s="5"/>
       <c r="H159" s="5" t="s">
@@ -12940,7 +12931,7 @@
       <c r="K159" s="5"/>
       <c r="L159" s="5"/>
       <c r="M159" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N159" s="5"/>
       <c r="O159" s="5">
@@ -12974,7 +12965,7 @@
       <c r="AC159" s="5"/>
       <c r="AD159" s="5"/>
       <c r="AE159" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AF159" s="5"/>
       <c r="AG159" s="5"/>
@@ -12991,20 +12982,20 @@
         <v>43</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G160" s="5"/>
       <c r="H160" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I160" s="5"/>
       <c r="J160" s="5" t="s">
@@ -13013,7 +13004,7 @@
       <c r="K160" s="5"/>
       <c r="L160" s="5"/>
       <c r="M160" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N160" s="5"/>
       <c r="O160" s="5">
@@ -13026,7 +13017,7 @@
         <v>96</v>
       </c>
       <c r="R160" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S160" s="5" t="s">
         <v>52</v>
@@ -13047,7 +13038,7 @@
       <c r="AC160" s="5"/>
       <c r="AD160" s="5"/>
       <c r="AE160" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AF160" s="5"/>
       <c r="AG160" s="5"/>
@@ -13064,13 +13055,13 @@
         <v>43</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>46</v>
@@ -13118,13 +13109,13 @@
       <c r="AC161" s="5"/>
       <c r="AD161" s="5"/>
       <c r="AE161" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AF161" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG161" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AH161" s="5"/>
       <c r="AI161" s="5"/>
@@ -13145,13 +13136,13 @@
         <v>43</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>46</v>
@@ -13199,13 +13190,13 @@
       <c r="AC162" s="5"/>
       <c r="AD162" s="5"/>
       <c r="AE162" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AF162" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG162" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AH162" s="5"/>
       <c r="AI162" s="5"/>
@@ -13226,20 +13217,20 @@
         <v>43</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I163" s="5"/>
       <c r="J163" s="5" t="s">
@@ -13259,7 +13250,7 @@
         <v>96</v>
       </c>
       <c r="R163" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S163" s="5" t="s">
         <v>52</v>
@@ -13280,13 +13271,13 @@
       <c r="AC163" s="5"/>
       <c r="AD163" s="5"/>
       <c r="AE163" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF163" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG163" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AH163" s="5"/>
       <c r="AI163" s="5"/>
@@ -13307,13 +13298,13 @@
         <v>43</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F164" s="5"/>
       <c r="G164" s="5"/>
@@ -13325,7 +13316,7 @@
       <c r="K164" s="5"/>
       <c r="L164" s="5"/>
       <c r="M164" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N164" s="5">
         <v>6.5</v>
@@ -13334,22 +13325,22 @@
         <v>9</v>
       </c>
       <c r="P164" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q164" s="5">
+        <v>1</v>
+      </c>
+      <c r="R164" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S164" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="Q164" s="5">
-        <v>1</v>
-      </c>
-      <c r="R164" s="5" t="s">
+      <c r="T164" s="5">
+        <v>1</v>
+      </c>
+      <c r="U164" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S164" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="T164" s="5">
-        <v>1</v>
-      </c>
-      <c r="U164" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V164" s="5"/>
       <c r="W164" s="5"/>
@@ -13376,13 +13367,13 @@
         <v>43</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>46</v>
@@ -13398,7 +13389,7 @@
       <c r="K165" s="5"/>
       <c r="L165" s="5"/>
       <c r="M165" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N165" s="5"/>
       <c r="O165" s="5">
@@ -13432,7 +13423,7 @@
       <c r="AC165" s="5"/>
       <c r="AD165" s="5"/>
       <c r="AE165" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AF165" s="5"/>
       <c r="AG165" s="5"/>
@@ -13449,20 +13440,20 @@
         <v>43</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G166" s="5"/>
       <c r="H166" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I166" s="5"/>
       <c r="J166" s="5" t="s">
@@ -13471,7 +13462,7 @@
       <c r="K166" s="5"/>
       <c r="L166" s="5"/>
       <c r="M166" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N166" s="5"/>
       <c r="O166" s="5">
@@ -13484,7 +13475,7 @@
         <v>96</v>
       </c>
       <c r="R166" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S166" s="5" t="s">
         <v>52</v>
@@ -13505,7 +13496,7 @@
       <c r="AC166" s="5"/>
       <c r="AD166" s="5"/>
       <c r="AE166" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AF166" s="5"/>
       <c r="AG166" s="5"/>
@@ -13522,16 +13513,16 @@
         <v>43</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E167" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F167" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="G167" s="5"/>
       <c r="H167" s="5" t="s">
@@ -13549,7 +13540,7 @@
       <c r="N167" s="5"/>
       <c r="O167" s="5"/>
       <c r="P167" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q167" s="5">
         <v>1</v>
@@ -13576,13 +13567,13 @@
       <c r="AC167" s="5"/>
       <c r="AD167" s="5"/>
       <c r="AE167" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AF167" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AG167" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AH167" s="5"/>
       <c r="AI167" s="5"/>
@@ -13609,20 +13600,20 @@
         <v>43</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E168" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F168" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="G168" s="5"/>
       <c r="H168" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I168" s="5"/>
       <c r="J168" s="5" t="s">
@@ -13636,13 +13627,13 @@
       <c r="N168" s="5"/>
       <c r="O168" s="5"/>
       <c r="P168" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q168" s="5">
         <v>30</v>
       </c>
       <c r="R168" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S168" s="5" t="s">
         <v>52</v>
@@ -13663,13 +13654,13 @@
       <c r="AC168" s="5"/>
       <c r="AD168" s="5"/>
       <c r="AE168" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF168" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="AF168" s="5" t="s">
+      <c r="AG168" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="AG168" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="AH168" s="5"/>
       <c r="AI168" s="5"/>
@@ -13684,20 +13675,20 @@
         <v>43</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E169" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F169" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="G169" s="5"/>
       <c r="H169" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I169" s="5"/>
       <c r="J169" s="5" t="s">
@@ -13711,13 +13702,13 @@
       <c r="N169" s="5"/>
       <c r="O169" s="5"/>
       <c r="P169" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q169" s="5">
         <v>30</v>
       </c>
       <c r="R169" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S169" s="5" t="s">
         <v>52</v>
@@ -13738,13 +13729,13 @@
       <c r="AC169" s="5"/>
       <c r="AD169" s="5"/>
       <c r="AE169" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF169" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG169" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="AF169" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG169" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="AH169" s="5"/>
       <c r="AI169" s="5"/>
@@ -13759,13 +13750,13 @@
         <v>43</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>46</v>
@@ -13781,7 +13772,7 @@
       <c r="K170" s="5"/>
       <c r="L170" s="5"/>
       <c r="M170" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N170" s="5"/>
       <c r="O170" s="5">
@@ -13830,20 +13821,20 @@
         <v>43</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G171" s="5"/>
       <c r="H171" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I171" s="5"/>
       <c r="J171" s="5" t="s">
@@ -13852,7 +13843,7 @@
       <c r="K171" s="5"/>
       <c r="L171" s="5"/>
       <c r="M171" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N171" s="5"/>
       <c r="O171" s="5">
@@ -13865,7 +13856,7 @@
         <v>96</v>
       </c>
       <c r="R171" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S171" s="5" t="s">
         <v>52</v>
@@ -13901,13 +13892,13 @@
         <v>43</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D172" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>46</v>
@@ -13955,13 +13946,13 @@
       <c r="AC172" s="5"/>
       <c r="AD172" s="5"/>
       <c r="AE172" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF172" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG172" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH172" s="5">
         <v>1.1366719999999999</v>
@@ -13986,20 +13977,20 @@
         <v>43</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G173" s="5"/>
       <c r="H173" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I173" s="5"/>
       <c r="J173" s="5" t="s">
@@ -14019,7 +14010,7 @@
         <v>96</v>
       </c>
       <c r="R173" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S173" s="5" t="s">
         <v>52</v>
@@ -14040,13 +14031,13 @@
       <c r="AC173" s="5"/>
       <c r="AD173" s="5"/>
       <c r="AE173" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF173" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG173" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH173" s="5">
         <v>1.101672</v>
@@ -14071,13 +14062,13 @@
         <v>43</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D174" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>46</v>
@@ -14093,7 +14084,7 @@
       <c r="K174" s="5"/>
       <c r="L174" s="5"/>
       <c r="M174" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N174" s="5"/>
       <c r="O174" s="5">
@@ -14127,7 +14118,7 @@
       <c r="AC174" s="5"/>
       <c r="AD174" s="5"/>
       <c r="AE174" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AF174" s="5"/>
       <c r="AG174" s="5"/>
@@ -14144,20 +14135,20 @@
         <v>43</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D175" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G175" s="5"/>
       <c r="H175" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I175" s="5"/>
       <c r="J175" s="5" t="s">
@@ -14166,7 +14157,7 @@
       <c r="K175" s="5"/>
       <c r="L175" s="5"/>
       <c r="M175" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N175" s="5"/>
       <c r="O175" s="5">
@@ -14179,7 +14170,7 @@
         <v>96</v>
       </c>
       <c r="R175" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S175" s="5" t="s">
         <v>52</v>
@@ -14200,7 +14191,7 @@
       <c r="AC175" s="5"/>
       <c r="AD175" s="5"/>
       <c r="AE175" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AF175" s="5"/>
       <c r="AG175" s="5"/>
@@ -14217,13 +14208,13 @@
         <v>43</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D176" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>46</v>
@@ -14239,7 +14230,7 @@
       <c r="K176" s="5"/>
       <c r="L176" s="5"/>
       <c r="M176" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N176" s="5"/>
       <c r="O176" s="5">
@@ -14288,20 +14279,20 @@
         <v>43</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D177" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G177" s="5"/>
       <c r="H177" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I177" s="5"/>
       <c r="J177" s="5" t="s">
@@ -14310,7 +14301,7 @@
       <c r="K177" s="5"/>
       <c r="L177" s="5"/>
       <c r="M177" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N177" s="5"/>
       <c r="O177" s="5">
@@ -14323,7 +14314,7 @@
         <v>96</v>
       </c>
       <c r="R177" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S177" s="5" t="s">
         <v>52</v>
@@ -14359,13 +14350,13 @@
         <v>43</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D178" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>46</v>
@@ -14413,13 +14404,13 @@
       <c r="AC178" s="5"/>
       <c r="AD178" s="5"/>
       <c r="AE178" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AF178" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG178" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AH178" s="5"/>
       <c r="AI178" s="5"/>
@@ -14440,20 +14431,20 @@
         <v>43</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G179" s="5"/>
       <c r="H179" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I179" s="5"/>
       <c r="J179" s="5" t="s">
@@ -14473,7 +14464,7 @@
         <v>96</v>
       </c>
       <c r="R179" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S179" s="5" t="s">
         <v>52</v>
@@ -14494,13 +14485,13 @@
       <c r="AC179" s="5"/>
       <c r="AD179" s="5"/>
       <c r="AE179" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AF179" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG179" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH179" s="5"/>
       <c r="AI179" s="5"/>
@@ -14521,20 +14512,20 @@
         <v>43</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D180" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G180" s="5"/>
       <c r="H180" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I180" s="5"/>
       <c r="J180" s="5" t="s">
@@ -14543,7 +14534,7 @@
       <c r="K180" s="5"/>
       <c r="L180" s="5"/>
       <c r="M180" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N180" s="5"/>
       <c r="O180" s="5">
@@ -14556,7 +14547,7 @@
         <v>96</v>
       </c>
       <c r="R180" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S180" s="5" t="s">
         <v>52</v>
@@ -14592,13 +14583,13 @@
         <v>43</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F181" s="5" t="s">
         <v>46</v>
@@ -14646,13 +14637,13 @@
       <c r="AC181" s="5"/>
       <c r="AD181" s="5"/>
       <c r="AE181" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AF181" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG181" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AH181" s="5">
         <v>1.4620299999999999</v>
@@ -14677,20 +14668,20 @@
         <v>43</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F182" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G182" s="5"/>
       <c r="H182" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I182" s="5"/>
       <c r="J182" s="5" t="s">
@@ -14710,7 +14701,7 @@
         <v>96</v>
       </c>
       <c r="R182" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S182" s="5" t="s">
         <v>52</v>
@@ -14731,13 +14722,13 @@
       <c r="AC182" s="5"/>
       <c r="AD182" s="5"/>
       <c r="AE182" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AF182" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG182" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AH182" s="5">
         <v>1.4620299999999999</v>
@@ -14762,13 +14753,13 @@
         <v>43</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>46</v>
@@ -14816,13 +14807,13 @@
       <c r="AC183" s="5"/>
       <c r="AD183" s="5"/>
       <c r="AE183" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF183" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG183" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AH183" s="5"/>
       <c r="AI183" s="5"/>
@@ -14843,20 +14834,20 @@
         <v>43</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G184" s="5"/>
       <c r="H184" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I184" s="5"/>
       <c r="J184" s="5" t="s">
@@ -14876,7 +14867,7 @@
         <v>96</v>
       </c>
       <c r="R184" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S184" s="5" t="s">
         <v>52</v>
@@ -14897,13 +14888,13 @@
       <c r="AC184" s="5"/>
       <c r="AD184" s="5"/>
       <c r="AE184" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AF184" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG184" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AH184" s="5"/>
       <c r="AI184" s="5"/>
@@ -14924,13 +14915,13 @@
         <v>43</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D185" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>46</v>
@@ -14946,7 +14937,7 @@
       <c r="K185" s="5"/>
       <c r="L185" s="5"/>
       <c r="M185" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N185" s="5"/>
       <c r="O185" s="5">
@@ -14995,20 +14986,20 @@
         <v>43</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G186" s="5"/>
       <c r="H186" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I186" s="5"/>
       <c r="J186" s="5" t="s">
@@ -15017,7 +15008,7 @@
       <c r="K186" s="5"/>
       <c r="L186" s="5"/>
       <c r="M186" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N186" s="5"/>
       <c r="O186" s="5">
@@ -15030,7 +15021,7 @@
         <v>96</v>
       </c>
       <c r="R186" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S186" s="5" t="s">
         <v>52</v>
@@ -15066,13 +15057,13 @@
         <v>43</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>46</v>
@@ -15120,13 +15111,13 @@
       <c r="AC187" s="5"/>
       <c r="AD187" s="5"/>
       <c r="AE187" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF187" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG187" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AH187" s="5"/>
       <c r="AI187" s="5"/>
@@ -15147,20 +15138,20 @@
         <v>43</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F188" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G188" s="5"/>
       <c r="H188" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I188" s="5"/>
       <c r="J188" s="5" t="s">
@@ -15180,7 +15171,7 @@
         <v>96</v>
       </c>
       <c r="R188" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S188" s="5" t="s">
         <v>52</v>
@@ -15201,13 +15192,13 @@
       <c r="AC188" s="5"/>
       <c r="AD188" s="5"/>
       <c r="AE188" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF188" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG188" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AH188" s="5"/>
       <c r="AI188" s="5"/>
@@ -15228,13 +15219,13 @@
         <v>43</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F189" s="5" t="s">
         <v>46</v>
@@ -15248,20 +15239,20 @@
       <c r="K189" s="5"/>
       <c r="L189" s="5"/>
       <c r="M189" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N189" s="5">
         <v>5.5</v>
       </c>
       <c r="O189" s="5"/>
       <c r="P189" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q189" s="5">
         <v>30</v>
       </c>
       <c r="R189" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S189" s="5" t="s">
         <v>52</v>
@@ -15282,7 +15273,7 @@
       <c r="AC189" s="5"/>
       <c r="AD189" s="5"/>
       <c r="AE189" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="AF189" s="5"/>
       <c r="AG189" s="5"/>
@@ -15299,13 +15290,13 @@
         <v>43</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F190" s="5" t="s">
         <v>46</v>
@@ -15319,20 +15310,20 @@
       <c r="K190" s="5"/>
       <c r="L190" s="5"/>
       <c r="M190" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N190" s="5">
         <v>6</v>
       </c>
       <c r="O190" s="5"/>
       <c r="P190" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q190" s="5">
         <v>7</v>
       </c>
       <c r="R190" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S190" s="5" t="s">
         <v>52</v>
@@ -15353,7 +15344,7 @@
       <c r="AC190" s="5"/>
       <c r="AD190" s="5"/>
       <c r="AE190" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AF190" s="5"/>
       <c r="AG190" s="5"/>
@@ -15370,13 +15361,13 @@
         <v>43</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>46</v>
@@ -15390,20 +15381,20 @@
       <c r="K191" s="5"/>
       <c r="L191" s="5"/>
       <c r="M191" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N191" s="5">
         <v>4</v>
       </c>
       <c r="O191" s="5"/>
       <c r="P191" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q191" s="5">
         <v>7</v>
       </c>
       <c r="R191" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S191" s="5" t="s">
         <v>52</v>
@@ -15424,7 +15415,7 @@
       <c r="AC191" s="5"/>
       <c r="AD191" s="5"/>
       <c r="AE191" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="AF191" s="5"/>
       <c r="AG191" s="5"/>
@@ -15441,13 +15432,13 @@
         <v>43</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D192" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F192" s="5" t="s">
         <v>46</v>
@@ -15461,23 +15452,23 @@
       <c r="K192" s="5"/>
       <c r="L192" s="5"/>
       <c r="M192" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N192" s="5">
         <v>5</v>
       </c>
       <c r="O192" s="5"/>
       <c r="P192" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q192" s="5">
         <v>1</v>
       </c>
       <c r="R192" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S192" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="T192" s="5">
         <v>1</v>
@@ -15495,7 +15486,7 @@
       <c r="AC192" s="5"/>
       <c r="AD192" s="5"/>
       <c r="AE192" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AF192" s="5"/>
       <c r="AG192" s="5"/>
@@ -15512,13 +15503,13 @@
         <v>43</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D193" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>46</v>
@@ -15532,29 +15523,29 @@
       <c r="K193" s="5"/>
       <c r="L193" s="5"/>
       <c r="M193" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N193" s="5">
         <v>3</v>
       </c>
       <c r="O193" s="5"/>
       <c r="P193" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q193" s="5">
         <v>1</v>
       </c>
       <c r="R193" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S193" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="T193" s="5">
+        <v>1</v>
+      </c>
+      <c r="U193" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S193" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="T193" s="5">
-        <v>1</v>
-      </c>
-      <c r="U193" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V193" s="5"/>
       <c r="W193" s="5"/>
@@ -15566,7 +15557,7 @@
       <c r="AC193" s="5"/>
       <c r="AD193" s="5"/>
       <c r="AE193" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="AF193" s="5"/>
       <c r="AG193" s="5"/>
@@ -15583,13 +15574,13 @@
         <v>43</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D194" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F194" s="5"/>
       <c r="G194" s="5"/>
@@ -15601,7 +15592,7 @@
       <c r="K194" s="5"/>
       <c r="L194" s="5"/>
       <c r="M194" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N194" s="5">
         <v>6.5</v>
@@ -15610,16 +15601,16 @@
         <v>9</v>
       </c>
       <c r="P194" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q194" s="5">
+        <v>1</v>
+      </c>
+      <c r="R194" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S194" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="Q194" s="5">
-        <v>1</v>
-      </c>
-      <c r="R194" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="S194" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="T194" s="5">
         <v>1</v>
@@ -15652,16 +15643,16 @@
         <v>43</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D195" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G195" s="5"/>
       <c r="H195" s="5" t="s">
@@ -15674,7 +15665,7 @@
       <c r="K195" s="5"/>
       <c r="L195" s="5"/>
       <c r="M195" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N195" s="5"/>
       <c r="O195" s="5">
@@ -15708,7 +15699,7 @@
       <c r="AC195" s="5"/>
       <c r="AD195" s="5"/>
       <c r="AE195" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AF195" s="5"/>
       <c r="AG195" s="5"/>
@@ -15725,20 +15716,20 @@
         <v>43</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D196" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G196" s="5"/>
       <c r="H196" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I196" s="5"/>
       <c r="J196" s="5" t="s">
@@ -15747,7 +15738,7 @@
       <c r="K196" s="5"/>
       <c r="L196" s="5"/>
       <c r="M196" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N196" s="5"/>
       <c r="O196" s="5">
@@ -15760,7 +15751,7 @@
         <v>96</v>
       </c>
       <c r="R196" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S196" s="5" t="s">
         <v>52</v>
@@ -15781,7 +15772,7 @@
       <c r="AC196" s="5"/>
       <c r="AD196" s="5"/>
       <c r="AE196" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AF196" s="5"/>
       <c r="AG196" s="5"/>
@@ -15798,13 +15789,13 @@
         <v>43</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>46</v>
@@ -15852,13 +15843,13 @@
       <c r="AC197" s="5"/>
       <c r="AD197" s="5"/>
       <c r="AE197" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AF197" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG197" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AH197" s="5"/>
       <c r="AI197" s="5"/>
@@ -15879,13 +15870,13 @@
         <v>43</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D198" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F198" s="5"/>
       <c r="G198" s="5"/>
@@ -15897,21 +15888,21 @@
       <c r="K198" s="5"/>
       <c r="L198" s="5"/>
       <c r="M198" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N198" s="5"/>
       <c r="O198" s="5"/>
       <c r="P198" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q198" s="5">
+        <v>1</v>
+      </c>
+      <c r="R198" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S198" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="Q198" s="5">
-        <v>1</v>
-      </c>
-      <c r="R198" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="S198" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="T198" s="5">
         <v>1</v>
@@ -15929,7 +15920,7 @@
       <c r="AC198" s="5"/>
       <c r="AD198" s="5"/>
       <c r="AE198" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="AF198" s="5"/>
       <c r="AG198" s="5"/>
@@ -15946,13 +15937,13 @@
         <v>43</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D199" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F199" s="5"/>
       <c r="G199" s="5"/>
@@ -15964,14 +15955,14 @@
       <c r="K199" s="5"/>
       <c r="L199" s="5"/>
       <c r="M199" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N199" s="5"/>
       <c r="O199" s="5">
         <v>30</v>
       </c>
       <c r="P199" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q199" s="5">
         <v>2</v>
@@ -16013,13 +16004,13 @@
         <v>43</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D200" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F200" s="5" t="s">
         <v>46</v>
@@ -16067,13 +16058,13 @@
       <c r="AC200" s="5"/>
       <c r="AD200" s="5"/>
       <c r="AE200" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AF200" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG200" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AH200" s="5"/>
       <c r="AI200" s="5"/>
@@ -16094,20 +16085,20 @@
         <v>43</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D201" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F201" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G201" s="5"/>
       <c r="H201" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I201" s="5"/>
       <c r="J201" s="5" t="s">
@@ -16127,7 +16118,7 @@
         <v>96</v>
       </c>
       <c r="R201" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S201" s="5" t="s">
         <v>52</v>
@@ -16148,13 +16139,13 @@
       <c r="AC201" s="5"/>
       <c r="AD201" s="5"/>
       <c r="AE201" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF201" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AG201" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AH201" s="5"/>
       <c r="AI201" s="5"/>
@@ -16175,16 +16166,16 @@
         <v>43</v>
       </c>
       <c r="C202" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E202" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D202" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E202" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="F202" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G202" s="5"/>
       <c r="H202" s="5"/>
@@ -16195,7 +16186,7 @@
       <c r="K202" s="5"/>
       <c r="L202" s="5"/>
       <c r="M202" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N202" s="5"/>
       <c r="O202" s="5">
@@ -16208,16 +16199,16 @@
         <v>30</v>
       </c>
       <c r="R202" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S202" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T202" s="5">
+        <v>1</v>
+      </c>
+      <c r="U202" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S202" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T202" s="5">
-        <v>1</v>
-      </c>
-      <c r="U202" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V202" s="5"/>
       <c r="W202" s="5"/>
@@ -16244,16 +16235,16 @@
         <v>43</v>
       </c>
       <c r="C203" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E203" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D203" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E203" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="F203" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G203" s="5"/>
       <c r="H203" s="5"/>
@@ -16264,7 +16255,7 @@
       <c r="K203" s="5"/>
       <c r="L203" s="5"/>
       <c r="M203" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N203" s="5"/>
       <c r="O203" s="5">
@@ -16277,16 +16268,16 @@
         <v>30</v>
       </c>
       <c r="R203" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S203" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T203" s="5">
+        <v>1</v>
+      </c>
+      <c r="U203" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S203" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T203" s="5">
-        <v>1</v>
-      </c>
-      <c r="U203" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V203" s="5"/>
       <c r="W203" s="5"/>
@@ -16313,16 +16304,16 @@
         <v>43</v>
       </c>
       <c r="C204" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E204" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D204" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E204" s="5" t="s">
-        <v>109</v>
-      </c>
       <c r="F204" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G204" s="5"/>
       <c r="H204" s="5"/>
@@ -16333,7 +16324,7 @@
       <c r="K204" s="5"/>
       <c r="L204" s="5"/>
       <c r="M204" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N204" s="5"/>
       <c r="O204" s="5">
@@ -16346,16 +16337,16 @@
         <v>30</v>
       </c>
       <c r="R204" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S204" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T204" s="5">
+        <v>1</v>
+      </c>
+      <c r="U204" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S204" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T204" s="5">
-        <v>1</v>
-      </c>
-      <c r="U204" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V204" s="5"/>
       <c r="W204" s="5"/>
@@ -16382,16 +16373,16 @@
         <v>43</v>
       </c>
       <c r="C205" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D205" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E205" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D205" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E205" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="F205" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G205" s="5"/>
       <c r="H205" s="5"/>
@@ -16402,7 +16393,7 @@
       <c r="K205" s="5"/>
       <c r="L205" s="5"/>
       <c r="M205" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N205" s="5"/>
       <c r="O205" s="5">
@@ -16415,16 +16406,16 @@
         <v>30</v>
       </c>
       <c r="R205" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S205" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T205" s="5">
+        <v>1</v>
+      </c>
+      <c r="U205" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S205" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T205" s="5">
-        <v>1</v>
-      </c>
-      <c r="U205" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V205" s="5"/>
       <c r="W205" s="5"/>
@@ -16451,16 +16442,16 @@
         <v>43</v>
       </c>
       <c r="C206" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D206" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E206" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D206" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E206" s="5" t="s">
-        <v>124</v>
-      </c>
       <c r="F206" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G206" s="5"/>
       <c r="H206" s="5"/>
@@ -16471,7 +16462,7 @@
       <c r="K206" s="5"/>
       <c r="L206" s="5"/>
       <c r="M206" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N206" s="5"/>
       <c r="O206" s="5">
@@ -16484,16 +16475,16 @@
         <v>30</v>
       </c>
       <c r="R206" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S206" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T206" s="5">
+        <v>1</v>
+      </c>
+      <c r="U206" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S206" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T206" s="5">
-        <v>1</v>
-      </c>
-      <c r="U206" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V206" s="5"/>
       <c r="W206" s="5"/>
@@ -16520,16 +16511,16 @@
         <v>43</v>
       </c>
       <c r="C207" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E207" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D207" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E207" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="F207" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G207" s="5"/>
       <c r="H207" s="5"/>
@@ -16540,7 +16531,7 @@
       <c r="K207" s="5"/>
       <c r="L207" s="5"/>
       <c r="M207" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N207" s="5"/>
       <c r="O207" s="5">
@@ -16553,16 +16544,16 @@
         <v>30</v>
       </c>
       <c r="R207" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S207" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T207" s="5">
+        <v>1</v>
+      </c>
+      <c r="U207" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S207" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T207" s="5">
-        <v>1</v>
-      </c>
-      <c r="U207" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V207" s="5"/>
       <c r="W207" s="5"/>
@@ -16589,16 +16580,16 @@
         <v>43</v>
       </c>
       <c r="C208" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D208" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E208" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D208" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E208" s="5" t="s">
-        <v>135</v>
-      </c>
       <c r="F208" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G208" s="5"/>
       <c r="H208" s="5"/>
@@ -16609,7 +16600,7 @@
       <c r="K208" s="5"/>
       <c r="L208" s="5"/>
       <c r="M208" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N208" s="5"/>
       <c r="O208" s="5">
@@ -16622,16 +16613,16 @@
         <v>30</v>
       </c>
       <c r="R208" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S208" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T208" s="5">
+        <v>1</v>
+      </c>
+      <c r="U208" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S208" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T208" s="5">
-        <v>1</v>
-      </c>
-      <c r="U208" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V208" s="5"/>
       <c r="W208" s="5"/>
@@ -16658,13 +16649,13 @@
         <v>43</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F209" s="5"/>
       <c r="G209" s="5"/>
@@ -16676,7 +16667,7 @@
       <c r="K209" s="5"/>
       <c r="L209" s="5"/>
       <c r="M209" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N209" s="5">
         <v>6.5</v>
@@ -16685,22 +16676,22 @@
         <v>9</v>
       </c>
       <c r="P209" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q209" s="5">
         <v>30</v>
       </c>
       <c r="R209" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S209" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="T209" s="5">
+        <v>1</v>
+      </c>
+      <c r="U209" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="S209" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="T209" s="5">
-        <v>1</v>
-      </c>
-      <c r="U209" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="V209" s="5"/>
       <c r="W209" s="5"/>

--- a/inst/extdata/wyoming_criteria_crosswalk.xlsx
+++ b/inst/extdata/wyoming_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/sheila_saia_tetratech_com/Documents/Documents/github/TADACommunityHub/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="109_{F9DE8C93-6FEC-45BA-9699-34AE0D0C7F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7260A03C-C2DC-4FBB-BF6E-C9228AF8B6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{254103FA-C5D3-4049-B135-21AE92C6DC6D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{254103FA-C5D3-4049-B135-21AE92C6DC6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -461,9 +461,6 @@
     <t>ESCHERICHIA COLI</t>
   </si>
   <si>
-    <t>#/100mL</t>
-  </si>
-  <si>
     <t>geometric mean</t>
   </si>
   <si>
@@ -660,6 +657,9 @@
   </si>
   <si>
     <t>(0.85)*e^(1.72*(ln(hardness))-6.52)*(0.5); Value multiplied by 0.5 to be comparable with other acute values derived using an averaging period. Value does not need to be multiplied by 0.5 if used as an instantaneous maximum or end of pipe value, as the original value was derived as a not to be exceeded instantaneous maximum.</t>
+  </si>
+  <si>
+    <t>CFU/100ML</t>
   </si>
 </sst>
 </file>
@@ -1079,12 +1079,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1AFC1C8-D989-4C34-AD6B-0180801AF6A9}">
   <dimension ref="A1:AP209"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="12" max="12" width="17.42578125" customWidth="1"/>
+    <col min="12" max="12" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>42</v>
@@ -1221,7 +1221,7 @@
         <v>58</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>59</v>
@@ -1288,7 +1288,7 @@
       <c r="AO2" s="5"/>
       <c r="AP2" s="5"/>
     </row>
-    <row r="3" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>42</v>
@@ -1364,7 +1364,7 @@
       <c r="AO3" s="5"/>
       <c r="AP3" s="5"/>
     </row>
-    <row r="4" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>42</v>
@@ -1428,10 +1428,10 @@
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
       <c r="AE4" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF4" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG4" s="4"/>
       <c r="AH4" s="4"/>
@@ -1444,7 +1444,7 @@
       <c r="AO4" s="5"/>
       <c r="AP4" s="5"/>
     </row>
-    <row r="5" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>42</v>
@@ -1453,7 +1453,7 @@
         <v>58</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>59</v>
@@ -1508,10 +1508,10 @@
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
       <c r="AE5" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF5" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
@@ -1524,7 +1524,7 @@
       <c r="AO5" s="5"/>
       <c r="AP5" s="5"/>
     </row>
-    <row r="6" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>42</v>
@@ -1600,7 +1600,7 @@
       <c r="AO6" s="5"/>
       <c r="AP6" s="5"/>
     </row>
-    <row r="7" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>42</v>
@@ -1664,10 +1664,10 @@
       <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
       <c r="AE7" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG7" s="4"/>
       <c r="AH7" s="4"/>
@@ -1680,7 +1680,7 @@
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
     </row>
-    <row r="8" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>42</v>
@@ -1756,7 +1756,7 @@
       <c r="AO8" s="5"/>
       <c r="AP8" s="5"/>
     </row>
-    <row r="9" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>42</v>
@@ -1820,10 +1820,10 @@
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
       <c r="AE9" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF9" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG9" s="4"/>
       <c r="AH9" s="4"/>
@@ -1836,7 +1836,7 @@
       <c r="AO9" s="5"/>
       <c r="AP9" s="5"/>
     </row>
-    <row r="10" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>42</v>
@@ -1912,7 +1912,7 @@
       <c r="AO10" s="5"/>
       <c r="AP10" s="5"/>
     </row>
-    <row r="11" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>42</v>
@@ -1976,10 +1976,10 @@
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
       <c r="AE11" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF11" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
@@ -1992,7 +1992,7 @@
       <c r="AO11" s="5"/>
       <c r="AP11" s="5"/>
     </row>
-    <row r="12" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>42</v>
@@ -2076,7 +2076,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>42</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>48</v>
@@ -2154,7 +2154,7 @@
       <c r="AO13" s="5"/>
       <c r="AP13" s="5"/>
     </row>
-    <row r="14" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>42</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>48</v>
@@ -2232,7 +2232,7 @@
       <c r="AO14" s="5"/>
       <c r="AP14" s="5"/>
     </row>
-    <row r="15" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>42</v>
@@ -2295,7 +2295,7 @@
         <v>67</v>
       </c>
       <c r="AF15" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG15" s="4"/>
       <c r="AH15" s="4"/>
@@ -2316,7 +2316,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>42</v>
@@ -2392,7 +2392,7 @@
       <c r="AO16" s="5"/>
       <c r="AP16" s="5"/>
     </row>
-    <row r="17" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>42</v>
@@ -2468,7 +2468,7 @@
       <c r="AO17" s="5"/>
       <c r="AP17" s="5"/>
     </row>
-    <row r="18" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>42</v>
@@ -2540,7 +2540,7 @@
       <c r="AO18" s="5"/>
       <c r="AP18" s="5"/>
     </row>
-    <row r="19" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>42</v>
@@ -2549,7 +2549,7 @@
         <v>115</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>116</v>
@@ -2612,7 +2612,7 @@
       <c r="AO19" s="5"/>
       <c r="AP19" s="5"/>
     </row>
-    <row r="20" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
         <v>42</v>
@@ -2621,7 +2621,7 @@
         <v>115</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>116</v>
@@ -2683,7 +2683,7 @@
       <c r="AO20" s="5"/>
       <c r="AP20" s="5"/>
     </row>
-    <row r="21" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
         <v>42</v>
@@ -2757,7 +2757,7 @@
       <c r="AO21" s="5"/>
       <c r="AP21" s="5"/>
     </row>
-    <row r="22" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
         <v>42</v>
@@ -2831,7 +2831,7 @@
       <c r="AO22" s="5"/>
       <c r="AP22" s="5"/>
     </row>
-    <row r="23" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
         <v>42</v>
@@ -2905,7 +2905,7 @@
       <c r="AO23" s="5"/>
       <c r="AP23" s="5"/>
     </row>
-    <row r="24" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
         <v>42</v>
@@ -2914,7 +2914,7 @@
         <v>72</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>73</v>
@@ -2979,7 +2979,7 @@
       <c r="AO24" s="5"/>
       <c r="AP24" s="5"/>
     </row>
-    <row r="25" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>42</v>
@@ -2988,7 +2988,7 @@
         <v>72</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>73</v>
@@ -3053,7 +3053,7 @@
       <c r="AO25" s="5"/>
       <c r="AP25" s="5"/>
     </row>
-    <row r="26" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
         <v>42</v>
@@ -3062,7 +3062,7 @@
         <v>72</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>73</v>
@@ -3125,7 +3125,7 @@
       <c r="AO26" s="5"/>
       <c r="AP26" s="5"/>
     </row>
-    <row r="27" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>42</v>
@@ -3199,7 +3199,7 @@
       <c r="AO27" s="5"/>
       <c r="AP27" s="5"/>
     </row>
-    <row r="28" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>42</v>
@@ -3273,7 +3273,7 @@
       <c r="AO28" s="5"/>
       <c r="AP28" s="5"/>
     </row>
-    <row r="29" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>42</v>
@@ -3347,7 +3347,7 @@
       <c r="AO29" s="5"/>
       <c r="AP29" s="5"/>
     </row>
-    <row r="30" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>42</v>
@@ -3421,7 +3421,7 @@
       <c r="AO30" s="5"/>
       <c r="AP30" s="5"/>
     </row>
-    <row r="31" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
         <v>42</v>
@@ -3495,7 +3495,7 @@
       <c r="AO31" s="5"/>
       <c r="AP31" s="5"/>
     </row>
-    <row r="32" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
         <v>42</v>
@@ -3569,7 +3569,7 @@
       <c r="AO32" s="5"/>
       <c r="AP32" s="5"/>
     </row>
-    <row r="33" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
         <v>42</v>
@@ -3578,7 +3578,7 @@
         <v>72</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>73</v>
@@ -3641,7 +3641,7 @@
       <c r="AO33" s="5"/>
       <c r="AP33" s="5"/>
     </row>
-    <row r="34" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
         <v>42</v>
@@ -3713,7 +3713,7 @@
       <c r="AO34" s="5"/>
       <c r="AP34" s="5"/>
     </row>
-    <row r="35" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>42</v>
@@ -3785,13 +3785,13 @@
       <c r="AO35" s="5"/>
       <c r="AP35" s="5"/>
     </row>
-    <row r="36" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>83</v>
@@ -3855,7 +3855,7 @@
       <c r="AO36" s="5"/>
       <c r="AP36" s="5"/>
     </row>
-    <row r="37" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
         <v>42</v>
@@ -3918,7 +3918,7 @@
         <v>53</v>
       </c>
       <c r="AF37" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG37" s="4">
         <v>1.1366719999999999</v>
@@ -3941,7 +3941,7 @@
       <c r="AO37" s="5"/>
       <c r="AP37" s="5"/>
     </row>
-    <row r="38" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
         <v>42</v>
@@ -4004,7 +4004,7 @@
         <v>53</v>
       </c>
       <c r="AF38" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG38" s="4">
         <v>1.101672</v>
@@ -4027,7 +4027,7 @@
       <c r="AO38" s="5"/>
       <c r="AP38" s="5"/>
     </row>
-    <row r="39" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
         <v>42</v>
@@ -4099,7 +4099,7 @@
       <c r="AO39" s="5"/>
       <c r="AP39" s="5"/>
     </row>
-    <row r="40" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
         <v>42</v>
@@ -4108,7 +4108,7 @@
         <v>74</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>75</v>
@@ -4162,7 +4162,7 @@
         <v>53</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG40" s="4">
         <v>1.1366719999999999</v>
@@ -4185,7 +4185,7 @@
       <c r="AO40" s="5"/>
       <c r="AP40" s="5"/>
     </row>
-    <row r="41" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
         <v>42</v>
@@ -4194,7 +4194,7 @@
         <v>74</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>75</v>
@@ -4248,7 +4248,7 @@
         <v>53</v>
       </c>
       <c r="AF41" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG41" s="4">
         <v>1.101672</v>
@@ -4271,7 +4271,7 @@
       <c r="AO41" s="5"/>
       <c r="AP41" s="5"/>
     </row>
-    <row r="42" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>42</v>
@@ -4334,7 +4334,7 @@
         <v>53</v>
       </c>
       <c r="AF42" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG42" s="4">
         <v>1.1366719999999999</v>
@@ -4357,7 +4357,7 @@
       <c r="AO42" s="5"/>
       <c r="AP42" s="5"/>
     </row>
-    <row r="43" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
         <v>42</v>
@@ -4420,7 +4420,7 @@
         <v>53</v>
       </c>
       <c r="AF43" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG43" s="4">
         <v>1.101672</v>
@@ -4443,7 +4443,7 @@
       <c r="AO43" s="5"/>
       <c r="AP43" s="5"/>
     </row>
-    <row r="44" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>42</v>
@@ -4506,7 +4506,7 @@
         <v>53</v>
       </c>
       <c r="AF44" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG44" s="4">
         <v>1.1366719999999999</v>
@@ -4529,7 +4529,7 @@
       <c r="AO44" s="5"/>
       <c r="AP44" s="5"/>
     </row>
-    <row r="45" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
         <v>42</v>
@@ -4592,7 +4592,7 @@
         <v>53</v>
       </c>
       <c r="AF45" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG45" s="4">
         <v>1.101672</v>
@@ -4615,7 +4615,7 @@
       <c r="AO45" s="5"/>
       <c r="AP45" s="5"/>
     </row>
-    <row r="46" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
         <v>42</v>
@@ -4678,7 +4678,7 @@
         <v>53</v>
       </c>
       <c r="AF46" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG46" s="4">
         <v>1.1366719999999999</v>
@@ -4701,7 +4701,7 @@
       <c r="AO46" s="5"/>
       <c r="AP46" s="5"/>
     </row>
-    <row r="47" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
         <v>42</v>
@@ -4764,7 +4764,7 @@
         <v>53</v>
       </c>
       <c r="AF47" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG47" s="4">
         <v>1.101672</v>
@@ -4787,7 +4787,7 @@
       <c r="AO47" s="5"/>
       <c r="AP47" s="5"/>
     </row>
-    <row r="48" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
         <v>42</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M48" s="4" t="s">
         <v>60</v>
@@ -4851,7 +4851,7 @@
       <c r="AC48" s="4"/>
       <c r="AD48" s="4"/>
       <c r="AE48" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF48" s="4" t="s">
         <v>78</v>
@@ -4867,7 +4867,7 @@
       <c r="AO48" s="5"/>
       <c r="AP48" s="5"/>
     </row>
-    <row r="49" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
         <v>42</v>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M49" s="4" t="s">
         <v>60</v>
@@ -4931,7 +4931,7 @@
       <c r="AC49" s="4"/>
       <c r="AD49" s="4"/>
       <c r="AE49" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF49" s="4" t="s">
         <v>78</v>
@@ -4947,7 +4947,7 @@
       <c r="AO49" s="5"/>
       <c r="AP49" s="5"/>
     </row>
-    <row r="50" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
         <v>42</v>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M50" s="4" t="s">
         <v>60</v>
@@ -5011,10 +5011,10 @@
       <c r="AC50" s="4"/>
       <c r="AD50" s="4"/>
       <c r="AE50" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF50" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AG50" s="4"/>
       <c r="AH50" s="4"/>
@@ -5027,7 +5027,7 @@
       <c r="AO50" s="5"/>
       <c r="AP50" s="5"/>
     </row>
-    <row r="51" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
         <v>42</v>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M51" s="4" t="s">
         <v>60</v>
@@ -5091,10 +5091,10 @@
       <c r="AC51" s="4"/>
       <c r="AD51" s="4"/>
       <c r="AE51" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF51" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AG51" s="4"/>
       <c r="AH51" s="4"/>
@@ -5107,7 +5107,7 @@
       <c r="AO51" s="5"/>
       <c r="AP51" s="5"/>
     </row>
-    <row r="52" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
         <v>42</v>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M52" s="4" t="s">
         <v>60</v>
@@ -5171,10 +5171,10 @@
       <c r="AC52" s="4"/>
       <c r="AD52" s="4"/>
       <c r="AE52" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF52" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG52" s="4"/>
       <c r="AH52" s="4"/>
@@ -5187,7 +5187,7 @@
       <c r="AO52" s="5"/>
       <c r="AP52" s="5"/>
     </row>
-    <row r="53" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
         <v>42</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M53" s="4" t="s">
         <v>60</v>
@@ -5251,10 +5251,10 @@
       <c r="AC53" s="4"/>
       <c r="AD53" s="4"/>
       <c r="AE53" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF53" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG53" s="4"/>
       <c r="AH53" s="4"/>
@@ -5267,13 +5267,13 @@
       <c r="AO53" s="5"/>
       <c r="AP53" s="5"/>
     </row>
-    <row r="54" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>43</v>
@@ -5330,7 +5330,7 @@
         <v>53</v>
       </c>
       <c r="AF54" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG54" s="4"/>
       <c r="AH54" s="4"/>
@@ -5349,13 +5349,13 @@
       <c r="AO54" s="5"/>
       <c r="AP54" s="5"/>
     </row>
-    <row r="55" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>54</v>
@@ -5412,7 +5412,7 @@
         <v>53</v>
       </c>
       <c r="AF55" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG55" s="4"/>
       <c r="AH55" s="4"/>
@@ -5431,13 +5431,13 @@
       <c r="AO55" s="5"/>
       <c r="AP55" s="5"/>
     </row>
-    <row r="56" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>55</v>
@@ -5494,7 +5494,7 @@
         <v>53</v>
       </c>
       <c r="AF56" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG56" s="4"/>
       <c r="AH56" s="4"/>
@@ -5513,13 +5513,13 @@
       <c r="AO56" s="5"/>
       <c r="AP56" s="5"/>
     </row>
-    <row r="57" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>56</v>
@@ -5576,7 +5576,7 @@
         <v>53</v>
       </c>
       <c r="AF57" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG57" s="4"/>
       <c r="AH57" s="4"/>
@@ -5595,16 +5595,16 @@
       <c r="AO57" s="5"/>
       <c r="AP57" s="5"/>
     </row>
-    <row r="58" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>44</v>
@@ -5658,7 +5658,7 @@
         <v>53</v>
       </c>
       <c r="AF58" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG58" s="4"/>
       <c r="AH58" s="4"/>
@@ -5677,16 +5677,16 @@
       <c r="AO58" s="5"/>
       <c r="AP58" s="5"/>
     </row>
-    <row r="59" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>44</v>
@@ -5740,7 +5740,7 @@
         <v>53</v>
       </c>
       <c r="AF59" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG59" s="4"/>
       <c r="AH59" s="4"/>
@@ -5759,13 +5759,13 @@
       <c r="AO59" s="5"/>
       <c r="AP59" s="5"/>
     </row>
-    <row r="60" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>43</v>
@@ -5822,7 +5822,7 @@
         <v>53</v>
       </c>
       <c r="AF60" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG60" s="4"/>
       <c r="AH60" s="4"/>
@@ -5841,13 +5841,13 @@
       <c r="AO60" s="5"/>
       <c r="AP60" s="5"/>
     </row>
-    <row r="61" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>54</v>
@@ -5904,7 +5904,7 @@
         <v>53</v>
       </c>
       <c r="AF61" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG61" s="4"/>
       <c r="AH61" s="4"/>
@@ -5923,13 +5923,13 @@
       <c r="AO61" s="5"/>
       <c r="AP61" s="5"/>
     </row>
-    <row r="62" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>55</v>
@@ -5986,7 +5986,7 @@
         <v>53</v>
       </c>
       <c r="AF62" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG62" s="4"/>
       <c r="AH62" s="4"/>
@@ -6005,13 +6005,13 @@
       <c r="AO62" s="5"/>
       <c r="AP62" s="5"/>
     </row>
-    <row r="63" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>56</v>
@@ -6068,7 +6068,7 @@
         <v>53</v>
       </c>
       <c r="AF63" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG63" s="4"/>
       <c r="AH63" s="4"/>
@@ -6087,13 +6087,13 @@
       <c r="AO63" s="5"/>
       <c r="AP63" s="5"/>
     </row>
-    <row r="64" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>83</v>
@@ -6159,13 +6159,13 @@
       <c r="AO64" s="5"/>
       <c r="AP64" s="5"/>
     </row>
-    <row r="65" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>43</v>
@@ -6233,13 +6233,13 @@
       <c r="AO65" s="5"/>
       <c r="AP65" s="5"/>
     </row>
-    <row r="66" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="4"/>
       <c r="B66" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>43</v>
@@ -6307,13 +6307,13 @@
       <c r="AO66" s="5"/>
       <c r="AP66" s="5"/>
     </row>
-    <row r="67" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="4"/>
       <c r="B67" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>83</v>
@@ -6379,16 +6379,16 @@
       <c r="AO67" s="5"/>
       <c r="AP67" s="5"/>
     </row>
-    <row r="68" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="4"/>
       <c r="B68" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>79</v>
@@ -6453,16 +6453,16 @@
       <c r="AO68" s="5"/>
       <c r="AP68" s="5"/>
     </row>
-    <row r="69" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>79</v>
@@ -6527,13 +6527,13 @@
       <c r="AO69" s="5"/>
       <c r="AP69" s="5"/>
     </row>
-    <row r="70" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>55</v>
@@ -6601,13 +6601,13 @@
       <c r="AO70" s="5"/>
       <c r="AP70" s="5"/>
     </row>
-    <row r="71" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>55</v>
@@ -6675,13 +6675,13 @@
       <c r="AO71" s="5"/>
       <c r="AP71" s="5"/>
     </row>
-    <row r="72" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="4"/>
       <c r="B72" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>56</v>
@@ -6749,13 +6749,13 @@
       <c r="AO72" s="5"/>
       <c r="AP72" s="5"/>
     </row>
-    <row r="73" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="4"/>
       <c r="B73" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>56</v>
@@ -6823,13 +6823,13 @@
       <c r="AO73" s="5"/>
       <c r="AP73" s="5"/>
     </row>
-    <row r="74" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="4"/>
       <c r="B74" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>54</v>
@@ -6897,13 +6897,13 @@
       <c r="AO74" s="5"/>
       <c r="AP74" s="5"/>
     </row>
-    <row r="75" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="4"/>
       <c r="B75" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>54</v>
@@ -6971,7 +6971,7 @@
       <c r="AO75" s="5"/>
       <c r="AP75" s="5"/>
     </row>
-    <row r="76" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="4"/>
       <c r="B76" s="4" t="s">
         <v>42</v>
@@ -7034,7 +7034,7 @@
         <v>53</v>
       </c>
       <c r="AF76" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG76" s="4"/>
       <c r="AH76" s="4"/>
@@ -7053,7 +7053,7 @@
       <c r="AO76" s="5"/>
       <c r="AP76" s="5"/>
     </row>
-    <row r="77" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="4"/>
       <c r="B77" s="4" t="s">
         <v>42</v>
@@ -7116,7 +7116,7 @@
         <v>53</v>
       </c>
       <c r="AF77" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG77" s="4"/>
       <c r="AH77" s="4"/>
@@ -7135,7 +7135,7 @@
       <c r="AO77" s="5"/>
       <c r="AP77" s="5"/>
     </row>
-    <row r="78" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="4"/>
       <c r="B78" s="4" t="s">
         <v>42</v>
@@ -7207,7 +7207,7 @@
       <c r="AO78" s="5"/>
       <c r="AP78" s="5"/>
     </row>
-    <row r="79" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="4"/>
       <c r="B79" s="4" t="s">
         <v>42</v>
@@ -7216,7 +7216,7 @@
         <v>80</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>81</v>
@@ -7270,7 +7270,7 @@
         <v>53</v>
       </c>
       <c r="AF79" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG79" s="4"/>
       <c r="AH79" s="4"/>
@@ -7289,7 +7289,7 @@
       <c r="AO79" s="5"/>
       <c r="AP79" s="5"/>
     </row>
-    <row r="80" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="4"/>
       <c r="B80" s="4" t="s">
         <v>42</v>
@@ -7298,7 +7298,7 @@
         <v>80</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>81</v>
@@ -7352,7 +7352,7 @@
         <v>53</v>
       </c>
       <c r="AF80" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG80" s="4"/>
       <c r="AH80" s="4"/>
@@ -7371,7 +7371,7 @@
       <c r="AO80" s="5"/>
       <c r="AP80" s="5"/>
     </row>
-    <row r="81" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="4"/>
       <c r="B81" s="4" t="s">
         <v>42</v>
@@ -7434,7 +7434,7 @@
         <v>53</v>
       </c>
       <c r="AF81" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG81" s="4"/>
       <c r="AH81" s="4"/>
@@ -7453,7 +7453,7 @@
       <c r="AO81" s="5"/>
       <c r="AP81" s="5"/>
     </row>
-    <row r="82" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="4"/>
       <c r="B82" s="4" t="s">
         <v>42</v>
@@ -7516,7 +7516,7 @@
         <v>53</v>
       </c>
       <c r="AF82" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG82" s="4"/>
       <c r="AH82" s="4"/>
@@ -7535,7 +7535,7 @@
       <c r="AO82" s="5"/>
       <c r="AP82" s="5"/>
     </row>
-    <row r="83" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="4"/>
       <c r="B83" s="4" t="s">
         <v>42</v>
@@ -7598,7 +7598,7 @@
         <v>53</v>
       </c>
       <c r="AF83" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG83" s="4"/>
       <c r="AH83" s="4"/>
@@ -7617,7 +7617,7 @@
       <c r="AO83" s="5"/>
       <c r="AP83" s="5"/>
     </row>
-    <row r="84" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="4"/>
       <c r="B84" s="4" t="s">
         <v>42</v>
@@ -7680,7 +7680,7 @@
         <v>53</v>
       </c>
       <c r="AF84" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG84" s="4"/>
       <c r="AH84" s="4"/>
@@ -7699,7 +7699,7 @@
       <c r="AO84" s="5"/>
       <c r="AP84" s="5"/>
     </row>
-    <row r="85" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="4"/>
       <c r="B85" s="4" t="s">
         <v>42</v>
@@ -7762,7 +7762,7 @@
         <v>53</v>
       </c>
       <c r="AF85" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG85" s="4"/>
       <c r="AH85" s="4"/>
@@ -7781,7 +7781,7 @@
       <c r="AO85" s="5"/>
       <c r="AP85" s="5"/>
     </row>
-    <row r="86" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="4"/>
       <c r="B86" s="4" t="s">
         <v>42</v>
@@ -7844,7 +7844,7 @@
         <v>53</v>
       </c>
       <c r="AF86" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG86" s="4"/>
       <c r="AH86" s="4"/>
@@ -7862,13 +7862,13 @@
       <c r="AO86" s="5"/>
       <c r="AP86" s="5"/>
     </row>
-    <row r="87" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="4"/>
       <c r="B87" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>43</v>
@@ -7936,13 +7936,13 @@
       <c r="AO87" s="5"/>
       <c r="AP87" s="5"/>
     </row>
-    <row r="88" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="4"/>
       <c r="B88" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>43</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="K88" s="4"/>
       <c r="L88" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M88" s="4" t="s">
         <v>60</v>
@@ -7998,10 +7998,10 @@
       <c r="AC88" s="4"/>
       <c r="AD88" s="4"/>
       <c r="AE88" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF88" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG88" s="4"/>
       <c r="AH88" s="4"/>
@@ -8014,13 +8014,13 @@
       <c r="AO88" s="5"/>
       <c r="AP88" s="5"/>
     </row>
-    <row r="89" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="4"/>
       <c r="B89" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>43</v>
@@ -8076,10 +8076,10 @@
       <c r="AC89" s="4"/>
       <c r="AD89" s="4"/>
       <c r="AE89" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF89" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG89" s="4"/>
       <c r="AH89" s="4"/>
@@ -8092,13 +8092,13 @@
       <c r="AO89" s="5"/>
       <c r="AP89" s="5"/>
     </row>
-    <row r="90" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="4"/>
       <c r="B90" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>43</v>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="K90" s="4"/>
       <c r="L90" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M90" s="4" t="s">
         <v>60</v>
@@ -8154,10 +8154,10 @@
       <c r="AC90" s="4"/>
       <c r="AD90" s="4"/>
       <c r="AE90" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF90" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG90" s="4"/>
       <c r="AH90" s="4"/>
@@ -8170,13 +8170,13 @@
       <c r="AO90" s="5"/>
       <c r="AP90" s="5"/>
     </row>
-    <row r="91" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="4"/>
       <c r="B91" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>43</v>
@@ -8232,10 +8232,10 @@
       <c r="AC91" s="4"/>
       <c r="AD91" s="4"/>
       <c r="AE91" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF91" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG91" s="4"/>
       <c r="AH91" s="4"/>
@@ -8248,13 +8248,13 @@
       <c r="AO91" s="5"/>
       <c r="AP91" s="5"/>
     </row>
-    <row r="92" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="4"/>
       <c r="B92" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>54</v>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="K92" s="4"/>
       <c r="L92" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M92" s="4" t="s">
         <v>60</v>
@@ -8310,10 +8310,10 @@
       <c r="AC92" s="4"/>
       <c r="AD92" s="4"/>
       <c r="AE92" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF92" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG92" s="4"/>
       <c r="AH92" s="4"/>
@@ -8326,13 +8326,13 @@
       <c r="AO92" s="5"/>
       <c r="AP92" s="5"/>
     </row>
-    <row r="93" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="4"/>
       <c r="B93" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>54</v>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="K93" s="4"/>
       <c r="L93" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M93" s="4" t="s">
         <v>60</v>
@@ -8388,10 +8388,10 @@
       <c r="AC93" s="4"/>
       <c r="AD93" s="4"/>
       <c r="AE93" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF93" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG93" s="4"/>
       <c r="AH93" s="4"/>
@@ -8404,13 +8404,13 @@
       <c r="AO93" s="5"/>
       <c r="AP93" s="5"/>
     </row>
-    <row r="94" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="4"/>
       <c r="B94" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>54</v>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="K94" s="4"/>
       <c r="L94" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M94" s="4" t="s">
         <v>60</v>
@@ -8466,10 +8466,10 @@
       <c r="AC94" s="4"/>
       <c r="AD94" s="4"/>
       <c r="AE94" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF94" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG94" s="4"/>
       <c r="AH94" s="4"/>
@@ -8482,13 +8482,13 @@
       <c r="AO94" s="5"/>
       <c r="AP94" s="5"/>
     </row>
-    <row r="95" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="4"/>
       <c r="B95" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>54</v>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="K95" s="4"/>
       <c r="L95" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M95" s="4" t="s">
         <v>60</v>
@@ -8544,10 +8544,10 @@
       <c r="AC95" s="4"/>
       <c r="AD95" s="4"/>
       <c r="AE95" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF95" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG95" s="4"/>
       <c r="AH95" s="4"/>
@@ -8560,13 +8560,13 @@
       <c r="AO95" s="5"/>
       <c r="AP95" s="5"/>
     </row>
-    <row r="96" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="4"/>
       <c r="B96" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>54</v>
@@ -8585,7 +8585,7 @@
       </c>
       <c r="K96" s="4"/>
       <c r="L96" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M96" s="4" t="s">
         <v>60</v>
@@ -8622,10 +8622,10 @@
       <c r="AC96" s="4"/>
       <c r="AD96" s="4"/>
       <c r="AE96" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF96" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG96" s="4"/>
       <c r="AH96" s="4"/>
@@ -8638,16 +8638,16 @@
       <c r="AO96" s="5"/>
       <c r="AP96" s="5"/>
     </row>
-    <row r="97" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="4"/>
       <c r="B97" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C97" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>147</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>132</v>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K97" s="4"/>
       <c r="L97" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M97" s="4" t="s">
         <v>60</v>
@@ -8671,7 +8671,7 @@
         <v>126</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>133</v>
+        <v>199</v>
       </c>
       <c r="Q97" s="4">
         <v>60</v>
@@ -8680,7 +8680,7 @@
         <v>85</v>
       </c>
       <c r="S97" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="T97" s="4">
         <v>1</v>
@@ -8692,22 +8692,22 @@
       <c r="W97" s="4"/>
       <c r="X97" s="4"/>
       <c r="Y97" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Z97" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA97" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="AA97" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="AB97" s="4"/>
       <c r="AC97" s="4"/>
       <c r="AD97" s="4"/>
       <c r="AE97" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF97" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AG97" s="4"/>
       <c r="AH97" s="4"/>
@@ -8720,16 +8720,16 @@
       <c r="AO97" s="5"/>
       <c r="AP97" s="5"/>
     </row>
-    <row r="98" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="4"/>
       <c r="B98" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C98" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>147</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>132</v>
@@ -8751,7 +8751,7 @@
         <v>630</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>133</v>
+        <v>199</v>
       </c>
       <c r="Q98" s="4">
         <v>60</v>
@@ -8760,7 +8760,7 @@
         <v>85</v>
       </c>
       <c r="S98" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="T98" s="4">
         <v>1</v>
@@ -8790,7 +8790,7 @@
       <c r="AO98" s="5"/>
       <c r="AP98" s="5"/>
     </row>
-    <row r="99" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="4"/>
       <c r="B99" s="4" t="s">
         <v>42</v>
@@ -8862,13 +8862,13 @@
       <c r="AO99" s="5"/>
       <c r="AP99" s="5"/>
     </row>
-    <row r="100" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="4"/>
       <c r="B100" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>83</v>
@@ -8932,7 +8932,7 @@
       <c r="AO100" s="5"/>
       <c r="AP100" s="5"/>
     </row>
-    <row r="101" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="4"/>
       <c r="B101" s="4" t="s">
         <v>42</v>
@@ -9006,7 +9006,7 @@
       <c r="AO101" s="5"/>
       <c r="AP101" s="5"/>
     </row>
-    <row r="102" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="4"/>
       <c r="B102" s="4" t="s">
         <v>42</v>
@@ -9066,10 +9066,10 @@
       <c r="AC102" s="4"/>
       <c r="AD102" s="4"/>
       <c r="AE102" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF102" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG102" s="4"/>
       <c r="AH102" s="4"/>
@@ -9082,7 +9082,7 @@
       <c r="AO102" s="5"/>
       <c r="AP102" s="5"/>
     </row>
-    <row r="103" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="4"/>
       <c r="B103" s="4" t="s">
         <v>42</v>
@@ -9091,7 +9091,7 @@
         <v>87</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>88</v>
@@ -9156,7 +9156,7 @@
       <c r="AO103" s="5"/>
       <c r="AP103" s="5"/>
     </row>
-    <row r="104" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" s="4"/>
       <c r="B104" s="4" t="s">
         <v>42</v>
@@ -9230,7 +9230,7 @@
       <c r="AO104" s="5"/>
       <c r="AP104" s="5"/>
     </row>
-    <row r="105" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" s="4"/>
       <c r="B105" s="4" t="s">
         <v>42</v>
@@ -9304,7 +9304,7 @@
       <c r="AO105" s="5"/>
       <c r="AP105" s="5"/>
     </row>
-    <row r="106" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" s="4"/>
       <c r="B106" s="4" t="s">
         <v>42</v>
@@ -9378,7 +9378,7 @@
       <c r="AO106" s="5"/>
       <c r="AP106" s="5"/>
     </row>
-    <row r="107" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" s="4"/>
       <c r="B107" s="4" t="s">
         <v>42</v>
@@ -9441,7 +9441,7 @@
         <v>53</v>
       </c>
       <c r="AF107" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG107" s="4">
         <v>1.4620299999999999</v>
@@ -9464,7 +9464,7 @@
       <c r="AO107" s="5"/>
       <c r="AP107" s="5"/>
     </row>
-    <row r="108" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" s="4"/>
       <c r="B108" s="4" t="s">
         <v>42</v>
@@ -9527,7 +9527,7 @@
         <v>53</v>
       </c>
       <c r="AF108" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG108" s="4">
         <v>1.4620299999999999</v>
@@ -9550,7 +9550,7 @@
       <c r="AO108" s="5"/>
       <c r="AP108" s="5"/>
     </row>
-    <row r="109" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" s="4"/>
       <c r="B109" s="4" t="s">
         <v>42</v>
@@ -9622,7 +9622,7 @@
       <c r="AO109" s="5"/>
       <c r="AP109" s="5"/>
     </row>
-    <row r="110" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" s="4"/>
       <c r="B110" s="4" t="s">
         <v>42</v>
@@ -9631,7 +9631,7 @@
         <v>89</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>90</v>
@@ -9685,7 +9685,7 @@
         <v>53</v>
       </c>
       <c r="AF110" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG110" s="4">
         <v>1.4620299999999999</v>
@@ -9708,7 +9708,7 @@
       <c r="AO110" s="5"/>
       <c r="AP110" s="5"/>
     </row>
-    <row r="111" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="4"/>
       <c r="B111" s="4" t="s">
         <v>42</v>
@@ -9717,7 +9717,7 @@
         <v>89</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>90</v>
@@ -9771,7 +9771,7 @@
         <v>53</v>
       </c>
       <c r="AF111" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG111" s="4">
         <v>1.4620299999999999</v>
@@ -9794,7 +9794,7 @@
       <c r="AO111" s="5"/>
       <c r="AP111" s="5"/>
     </row>
-    <row r="112" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" s="4"/>
       <c r="B112" s="4" t="s">
         <v>42</v>
@@ -9857,7 +9857,7 @@
         <v>53</v>
       </c>
       <c r="AF112" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG112" s="4">
         <v>1.4620299999999999</v>
@@ -9880,7 +9880,7 @@
       <c r="AO112" s="5"/>
       <c r="AP112" s="5"/>
     </row>
-    <row r="113" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="4"/>
       <c r="B113" s="4" t="s">
         <v>42</v>
@@ -9943,7 +9943,7 @@
         <v>53</v>
       </c>
       <c r="AF113" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG113" s="4">
         <v>1.4620299999999999</v>
@@ -9966,7 +9966,7 @@
       <c r="AO113" s="5"/>
       <c r="AP113" s="5"/>
     </row>
-    <row r="114" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" s="4"/>
       <c r="B114" s="4" t="s">
         <v>42</v>
@@ -10029,7 +10029,7 @@
         <v>53</v>
       </c>
       <c r="AF114" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG114" s="4">
         <v>1.4620299999999999</v>
@@ -10052,7 +10052,7 @@
       <c r="AO114" s="5"/>
       <c r="AP114" s="5"/>
     </row>
-    <row r="115" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="4"/>
       <c r="B115" s="4" t="s">
         <v>42</v>
@@ -10115,7 +10115,7 @@
         <v>53</v>
       </c>
       <c r="AF115" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG115" s="4">
         <v>1.4620299999999999</v>
@@ -10138,7 +10138,7 @@
       <c r="AO115" s="5"/>
       <c r="AP115" s="5"/>
     </row>
-    <row r="116" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" s="4"/>
       <c r="B116" s="4" t="s">
         <v>42</v>
@@ -10201,7 +10201,7 @@
         <v>53</v>
       </c>
       <c r="AF116" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG116" s="4">
         <v>1.4620299999999999</v>
@@ -10224,7 +10224,7 @@
       <c r="AO116" s="5"/>
       <c r="AP116" s="5"/>
     </row>
-    <row r="117" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="4"/>
       <c r="B117" s="4" t="s">
         <v>42</v>
@@ -10287,7 +10287,7 @@
         <v>53</v>
       </c>
       <c r="AF117" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG117" s="4">
         <v>1.4620299999999999</v>
@@ -10310,7 +10310,7 @@
       <c r="AO117" s="5"/>
       <c r="AP117" s="5"/>
     </row>
-    <row r="118" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" s="4"/>
       <c r="B118" s="4" t="s">
         <v>42</v>
@@ -10373,7 +10373,7 @@
         <v>53</v>
       </c>
       <c r="AF118" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG118" s="4"/>
       <c r="AH118" s="4"/>
@@ -10392,7 +10392,7 @@
       <c r="AO118" s="5"/>
       <c r="AP118" s="5"/>
     </row>
-    <row r="119" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="4"/>
       <c r="B119" s="4" t="s">
         <v>42</v>
@@ -10455,7 +10455,7 @@
         <v>53</v>
       </c>
       <c r="AF119" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG119" s="4"/>
       <c r="AH119" s="4"/>
@@ -10474,7 +10474,7 @@
       <c r="AO119" s="5"/>
       <c r="AP119" s="5"/>
     </row>
-    <row r="120" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" s="4"/>
       <c r="B120" s="4" t="s">
         <v>42</v>
@@ -10534,7 +10534,7 @@
       <c r="AC120" s="4"/>
       <c r="AD120" s="4"/>
       <c r="AE120" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF120" s="4" t="s">
         <v>131</v>
@@ -10550,7 +10550,7 @@
       <c r="AO120" s="5"/>
       <c r="AP120" s="5"/>
     </row>
-    <row r="121" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="4"/>
       <c r="B121" s="4" t="s">
         <v>42</v>
@@ -10559,7 +10559,7 @@
         <v>91</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E121" s="4" t="s">
         <v>92</v>
@@ -10613,7 +10613,7 @@
         <v>53</v>
       </c>
       <c r="AF121" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG121" s="4"/>
       <c r="AH121" s="4"/>
@@ -10632,7 +10632,7 @@
       <c r="AO121" s="5"/>
       <c r="AP121" s="5"/>
     </row>
-    <row r="122" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" s="4"/>
       <c r="B122" s="4" t="s">
         <v>42</v>
@@ -10641,7 +10641,7 @@
         <v>91</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>92</v>
@@ -10695,7 +10695,7 @@
         <v>53</v>
       </c>
       <c r="AF122" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG122" s="4"/>
       <c r="AH122" s="4"/>
@@ -10714,7 +10714,7 @@
       <c r="AO122" s="5"/>
       <c r="AP122" s="5"/>
     </row>
-    <row r="123" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="4"/>
       <c r="B123" s="4" t="s">
         <v>42</v>
@@ -10777,7 +10777,7 @@
         <v>53</v>
       </c>
       <c r="AF123" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG123" s="4"/>
       <c r="AH123" s="4"/>
@@ -10796,7 +10796,7 @@
       <c r="AO123" s="5"/>
       <c r="AP123" s="5"/>
     </row>
-    <row r="124" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" s="4"/>
       <c r="B124" s="4" t="s">
         <v>42</v>
@@ -10859,7 +10859,7 @@
         <v>53</v>
       </c>
       <c r="AF124" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG124" s="4"/>
       <c r="AH124" s="4"/>
@@ -10878,7 +10878,7 @@
       <c r="AO124" s="5"/>
       <c r="AP124" s="5"/>
     </row>
-    <row r="125" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="4"/>
       <c r="B125" s="4" t="s">
         <v>42</v>
@@ -10941,7 +10941,7 @@
         <v>53</v>
       </c>
       <c r="AF125" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG125" s="4"/>
       <c r="AH125" s="4"/>
@@ -10960,7 +10960,7 @@
       <c r="AO125" s="5"/>
       <c r="AP125" s="5"/>
     </row>
-    <row r="126" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" s="4"/>
       <c r="B126" s="4" t="s">
         <v>42</v>
@@ -11023,7 +11023,7 @@
         <v>53</v>
       </c>
       <c r="AF126" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG126" s="4"/>
       <c r="AH126" s="4"/>
@@ -11042,7 +11042,7 @@
       <c r="AO126" s="5"/>
       <c r="AP126" s="5"/>
     </row>
-    <row r="127" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" s="4"/>
       <c r="B127" s="4" t="s">
         <v>42</v>
@@ -11105,7 +11105,7 @@
         <v>53</v>
       </c>
       <c r="AF127" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG127" s="4"/>
       <c r="AH127" s="4"/>
@@ -11124,7 +11124,7 @@
       <c r="AO127" s="5"/>
       <c r="AP127" s="5"/>
     </row>
-    <row r="128" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" s="4"/>
       <c r="B128" s="4" t="s">
         <v>42</v>
@@ -11187,7 +11187,7 @@
         <v>53</v>
       </c>
       <c r="AF128" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG128" s="4"/>
       <c r="AH128" s="4"/>
@@ -11206,7 +11206,7 @@
       <c r="AO128" s="5"/>
       <c r="AP128" s="5"/>
     </row>
-    <row r="129" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" s="4"/>
       <c r="B129" s="4" t="s">
         <v>42</v>
@@ -11280,7 +11280,7 @@
       <c r="AO129" s="5"/>
       <c r="AP129" s="5"/>
     </row>
-    <row r="130" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="4"/>
       <c r="B130" s="4" t="s">
         <v>42</v>
@@ -11354,7 +11354,7 @@
       <c r="AO130" s="5"/>
       <c r="AP130" s="5"/>
     </row>
-    <row r="131" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" s="4"/>
       <c r="B131" s="4" t="s">
         <v>42</v>
@@ -11426,7 +11426,7 @@
       <c r="AO131" s="5"/>
       <c r="AP131" s="5"/>
     </row>
-    <row r="132" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" s="4"/>
       <c r="B132" s="4" t="s">
         <v>42</v>
@@ -11435,7 +11435,7 @@
         <v>93</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>94</v>
@@ -11500,7 +11500,7 @@
       <c r="AO132" s="5"/>
       <c r="AP132" s="5"/>
     </row>
-    <row r="133" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="4"/>
       <c r="B133" s="4" t="s">
         <v>42</v>
@@ -11509,7 +11509,7 @@
         <v>93</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>94</v>
@@ -11574,7 +11574,7 @@
       <c r="AO133" s="5"/>
       <c r="AP133" s="5"/>
     </row>
-    <row r="134" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" s="4"/>
       <c r="B134" s="4" t="s">
         <v>42</v>
@@ -11583,7 +11583,7 @@
         <v>93</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>94</v>
@@ -11646,7 +11646,7 @@
       <c r="AO134" s="5"/>
       <c r="AP134" s="5"/>
     </row>
-    <row r="135" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" s="4"/>
       <c r="B135" s="4" t="s">
         <v>42</v>
@@ -11720,7 +11720,7 @@
       <c r="AO135" s="5"/>
       <c r="AP135" s="5"/>
     </row>
-    <row r="136" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" s="4"/>
       <c r="B136" s="4" t="s">
         <v>42</v>
@@ -11794,7 +11794,7 @@
       <c r="AO136" s="5"/>
       <c r="AP136" s="5"/>
     </row>
-    <row r="137" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" s="4"/>
       <c r="B137" s="4" t="s">
         <v>42</v>
@@ -11868,7 +11868,7 @@
       <c r="AO137" s="5"/>
       <c r="AP137" s="5"/>
     </row>
-    <row r="138" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" s="4"/>
       <c r="B138" s="4" t="s">
         <v>42</v>
@@ -11942,7 +11942,7 @@
       <c r="AO138" s="5"/>
       <c r="AP138" s="5"/>
     </row>
-    <row r="139" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" s="4"/>
       <c r="B139" s="4" t="s">
         <v>42</v>
@@ -12016,7 +12016,7 @@
       <c r="AO139" s="5"/>
       <c r="AP139" s="5"/>
     </row>
-    <row r="140" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" s="4"/>
       <c r="B140" s="4" t="s">
         <v>42</v>
@@ -12090,7 +12090,7 @@
       <c r="AO140" s="5"/>
       <c r="AP140" s="5"/>
     </row>
-    <row r="141" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" s="4"/>
       <c r="B141" s="4" t="s">
         <v>42</v>
@@ -12099,7 +12099,7 @@
         <v>93</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>94</v>
@@ -12162,7 +12162,7 @@
       <c r="AO141" s="5"/>
       <c r="AP141" s="5"/>
     </row>
-    <row r="142" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" s="4"/>
       <c r="B142" s="4" t="s">
         <v>42</v>
@@ -12225,7 +12225,7 @@
         <v>53</v>
       </c>
       <c r="AF142" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG142" s="4"/>
       <c r="AH142" s="4"/>
@@ -12244,7 +12244,7 @@
       <c r="AO142" s="5"/>
       <c r="AP142" s="5"/>
     </row>
-    <row r="143" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" s="4"/>
       <c r="B143" s="4" t="s">
         <v>42</v>
@@ -12307,7 +12307,7 @@
         <v>53</v>
       </c>
       <c r="AF143" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG143" s="4"/>
       <c r="AH143" s="4"/>
@@ -12326,7 +12326,7 @@
       <c r="AO143" s="5"/>
       <c r="AP143" s="5"/>
     </row>
-    <row r="144" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" s="4"/>
       <c r="B144" s="4" t="s">
         <v>42</v>
@@ -12398,7 +12398,7 @@
       <c r="AO144" s="5"/>
       <c r="AP144" s="5"/>
     </row>
-    <row r="145" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" s="4"/>
       <c r="B145" s="4" t="s">
         <v>42</v>
@@ -12407,7 +12407,7 @@
         <v>95</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>96</v>
@@ -12461,7 +12461,7 @@
         <v>53</v>
       </c>
       <c r="AF145" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG145" s="4"/>
       <c r="AH145" s="4"/>
@@ -12480,7 +12480,7 @@
       <c r="AO145" s="5"/>
       <c r="AP145" s="5"/>
     </row>
-    <row r="146" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" s="4"/>
       <c r="B146" s="4" t="s">
         <v>42</v>
@@ -12489,7 +12489,7 @@
         <v>95</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>96</v>
@@ -12543,7 +12543,7 @@
         <v>53</v>
       </c>
       <c r="AF146" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG146" s="4"/>
       <c r="AH146" s="4"/>
@@ -12562,7 +12562,7 @@
       <c r="AO146" s="5"/>
       <c r="AP146" s="5"/>
     </row>
-    <row r="147" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" s="4"/>
       <c r="B147" s="4" t="s">
         <v>42</v>
@@ -12571,7 +12571,7 @@
         <v>95</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>96</v>
@@ -12634,7 +12634,7 @@
       <c r="AO147" s="5"/>
       <c r="AP147" s="5"/>
     </row>
-    <row r="148" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" s="4"/>
       <c r="B148" s="4" t="s">
         <v>42</v>
@@ -12697,7 +12697,7 @@
         <v>53</v>
       </c>
       <c r="AF148" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG148" s="4"/>
       <c r="AH148" s="4"/>
@@ -12716,7 +12716,7 @@
       <c r="AO148" s="5"/>
       <c r="AP148" s="5"/>
     </row>
-    <row r="149" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" s="4"/>
       <c r="B149" s="4" t="s">
         <v>42</v>
@@ -12779,7 +12779,7 @@
         <v>53</v>
       </c>
       <c r="AF149" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG149" s="4"/>
       <c r="AH149" s="4"/>
@@ -12798,7 +12798,7 @@
       <c r="AO149" s="5"/>
       <c r="AP149" s="5"/>
     </row>
-    <row r="150" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A150" s="4"/>
       <c r="B150" s="4" t="s">
         <v>42</v>
@@ -12861,7 +12861,7 @@
         <v>53</v>
       </c>
       <c r="AF150" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG150" s="4"/>
       <c r="AH150" s="4"/>
@@ -12880,7 +12880,7 @@
       <c r="AO150" s="5"/>
       <c r="AP150" s="5"/>
     </row>
-    <row r="151" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A151" s="4"/>
       <c r="B151" s="4" t="s">
         <v>42</v>
@@ -12943,7 +12943,7 @@
         <v>53</v>
       </c>
       <c r="AF151" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG151" s="4"/>
       <c r="AH151" s="4"/>
@@ -12962,7 +12962,7 @@
       <c r="AO151" s="5"/>
       <c r="AP151" s="5"/>
     </row>
-    <row r="152" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A152" s="4"/>
       <c r="B152" s="4" t="s">
         <v>42</v>
@@ -13025,7 +13025,7 @@
         <v>53</v>
       </c>
       <c r="AF152" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG152" s="4"/>
       <c r="AH152" s="4"/>
@@ -13044,7 +13044,7 @@
       <c r="AO152" s="5"/>
       <c r="AP152" s="5"/>
     </row>
-    <row r="153" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" s="4"/>
       <c r="B153" s="4" t="s">
         <v>42</v>
@@ -13107,7 +13107,7 @@
         <v>53</v>
       </c>
       <c r="AF153" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG153" s="4"/>
       <c r="AH153" s="4"/>
@@ -13126,7 +13126,7 @@
       <c r="AO153" s="5"/>
       <c r="AP153" s="5"/>
     </row>
-    <row r="154" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A154" s="4"/>
       <c r="B154" s="4" t="s">
         <v>42</v>
@@ -13135,7 +13135,7 @@
         <v>95</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E154" s="4" t="s">
         <v>96</v>
@@ -13198,7 +13198,7 @@
       <c r="AO154" s="5"/>
       <c r="AP154" s="5"/>
     </row>
-    <row r="155" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A155" s="4"/>
       <c r="B155" s="4" t="s">
         <v>42</v>
@@ -13270,7 +13270,7 @@
       <c r="AO155" s="5"/>
       <c r="AP155" s="5"/>
     </row>
-    <row r="156" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A156" s="4"/>
       <c r="B156" s="4" t="s">
         <v>42</v>
@@ -13342,7 +13342,7 @@
       <c r="AO156" s="5"/>
       <c r="AP156" s="5"/>
     </row>
-    <row r="157" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A157" s="4"/>
       <c r="B157" s="4" t="s">
         <v>42</v>
@@ -13351,7 +13351,7 @@
         <v>67</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>100</v>
@@ -13414,7 +13414,7 @@
       <c r="AO157" s="5"/>
       <c r="AP157" s="5"/>
     </row>
-    <row r="158" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A158" s="4"/>
       <c r="B158" s="4" t="s">
         <v>42</v>
@@ -13423,7 +13423,7 @@
         <v>67</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E158" s="4" t="s">
         <v>100</v>
@@ -13486,7 +13486,7 @@
       <c r="AO158" s="5"/>
       <c r="AP158" s="5"/>
     </row>
-    <row r="159" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A159" s="4"/>
       <c r="B159" s="4" t="s">
         <v>42</v>
@@ -13495,7 +13495,7 @@
         <v>67</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E159" s="4" t="s">
         <v>100</v>
@@ -13558,7 +13558,7 @@
       <c r="AO159" s="5"/>
       <c r="AP159" s="5"/>
     </row>
-    <row r="160" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A160" s="4"/>
       <c r="B160" s="4" t="s">
         <v>42</v>
@@ -13567,7 +13567,7 @@
         <v>67</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>100</v>
@@ -13630,7 +13630,7 @@
       <c r="AO160" s="5"/>
       <c r="AP160" s="5"/>
     </row>
-    <row r="161" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A161" s="4"/>
       <c r="B161" s="4" t="s">
         <v>42</v>
@@ -13639,7 +13639,7 @@
         <v>67</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E161" s="4" t="s">
         <v>100</v>
@@ -13702,7 +13702,7 @@
       <c r="AO161" s="5"/>
       <c r="AP161" s="5"/>
     </row>
-    <row r="162" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A162" s="4"/>
       <c r="B162" s="4" t="s">
         <v>42</v>
@@ -13774,7 +13774,7 @@
       <c r="AO162" s="5"/>
       <c r="AP162" s="5"/>
     </row>
-    <row r="163" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A163" s="4"/>
       <c r="B163" s="4" t="s">
         <v>42</v>
@@ -13783,7 +13783,7 @@
         <v>67</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E163" s="4" t="s">
         <v>100</v>
@@ -13846,7 +13846,7 @@
       <c r="AO163" s="5"/>
       <c r="AP163" s="5"/>
     </row>
-    <row r="164" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A164" s="4"/>
       <c r="B164" s="4" t="s">
         <v>42</v>
@@ -13855,7 +13855,7 @@
         <v>67</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>100</v>
@@ -13918,7 +13918,7 @@
       <c r="AO164" s="5"/>
       <c r="AP164" s="5"/>
     </row>
-    <row r="165" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A165" s="4"/>
       <c r="B165" s="4" t="s">
         <v>42</v>
@@ -13990,7 +13990,7 @@
       <c r="AO165" s="5"/>
       <c r="AP165" s="5"/>
     </row>
-    <row r="166" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A166" s="4"/>
       <c r="B166" s="4" t="s">
         <v>42</v>
@@ -13999,7 +13999,7 @@
         <v>67</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>100</v>
@@ -14062,7 +14062,7 @@
       <c r="AO166" s="5"/>
       <c r="AP166" s="5"/>
     </row>
-    <row r="167" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A167" s="4"/>
       <c r="B167" s="4" t="s">
         <v>42</v>
@@ -14134,7 +14134,7 @@
       <c r="AO167" s="5"/>
       <c r="AP167" s="5"/>
     </row>
-    <row r="168" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A168" s="4"/>
       <c r="B168" s="4" t="s">
         <v>42</v>
@@ -14143,7 +14143,7 @@
         <v>67</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E168" s="4" t="s">
         <v>100</v>
@@ -14206,13 +14206,13 @@
       <c r="AO168" s="5"/>
       <c r="AP168" s="5"/>
     </row>
-    <row r="169" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A169" s="4"/>
       <c r="B169" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D169" s="4" t="s">
         <v>83</v>
@@ -14276,7 +14276,7 @@
       <c r="AO169" s="5"/>
       <c r="AP169" s="5"/>
     </row>
-    <row r="170" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A170" s="4"/>
       <c r="B170" s="4" t="s">
         <v>42</v>
@@ -14338,7 +14338,7 @@
       <c r="AC170" s="4"/>
       <c r="AD170" s="4"/>
       <c r="AE170" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF170" s="4" t="s">
         <v>105</v>
@@ -14354,7 +14354,7 @@
       <c r="AO170" s="5"/>
       <c r="AP170" s="5"/>
     </row>
-    <row r="171" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171" s="4"/>
       <c r="B171" s="4" t="s">
         <v>42</v>
@@ -14416,7 +14416,7 @@
       <c r="AC171" s="4"/>
       <c r="AD171" s="4"/>
       <c r="AE171" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF171" s="4" t="s">
         <v>105</v>
@@ -14432,7 +14432,7 @@
       <c r="AO171" s="5"/>
       <c r="AP171" s="5"/>
     </row>
-    <row r="172" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" s="4"/>
       <c r="B172" s="4" t="s">
         <v>42</v>
@@ -14504,7 +14504,7 @@
       <c r="AO172" s="5"/>
       <c r="AP172" s="5"/>
     </row>
-    <row r="173" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A173" s="4"/>
       <c r="B173" s="4" t="s">
         <v>42</v>
@@ -14513,7 +14513,7 @@
         <v>103</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E173" s="4" t="s">
         <v>104</v>
@@ -14566,7 +14566,7 @@
       <c r="AC173" s="4"/>
       <c r="AD173" s="4"/>
       <c r="AE173" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF173" s="4" t="s">
         <v>105</v>
@@ -14582,7 +14582,7 @@
       <c r="AO173" s="5"/>
       <c r="AP173" s="5"/>
     </row>
-    <row r="174" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A174" s="4"/>
       <c r="B174" s="4" t="s">
         <v>42</v>
@@ -14591,7 +14591,7 @@
         <v>103</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>104</v>
@@ -14644,7 +14644,7 @@
       <c r="AC174" s="4"/>
       <c r="AD174" s="4"/>
       <c r="AE174" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF174" s="4" t="s">
         <v>105</v>
@@ -14660,7 +14660,7 @@
       <c r="AO174" s="5"/>
       <c r="AP174" s="5"/>
     </row>
-    <row r="175" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A175" s="4"/>
       <c r="B175" s="4" t="s">
         <v>42</v>
@@ -14669,7 +14669,7 @@
         <v>103</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>104</v>
@@ -14732,7 +14732,7 @@
       <c r="AO175" s="5"/>
       <c r="AP175" s="5"/>
     </row>
-    <row r="176" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A176" s="4"/>
       <c r="B176" s="4" t="s">
         <v>42</v>
@@ -14794,7 +14794,7 @@
       <c r="AC176" s="4"/>
       <c r="AD176" s="4"/>
       <c r="AE176" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF176" s="4" t="s">
         <v>105</v>
@@ -14810,7 +14810,7 @@
       <c r="AO176" s="5"/>
       <c r="AP176" s="5"/>
     </row>
-    <row r="177" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A177" s="4"/>
       <c r="B177" s="4" t="s">
         <v>42</v>
@@ -14872,7 +14872,7 @@
       <c r="AC177" s="4"/>
       <c r="AD177" s="4"/>
       <c r="AE177" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF177" s="4" t="s">
         <v>105</v>
@@ -14888,7 +14888,7 @@
       <c r="AO177" s="5"/>
       <c r="AP177" s="5"/>
     </row>
-    <row r="178" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A178" s="4"/>
       <c r="B178" s="4" t="s">
         <v>42</v>
@@ -14950,7 +14950,7 @@
       <c r="AC178" s="4"/>
       <c r="AD178" s="4"/>
       <c r="AE178" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF178" s="4" t="s">
         <v>105</v>
@@ -14966,7 +14966,7 @@
       <c r="AO178" s="5"/>
       <c r="AP178" s="5"/>
     </row>
-    <row r="179" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" s="4"/>
       <c r="B179" s="4" t="s">
         <v>42</v>
@@ -15028,7 +15028,7 @@
       <c r="AC179" s="4"/>
       <c r="AD179" s="4"/>
       <c r="AE179" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF179" s="4" t="s">
         <v>105</v>
@@ -15044,7 +15044,7 @@
       <c r="AO179" s="5"/>
       <c r="AP179" s="5"/>
     </row>
-    <row r="180" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A180" s="4"/>
       <c r="B180" s="4" t="s">
         <v>42</v>
@@ -15106,7 +15106,7 @@
       <c r="AC180" s="4"/>
       <c r="AD180" s="4"/>
       <c r="AE180" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF180" s="4" t="s">
         <v>105</v>
@@ -15122,7 +15122,7 @@
       <c r="AO180" s="5"/>
       <c r="AP180" s="5"/>
     </row>
-    <row r="181" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A181" s="4"/>
       <c r="B181" s="4" t="s">
         <v>42</v>
@@ -15184,7 +15184,7 @@
       <c r="AC181" s="4"/>
       <c r="AD181" s="4"/>
       <c r="AE181" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF181" s="4" t="s">
         <v>105</v>
@@ -15200,7 +15200,7 @@
       <c r="AO181" s="5"/>
       <c r="AP181" s="5"/>
     </row>
-    <row r="182" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A182" s="4"/>
       <c r="B182" s="4" t="s">
         <v>42</v>
@@ -15209,7 +15209,7 @@
         <v>103</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>104</v>
@@ -15272,7 +15272,7 @@
       <c r="AO182" s="5"/>
       <c r="AP182" s="5"/>
     </row>
-    <row r="183" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A183" s="4"/>
       <c r="B183" s="4" t="s">
         <v>42</v>
@@ -15332,10 +15332,10 @@
       <c r="AC183" s="4"/>
       <c r="AD183" s="4"/>
       <c r="AE183" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF183" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG183" s="4"/>
       <c r="AH183" s="4"/>
@@ -15354,7 +15354,7 @@
       <c r="AO183" s="5"/>
       <c r="AP183" s="5"/>
     </row>
-    <row r="184" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A184" s="4"/>
       <c r="B184" s="4" t="s">
         <v>42</v>
@@ -15426,7 +15426,7 @@
       <c r="AO184" s="5"/>
       <c r="AP184" s="5"/>
     </row>
-    <row r="185" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A185" s="4"/>
       <c r="B185" s="4" t="s">
         <v>42</v>
@@ -15435,7 +15435,7 @@
         <v>106</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E185" s="4" t="s">
         <v>107</v>
@@ -15489,7 +15489,7 @@
         <v>53</v>
       </c>
       <c r="AF185" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG185" s="4"/>
       <c r="AH185" s="4"/>
@@ -15508,7 +15508,7 @@
       <c r="AO185" s="5"/>
       <c r="AP185" s="5"/>
     </row>
-    <row r="186" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A186" s="4"/>
       <c r="B186" s="4" t="s">
         <v>42</v>
@@ -15571,7 +15571,7 @@
         <v>53</v>
       </c>
       <c r="AF186" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG186" s="4"/>
       <c r="AH186" s="4"/>
@@ -15590,7 +15590,7 @@
       <c r="AO186" s="5"/>
       <c r="AP186" s="5"/>
     </row>
-    <row r="187" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A187" s="4"/>
       <c r="B187" s="4" t="s">
         <v>42</v>
@@ -15653,7 +15653,7 @@
         <v>53</v>
       </c>
       <c r="AF187" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG187" s="4"/>
       <c r="AH187" s="4"/>
@@ -15672,7 +15672,7 @@
       <c r="AO187" s="5"/>
       <c r="AP187" s="5"/>
     </row>
-    <row r="188" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A188" s="4"/>
       <c r="B188" s="4" t="s">
         <v>42</v>
@@ -15735,7 +15735,7 @@
         <v>53</v>
       </c>
       <c r="AF188" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG188" s="4"/>
       <c r="AH188" s="4"/>
@@ -15754,7 +15754,7 @@
       <c r="AO188" s="5"/>
       <c r="AP188" s="5"/>
     </row>
-    <row r="189" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A189" s="4"/>
       <c r="B189" s="4" t="s">
         <v>42</v>
@@ -15810,7 +15810,7 @@
       <c r="AC189" s="4"/>
       <c r="AD189" s="4"/>
       <c r="AE189" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF189" s="4" t="s">
         <v>112</v>
@@ -15826,7 +15826,7 @@
       <c r="AO189" s="5"/>
       <c r="AP189" s="5"/>
     </row>
-    <row r="190" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A190" s="4"/>
       <c r="B190" s="4" t="s">
         <v>42</v>
@@ -15896,7 +15896,7 @@
       <c r="AO190" s="5"/>
       <c r="AP190" s="5"/>
     </row>
-    <row r="191" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A191" s="4"/>
       <c r="B191" s="4" t="s">
         <v>42</v>
@@ -15952,10 +15952,10 @@
       <c r="AC191" s="4"/>
       <c r="AD191" s="4"/>
       <c r="AE191" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF191" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG191" s="4"/>
       <c r="AH191" s="4"/>
@@ -15968,7 +15968,7 @@
       <c r="AO191" s="5"/>
       <c r="AP191" s="5"/>
     </row>
-    <row r="192" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A192" s="4"/>
       <c r="B192" s="4" t="s">
         <v>42</v>
@@ -16038,7 +16038,7 @@
       <c r="AO192" s="5"/>
       <c r="AP192" s="5"/>
     </row>
-    <row r="193" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A193" s="4"/>
       <c r="B193" s="4" t="s">
         <v>42</v>
@@ -16110,7 +16110,7 @@
       <c r="AO193" s="5"/>
       <c r="AP193" s="5"/>
     </row>
-    <row r="194" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A194" s="4"/>
       <c r="B194" s="4" t="s">
         <v>42</v>
@@ -16119,7 +16119,7 @@
         <v>122</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E194" s="4" t="s">
         <v>123</v>
@@ -16182,7 +16182,7 @@
       <c r="AO194" s="5"/>
       <c r="AP194" s="5"/>
     </row>
-    <row r="195" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A195" s="4"/>
       <c r="B195" s="4" t="s">
         <v>42</v>
@@ -16191,7 +16191,7 @@
         <v>122</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E195" s="4" t="s">
         <v>123</v>
@@ -16254,7 +16254,7 @@
       <c r="AO195" s="5"/>
       <c r="AP195" s="5"/>
     </row>
-    <row r="196" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A196" s="4"/>
       <c r="B196" s="4" t="s">
         <v>42</v>
@@ -16324,7 +16324,7 @@
       <c r="AO196" s="5"/>
       <c r="AP196" s="5"/>
     </row>
-    <row r="197" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A197" s="4"/>
       <c r="B197" s="4" t="s">
         <v>42</v>
@@ -16387,7 +16387,7 @@
         <v>53</v>
       </c>
       <c r="AF197" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG197" s="4"/>
       <c r="AH197" s="4"/>
@@ -16406,7 +16406,7 @@
       <c r="AO197" s="5"/>
       <c r="AP197" s="5"/>
     </row>
-    <row r="198" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A198" s="4"/>
       <c r="B198" s="4" t="s">
         <v>42</v>
@@ -16469,7 +16469,7 @@
         <v>53</v>
       </c>
       <c r="AF198" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG198" s="4"/>
       <c r="AH198" s="4"/>
@@ -16488,7 +16488,7 @@
       <c r="AO198" s="5"/>
       <c r="AP198" s="5"/>
     </row>
-    <row r="199" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A199" s="4"/>
       <c r="B199" s="4" t="s">
         <v>42</v>
@@ -16560,7 +16560,7 @@
       <c r="AO199" s="5"/>
       <c r="AP199" s="5"/>
     </row>
-    <row r="200" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A200" s="4"/>
       <c r="B200" s="4" t="s">
         <v>42</v>
@@ -16569,7 +16569,7 @@
         <v>113</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E200" s="4" t="s">
         <v>114</v>
@@ -16623,7 +16623,7 @@
         <v>53</v>
       </c>
       <c r="AF200" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG200" s="4"/>
       <c r="AH200" s="4"/>
@@ -16642,7 +16642,7 @@
       <c r="AO200" s="5"/>
       <c r="AP200" s="5"/>
     </row>
-    <row r="201" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A201" s="4"/>
       <c r="B201" s="4" t="s">
         <v>42</v>
@@ -16651,7 +16651,7 @@
         <v>113</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E201" s="4" t="s">
         <v>114</v>
@@ -16705,7 +16705,7 @@
         <v>53</v>
       </c>
       <c r="AF201" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG201" s="4"/>
       <c r="AH201" s="4"/>
@@ -16724,7 +16724,7 @@
       <c r="AO201" s="5"/>
       <c r="AP201" s="5"/>
     </row>
-    <row r="202" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A202" s="4"/>
       <c r="B202" s="4" t="s">
         <v>42</v>
@@ -16733,7 +16733,7 @@
         <v>113</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E202" s="4" t="s">
         <v>114</v>
@@ -16796,7 +16796,7 @@
       <c r="AO202" s="5"/>
       <c r="AP202" s="5"/>
     </row>
-    <row r="203" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A203" s="4"/>
       <c r="B203" s="4" t="s">
         <v>42</v>
@@ -16859,7 +16859,7 @@
         <v>53</v>
       </c>
       <c r="AF203" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG203" s="4"/>
       <c r="AH203" s="4"/>
@@ -16878,7 +16878,7 @@
       <c r="AO203" s="5"/>
       <c r="AP203" s="5"/>
     </row>
-    <row r="204" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A204" s="4"/>
       <c r="B204" s="4" t="s">
         <v>42</v>
@@ -16941,7 +16941,7 @@
         <v>53</v>
       </c>
       <c r="AF204" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG204" s="4"/>
       <c r="AH204" s="4"/>
@@ -16960,7 +16960,7 @@
       <c r="AO204" s="5"/>
       <c r="AP204" s="5"/>
     </row>
-    <row r="205" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A205" s="4"/>
       <c r="B205" s="4" t="s">
         <v>42</v>
@@ -17023,7 +17023,7 @@
         <v>53</v>
       </c>
       <c r="AF205" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG205" s="4"/>
       <c r="AH205" s="4"/>
@@ -17042,7 +17042,7 @@
       <c r="AO205" s="5"/>
       <c r="AP205" s="5"/>
     </row>
-    <row r="206" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A206" s="4"/>
       <c r="B206" s="4" t="s">
         <v>42</v>
@@ -17105,7 +17105,7 @@
         <v>53</v>
       </c>
       <c r="AF206" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG206" s="4"/>
       <c r="AH206" s="4"/>
@@ -17124,7 +17124,7 @@
       <c r="AO206" s="5"/>
       <c r="AP206" s="5"/>
     </row>
-    <row r="207" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A207" s="4"/>
       <c r="B207" s="4" t="s">
         <v>42</v>
@@ -17187,7 +17187,7 @@
         <v>53</v>
       </c>
       <c r="AF207" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG207" s="4"/>
       <c r="AH207" s="4"/>
@@ -17206,7 +17206,7 @@
       <c r="AO207" s="5"/>
       <c r="AP207" s="5"/>
     </row>
-    <row r="208" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A208" s="4"/>
       <c r="B208" s="4" t="s">
         <v>42</v>
@@ -17269,7 +17269,7 @@
         <v>53</v>
       </c>
       <c r="AF208" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG208" s="4"/>
       <c r="AH208" s="4"/>
@@ -17288,7 +17288,7 @@
       <c r="AO208" s="5"/>
       <c r="AP208" s="5"/>
     </row>
-    <row r="209" spans="1:42" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:42" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A209" s="4"/>
       <c r="B209" s="4" t="s">
         <v>42</v>
@@ -17297,7 +17297,7 @@
         <v>113</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E209" s="4" t="s">
         <v>114</v>

--- a/inst/extdata/wyoming_criteria_crosswalk.xlsx
+++ b/inst/extdata/wyoming_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{D95CC2E3-7BD7-43D9-9C03-5A64357668C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EB15A9C-D17D-40ED-B5B1-72B65FEEAEFF}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{D95CC2E3-7BD7-43D9-9C03-5A64357668C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42895750-7AEE-43ED-BBD9-FA8BB4FD3B7D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{254103FA-C5D3-4049-B135-21AE92C6DC6D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{254103FA-C5D3-4049-B135-21AE92C6DC6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="195">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -284,9 +284,6 @@
     <t>CHLORIDE</t>
   </si>
   <si>
-    <t>Value applies to waters designated for coldwater aquatic life, warmwater aquatic life, and modified aquatic life only. There are several waterbodies with site-specific criteria for chloride.  See footnote f in Table 7 of the revised standards.</t>
-  </si>
-  <si>
     <t>CHROMIUM(VI)</t>
   </si>
   <si>
@@ -365,9 +362,6 @@
     <t>SELENIUM</t>
   </si>
   <si>
-    <t>In accordance with Chapter 1, Appendix B(c) Cottonwood Creek near Hamilton Dome in the Bighorn River watershed has an instantaneous maximum total selenium criterion of 43 ug/L not to be exceeded at any time.</t>
-  </si>
-  <si>
     <t>Silver</t>
   </si>
   <si>
@@ -386,9 +380,6 @@
     <t>arithmetic max</t>
   </si>
   <si>
-    <t>When ambient temperature is &gt;15.6 degrees, exceedance occurs if pollution increases temperature &gt;1.1 degrees than existing temperatures</t>
-  </si>
-  <si>
     <t>Zinc</t>
   </si>
   <si>
@@ -443,18 +434,12 @@
     <t>mrem/day</t>
   </si>
   <si>
-    <t>Based on taste and odor effects and is more stringent than if based solely on toxic or carcinogenic effects.  See Chapter 1 Table 9, footnote k - this criterion does not apply to the Belle Fourche River above the confluence with Donkey Creek, mainstem of the Belle Fourche River, tributaries to Antelope Creek in the Cheyenne River watershed, Little Thunder Creek and all of its tributaries below the confluence with North Prong Creek in the Cheyenne River watershed, the Little Powder River watershed, the mainstem of Clear Creek and its tributaries upstream of Clearmont, WY in the Powder River watershed, the mainstem of Crazy Woman Creek and its tributaries in the Powder River watershed, the North Fork of the Powder River and all its tributaries in the Powder River watershed, and the Middle Fork of the Powder River and all its tributaries in the Powder River watershed.</t>
-  </si>
-  <si>
     <t>ESCHERICHIA COLI</t>
   </si>
   <si>
     <t>geometric mean</t>
   </si>
   <si>
-    <t>For waters designated for full-body contact water recreation, the criterion 630 organisms/100 mL applies October 1 - April 30.</t>
-  </si>
-  <si>
     <t>Industry</t>
   </si>
   <si>
@@ -464,9 +449,6 @@
     <t>0.411/(1+10^(7.204-pH)) + 58.4/(1+10^(pH-7.204))</t>
   </si>
   <si>
-    <t>When ambient temperature is &gt;15.6 degrees, exceedance occurs if pollution increases temperature &gt;2.2 degrees than existing temperatures</t>
-  </si>
-  <si>
     <t>CHROMIUM, TRIVALENT, TOTAL</t>
   </si>
   <si>
@@ -524,9 +506,6 @@
     <t>0.860*(e^(0.8190*(ln(hardness))+0.6848))</t>
   </si>
   <si>
-    <t>Additional Information</t>
-  </si>
-  <si>
     <t>(1.136672-(ln(hardness)*0.041838))*(e^(1.0166*(ln(hardness))-3.924))</t>
   </si>
   <si>
@@ -563,36 +542,15 @@
     <t>(0.986)*e^(0.846*(ln(hardness))+0.884)</t>
   </si>
   <si>
-    <t>Based on SDWA secondary standards to prevent undesirable cosmetic or aesthetic effects. See Chapter 1 Table 9, footnote k - this criterion does not apply to the Belle Fourche River above the confluence with Donkey Creek, mainstem of the Belle Fourche River, tributaries to Antelope Creek in the Cheyenne River watershed, Little Thunder Creek and all of its tributaries below the confluence with North Prong Creek in the Cheyenne River watershed, the Little Powder River watershed, the mainstem of Clear Creek and its tributaries upstream of Clearmont, WY in the Powder River watershed, the mainstem of Crazy Woman Creek and its tributaries in the Powder River watershed, the North Fork of the Powder River and all its tributaries in the Powder River watershed, and the Middle Fork of the Powder River and all its tributaries in the Powder River watershed.</t>
-  </si>
-  <si>
     <t>Oct 1</t>
   </si>
   <si>
     <t>Apr 30</t>
   </si>
   <si>
-    <t>Applies except where the receiving water after mixing has a pH &gt;= 7.0 and a CaCO3 hardness &gt;= 50 mg/L, where the 750 ug/L acute criterion will apply.</t>
-  </si>
-  <si>
-    <t>Clarify that the 6.5 mg/L criterion applies to early life stages that are exposed directly to the water column (e.g., lakes). A criterion of 9.5 mg/L applies where early life stages are not exposed directly to the water column (e.g., streams) and is the required concentration to achieve an intergravel DO of 6.5 mg/L. In the lower portion of a lake or reservoir, dissolved oxygen may be less than the applicable value provided that, where those excursions occur, there is adequate habitat for aquatic life where both the applicable biologically-based temperature requriements and dissolved oxygen criteria are met.</t>
-  </si>
-  <si>
-    <t>In the lower portion of a lake or reservoir, dissolved oxygen may be less than the applicable value provided that, where those excursions occur, there is adequate habitat for aquatic life where both the applicable biologically-based temperature requriements and dissolved oxygen criteria are met.</t>
-  </si>
-  <si>
-    <t>The 5.0 mg/L criterion applies to early life stages that are exposed directly to the water column (e.g., lakes).  A criterion of 8.0 mg/L criterion applies where early life stages are not exposed directly to the water column (e.g., streams) and is the required concentration to achieve anintergravel DO of 5.0 mg/L.  In the lower portion of a lake or reservoir, dissolved oxygen may be less than the applicable value provided that, where those excursions occur, there is adequate habitat for aquatic life where both the applicable biologically-based temperature requriements and dissolved oxygen criteria are met.</t>
-  </si>
-  <si>
     <t>Applies to coldwater aquatic life, warmwater aquatic life, and modified aquatic life only</t>
   </si>
   <si>
-    <t>There are several waterbodies with site-specific criteria for chloride.  See footnote f in Table 7 of the revised standards.</t>
-  </si>
-  <si>
-    <t>There are several waterbodies with site-specific criteria for chloride. See footnote f in Table 7 of the revised standards.</t>
-  </si>
-  <si>
     <t>Oct-Apr</t>
   </si>
   <si>
@@ -605,9 +563,6 @@
     <t>(1.101672-(ln(hardness)*0.041838))*e^(0.7409*(ln(hardness)) - 4.719)</t>
   </si>
   <si>
-    <t>(1.136672 - (ln(hardness)*0.041838))*e^(1.0166*(ln(hardness)) - 3.924);  Use a value of 1.0 for the portion of the equation after the if the calculated value of that portion of the equation exceeds 1.0.</t>
-  </si>
-  <si>
     <t>(1.46203 - (ln(hardness)*0.145712))*e^(1.273*(ln(hardness)) - 4.705)</t>
   </si>
   <si>
@@ -641,12 +596,6 @@
     <t>(1.101672 - (ln(hardness)*0.041838))*e^(0.7409*(ln(hardness)) - 4.719)</t>
   </si>
   <si>
-    <t>0.85*e^(1.72*(ln(hardness)) - 6.52)*(0.5); Value multiplied by 0.5 to be comparable with other acute values derived using an averaging period. Value does not need to be multiplied by 0.5 if used as an instantaneous maximum or end of pipe value, as the original value was derived as a not to be exceeded instantaneous maximum.</t>
-  </si>
-  <si>
-    <t>(0.85)*e^(1.72*(ln(hardness))-6.52)*(0.5); Value multiplied by 0.5 to be comparable with other acute values derived using an averaging period. Value does not need to be multiplied by 0.5 if used as an instantaneous maximum or end of pipe value, as the original value was derived as a not to be exceeded instantaneous maximum.</t>
-  </si>
-  <si>
     <t>CFU/100ML</t>
   </si>
   <si>
@@ -659,9 +608,6 @@
     <t>pHDirection</t>
   </si>
   <si>
-    <t>TemperatureExtreme</t>
-  </si>
-  <si>
     <t>MinEqMagnitude</t>
   </si>
   <si>
@@ -686,10 +632,19 @@
     <t>((0.0577/(1+10^(7.688-pH))) + (2.487/(1+10^(pH-7.688)))) * 1.45*10^(0.028*(25-max(Temperature,7)))</t>
   </si>
   <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
+    <t>(0.85)*e^(1.72*(ln(hardness))-6.52)*(0.5)</t>
+  </si>
+  <si>
+    <t>(1.136672 - (ln(hardness)*0.041838))*e^(1.0166*(ln(hardness)) - 3.924)</t>
+  </si>
+  <si>
+    <t>AmmoniaEqType</t>
+  </si>
+  <si>
+    <t>Min Multiplier</t>
+  </si>
+  <si>
+    <t>Max Exponent</t>
   </si>
 </sst>
 </file>
@@ -1100,17 +1055,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1AFC1C8-D989-4C34-AD6B-0180801AF6A9}">
   <dimension ref="A1:AX209"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="12" max="12" width="17.42578125" customWidth="1"/>
-    <col min="31" max="31" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.44140625" customWidth="1"/>
+    <col min="31" max="31" width="22.109375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="88" customWidth="1"/>
-    <col min="33" max="33" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="15" bestFit="1" customWidth="1"/>
     <col min="35" max="38" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1205,13 +1160,13 @@
         <v>30</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="AI1" s="2" t="s">
         <v>31</v>
@@ -1226,7 +1181,7 @@
         <v>34</v>
       </c>
       <c r="AM1" s="2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="AN1" s="2" t="s">
         <v>35</v>
@@ -1241,28 +1196,28 @@
         <v>38</v>
       </c>
       <c r="AR1" s="2" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="AS1" s="2" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="AT1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="AU1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="AV1" s="2" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="AW1" s="6" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="AX1" s="6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="2" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -1271,7 +1226,7 @@
         <v>55</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>56</v>
@@ -1339,7 +1294,7 @@
       <c r="AP2" s="4"/>
       <c r="AQ2" s="4"/>
     </row>
-    <row r="3" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -1416,7 +1371,7 @@
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
     </row>
-    <row r="4" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>39</v>
@@ -1479,12 +1434,8 @@
       <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
-      <c r="AE4" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF4" s="3" t="s">
-        <v>170</v>
-      </c>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
@@ -1497,7 +1448,7 @@
       <c r="AP4" s="4"/>
       <c r="AQ4" s="4"/>
     </row>
-    <row r="5" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>39</v>
@@ -1506,7 +1457,7 @@
         <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>56</v>
@@ -1540,7 +1491,7 @@
         <v>96</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>48</v>
@@ -1560,12 +1511,8 @@
       <c r="AB5" s="3"/>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
-      <c r="AE5" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF5" s="3" t="s">
-        <v>170</v>
-      </c>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
       <c r="AI5" s="3"/>
@@ -1578,7 +1525,7 @@
       <c r="AP5" s="4"/>
       <c r="AQ5" s="4"/>
     </row>
-    <row r="6" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -1655,7 +1602,7 @@
       <c r="AP6" s="4"/>
       <c r="AQ6" s="4"/>
     </row>
-    <row r="7" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -1698,7 +1645,7 @@
         <v>96</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S7" s="3" t="s">
         <v>48</v>
@@ -1718,12 +1665,8 @@
       <c r="AB7" s="3"/>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
-      <c r="AE7" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF7" s="3" t="s">
-        <v>170</v>
-      </c>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
       <c r="AI7" s="3"/>
@@ -1736,7 +1679,7 @@
       <c r="AP7" s="4"/>
       <c r="AQ7" s="4"/>
     </row>
-    <row r="8" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -1813,7 +1756,7 @@
       <c r="AP8" s="4"/>
       <c r="AQ8" s="4"/>
     </row>
-    <row r="9" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -1856,7 +1799,7 @@
         <v>96</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>48</v>
@@ -1876,12 +1819,8 @@
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
-      <c r="AE9" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF9" s="3" t="s">
-        <v>170</v>
-      </c>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
       <c r="AI9" s="3"/>
@@ -1894,7 +1833,7 @@
       <c r="AP9" s="4"/>
       <c r="AQ9" s="4"/>
     </row>
-    <row r="10" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -1971,7 +1910,7 @@
       <c r="AP10" s="4"/>
       <c r="AQ10" s="4"/>
     </row>
-    <row r="11" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -2014,7 +1953,7 @@
         <v>96</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S11" s="3" t="s">
         <v>48</v>
@@ -2034,12 +1973,8 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-      <c r="AE11" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF11" s="3" t="s">
-        <v>170</v>
-      </c>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
@@ -2052,7 +1987,7 @@
       <c r="AP11" s="4"/>
       <c r="AQ11" s="4"/>
     </row>
-    <row r="12" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>39</v>
@@ -2137,7 +2072,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -2164,7 +2099,7 @@
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>45</v>
@@ -2211,7 +2146,7 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
       <c r="AM13" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="AN13" s="4">
         <v>5.7700000000000001E-2</v>
@@ -2241,7 +2176,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -2268,7 +2203,7 @@
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>45</v>
@@ -2306,7 +2241,7 @@
         <v>66</v>
       </c>
       <c r="AF14" s="3" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
@@ -2315,7 +2250,7 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
       <c r="AM14" s="3" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="AN14" s="4">
         <v>5.7700000000000001E-2</v>
@@ -2345,7 +2280,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -2408,7 +2343,7 @@
         <v>64</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="AG15" s="3"/>
       <c r="AH15" s="3"/>
@@ -2430,7 +2365,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:50" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -2469,7 +2404,7 @@
         <v>30</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>48</v>
@@ -2502,7 +2437,7 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="AN16" s="4">
         <v>5.7700000000000001E-2</v>
@@ -2532,7 +2467,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -2571,7 +2506,7 @@
         <v>30</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>48</v>
@@ -2595,7 +2530,7 @@
         <v>66</v>
       </c>
       <c r="AF17" s="3" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="AG17" s="3"/>
       <c r="AH17" s="3"/>
@@ -2604,7 +2539,7 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
       <c r="AM17" s="3" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="AN17" s="4">
         <v>5.7700000000000001E-2</v>
@@ -2634,19 +2569,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>62</v>
@@ -2673,7 +2608,7 @@
         <v>30</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>48</v>
@@ -2707,19 +2642,19 @@
       <c r="AP18" s="4"/>
       <c r="AQ18" s="4"/>
     </row>
-    <row r="19" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>62</v>
@@ -2746,16 +2681,16 @@
         <v>30</v>
       </c>
       <c r="R19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T19" s="3">
+        <v>1</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T19" s="3">
-        <v>1</v>
-      </c>
-      <c r="U19" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2780,19 +2715,19 @@
       <c r="AP19" s="4"/>
       <c r="AQ19" s="4"/>
     </row>
-    <row r="20" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>62</v>
@@ -2819,16 +2754,16 @@
         <v>30</v>
       </c>
       <c r="R20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T20" s="3">
+        <v>1</v>
+      </c>
+      <c r="U20" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T20" s="3">
-        <v>1</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2852,7 +2787,7 @@
       <c r="AP20" s="4"/>
       <c r="AQ20" s="4"/>
     </row>
-    <row r="21" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -2927,7 +2862,7 @@
       <c r="AP21" s="4"/>
       <c r="AQ21" s="4"/>
     </row>
-    <row r="22" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -3002,7 +2937,7 @@
       <c r="AP22" s="4"/>
       <c r="AQ22" s="4"/>
     </row>
-    <row r="23" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -3011,7 +2946,7 @@
         <v>68</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>69</v>
@@ -3027,7 +2962,7 @@
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>57</v>
@@ -3043,7 +2978,7 @@
         <v>30</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>48</v>
@@ -3077,7 +3012,7 @@
       <c r="AP23" s="4"/>
       <c r="AQ23" s="4"/>
     </row>
-    <row r="24" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -3086,7 +3021,7 @@
         <v>68</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>69</v>
@@ -3152,7 +3087,7 @@
       <c r="AP24" s="4"/>
       <c r="AQ24" s="4"/>
     </row>
-    <row r="25" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -3161,7 +3096,7 @@
         <v>68</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>69</v>
@@ -3227,7 +3162,7 @@
       <c r="AP25" s="4"/>
       <c r="AQ25" s="4"/>
     </row>
-    <row r="26" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -3236,7 +3171,7 @@
         <v>68</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>69</v>
@@ -3266,16 +3201,16 @@
         <v>30</v>
       </c>
       <c r="R26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T26" s="3">
+        <v>1</v>
+      </c>
+      <c r="U26" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T26" s="3">
-        <v>1</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -3300,7 +3235,7 @@
       <c r="AP26" s="4"/>
       <c r="AQ26" s="4"/>
     </row>
-    <row r="27" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -3375,7 +3310,7 @@
       <c r="AP27" s="4"/>
       <c r="AQ27" s="4"/>
     </row>
-    <row r="28" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -3416,7 +3351,7 @@
         <v>96</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>48</v>
@@ -3450,7 +3385,7 @@
       <c r="AP28" s="4"/>
       <c r="AQ28" s="4"/>
     </row>
-    <row r="29" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -3525,7 +3460,7 @@
       <c r="AP29" s="4"/>
       <c r="AQ29" s="4"/>
     </row>
-    <row r="30" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>39</v>
@@ -3566,7 +3501,7 @@
         <v>96</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S30" s="3" t="s">
         <v>48</v>
@@ -3600,7 +3535,7 @@
       <c r="AP30" s="4"/>
       <c r="AQ30" s="4"/>
     </row>
-    <row r="31" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>39</v>
@@ -3675,7 +3610,7 @@
       <c r="AP31" s="4"/>
       <c r="AQ31" s="4"/>
     </row>
-    <row r="32" spans="1:48" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>39</v>
@@ -3716,7 +3651,7 @@
         <v>96</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>48</v>
@@ -3750,7 +3685,7 @@
       <c r="AP32" s="4"/>
       <c r="AQ32" s="4"/>
     </row>
-    <row r="33" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>39</v>
@@ -3759,7 +3694,7 @@
         <v>68</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>69</v>
@@ -3789,16 +3724,16 @@
         <v>30</v>
       </c>
       <c r="R33" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T33" s="3">
+        <v>1</v>
+      </c>
+      <c r="U33" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T33" s="3">
-        <v>1</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3823,19 +3758,19 @@
       <c r="AP33" s="4"/>
       <c r="AQ33" s="4"/>
     </row>
-    <row r="34" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>62</v>
@@ -3862,7 +3797,7 @@
         <v>30</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S34" s="3" t="s">
         <v>48</v>
@@ -3896,19 +3831,19 @@
       <c r="AP34" s="4"/>
       <c r="AQ34" s="4"/>
     </row>
-    <row r="35" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>62</v>
@@ -3935,7 +3870,7 @@
         <v>30</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>48</v>
@@ -3969,19 +3904,19 @@
       <c r="AP35" s="4"/>
       <c r="AQ35" s="4"/>
     </row>
-    <row r="36" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
@@ -4000,13 +3935,13 @@
         <v>0.01</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q36" s="3">
         <v>30</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S36" s="3" t="s">
         <v>48</v>
@@ -4040,7 +3975,7 @@
       <c r="AP36" s="4"/>
       <c r="AQ36" s="4"/>
     </row>
-    <row r="37" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>39</v>
@@ -4103,7 +4038,7 @@
         <v>50</v>
       </c>
       <c r="AF37" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="AG37" s="3"/>
       <c r="AH37" s="3"/>
@@ -4124,7 +4059,7 @@
       <c r="AP37" s="4"/>
       <c r="AQ37" s="4"/>
     </row>
-    <row r="38" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>39</v>
@@ -4187,7 +4122,7 @@
         <v>50</v>
       </c>
       <c r="AF38" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="AG38" s="3"/>
       <c r="AH38" s="3"/>
@@ -4208,7 +4143,7 @@
       <c r="AP38" s="4"/>
       <c r="AQ38" s="4"/>
     </row>
-    <row r="39" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>39</v>
@@ -4217,7 +4152,7 @@
         <v>70</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>71</v>
@@ -4247,7 +4182,7 @@
         <v>30</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S39" s="3" t="s">
         <v>48</v>
@@ -4280,7 +4215,7 @@
       <c r="AP39" s="4"/>
       <c r="AQ39" s="4"/>
     </row>
-    <row r="40" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>39</v>
@@ -4289,7 +4224,7 @@
         <v>70</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>71</v>
@@ -4343,7 +4278,7 @@
         <v>50</v>
       </c>
       <c r="AF40" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
@@ -4364,7 +4299,7 @@
       <c r="AP40" s="4"/>
       <c r="AQ40" s="4"/>
     </row>
-    <row r="41" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>39</v>
@@ -4373,7 +4308,7 @@
         <v>70</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>71</v>
@@ -4427,7 +4362,7 @@
         <v>50</v>
       </c>
       <c r="AF41" s="3" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="AG41" s="3"/>
       <c r="AH41" s="3"/>
@@ -4448,7 +4383,7 @@
       <c r="AP41" s="4"/>
       <c r="AQ41" s="4"/>
     </row>
-    <row r="42" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>39</v>
@@ -4511,7 +4446,7 @@
         <v>50</v>
       </c>
       <c r="AF42" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="AG42" s="3"/>
       <c r="AH42" s="3"/>
@@ -4532,7 +4467,7 @@
       <c r="AP42" s="4"/>
       <c r="AQ42" s="4"/>
     </row>
-    <row r="43" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>39</v>
@@ -4571,7 +4506,7 @@
         <v>96</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>48</v>
@@ -4595,7 +4530,7 @@
         <v>50</v>
       </c>
       <c r="AF43" s="3" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="AG43" s="3"/>
       <c r="AH43" s="3"/>
@@ -4616,7 +4551,7 @@
       <c r="AP43" s="4"/>
       <c r="AQ43" s="4"/>
     </row>
-    <row r="44" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>39</v>
@@ -4679,7 +4614,7 @@
         <v>50</v>
       </c>
       <c r="AF44" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="AG44" s="3"/>
       <c r="AH44" s="3"/>
@@ -4700,7 +4635,7 @@
       <c r="AP44" s="4"/>
       <c r="AQ44" s="4"/>
     </row>
-    <row r="45" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>39</v>
@@ -4739,7 +4674,7 @@
         <v>96</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>48</v>
@@ -4763,7 +4698,7 @@
         <v>50</v>
       </c>
       <c r="AF45" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="AG45" s="3"/>
       <c r="AH45" s="3"/>
@@ -4784,7 +4719,7 @@
       <c r="AP45" s="4"/>
       <c r="AQ45" s="4"/>
     </row>
-    <row r="46" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>39</v>
@@ -4847,7 +4782,7 @@
         <v>50</v>
       </c>
       <c r="AF46" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="AG46" s="3"/>
       <c r="AH46" s="3"/>
@@ -4868,7 +4803,7 @@
       <c r="AP46" s="4"/>
       <c r="AQ46" s="4"/>
     </row>
-    <row r="47" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>39</v>
@@ -4907,7 +4842,7 @@
         <v>96</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>48</v>
@@ -4931,7 +4866,7 @@
         <v>50</v>
       </c>
       <c r="AF47" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="AG47" s="3"/>
       <c r="AH47" s="3"/>
@@ -4952,7 +4887,7 @@
       <c r="AP47" s="4"/>
       <c r="AQ47" s="4"/>
     </row>
-    <row r="48" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>39</v>
@@ -4979,7 +4914,7 @@
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>57</v>
@@ -5015,12 +4950,8 @@
       <c r="AB48" s="3"/>
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
-      <c r="AE48" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF48" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="AE48" s="3"/>
+      <c r="AF48" s="3"/>
       <c r="AG48" s="3"/>
       <c r="AH48" s="3"/>
       <c r="AI48" s="3"/>
@@ -5033,7 +4964,7 @@
       <c r="AP48" s="4"/>
       <c r="AQ48" s="4"/>
     </row>
-    <row r="49" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>39</v>
@@ -5060,7 +4991,7 @@
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>57</v>
@@ -5096,12 +5027,8 @@
       <c r="AB49" s="3"/>
       <c r="AC49" s="3"/>
       <c r="AD49" s="3"/>
-      <c r="AE49" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF49" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="AE49" s="3"/>
+      <c r="AF49" s="3"/>
       <c r="AG49" s="3"/>
       <c r="AH49" s="3"/>
       <c r="AI49" s="3"/>
@@ -5114,7 +5041,7 @@
       <c r="AP49" s="4"/>
       <c r="AQ49" s="4"/>
     </row>
-    <row r="50" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>39</v>
@@ -5141,7 +5068,7 @@
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="M50" s="3" t="s">
         <v>57</v>
@@ -5177,12 +5104,8 @@
       <c r="AB50" s="3"/>
       <c r="AC50" s="3"/>
       <c r="AD50" s="3"/>
-      <c r="AE50" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF50" s="3" t="s">
-        <v>175</v>
-      </c>
+      <c r="AE50" s="3"/>
+      <c r="AF50" s="3"/>
       <c r="AG50" s="3"/>
       <c r="AH50" s="3"/>
       <c r="AI50" s="3"/>
@@ -5195,7 +5118,7 @@
       <c r="AP50" s="4"/>
       <c r="AQ50" s="4"/>
     </row>
-    <row r="51" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>39</v>
@@ -5222,7 +5145,7 @@
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="M51" s="3" t="s">
         <v>57</v>
@@ -5238,7 +5161,7 @@
         <v>96</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S51" s="3" t="s">
         <v>48</v>
@@ -5258,12 +5181,8 @@
       <c r="AB51" s="3"/>
       <c r="AC51" s="3"/>
       <c r="AD51" s="3"/>
-      <c r="AE51" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF51" s="3" t="s">
-        <v>175</v>
-      </c>
+      <c r="AE51" s="3"/>
+      <c r="AF51" s="3"/>
       <c r="AG51" s="3"/>
       <c r="AH51" s="3"/>
       <c r="AI51" s="3"/>
@@ -5276,7 +5195,7 @@
       <c r="AP51" s="4"/>
       <c r="AQ51" s="4"/>
     </row>
-    <row r="52" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>39</v>
@@ -5303,7 +5222,7 @@
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>57</v>
@@ -5339,12 +5258,8 @@
       <c r="AB52" s="3"/>
       <c r="AC52" s="3"/>
       <c r="AD52" s="3"/>
-      <c r="AE52" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF52" s="3" t="s">
-        <v>176</v>
-      </c>
+      <c r="AE52" s="3"/>
+      <c r="AF52" s="3"/>
       <c r="AG52" s="3"/>
       <c r="AH52" s="3"/>
       <c r="AI52" s="3"/>
@@ -5357,7 +5272,7 @@
       <c r="AP52" s="4"/>
       <c r="AQ52" s="4"/>
     </row>
-    <row r="53" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>39</v>
@@ -5384,7 +5299,7 @@
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="M53" s="3" t="s">
         <v>57</v>
@@ -5400,7 +5315,7 @@
         <v>96</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S53" s="3" t="s">
         <v>48</v>
@@ -5420,12 +5335,8 @@
       <c r="AB53" s="3"/>
       <c r="AC53" s="3"/>
       <c r="AD53" s="3"/>
-      <c r="AE53" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF53" s="3" t="s">
-        <v>176</v>
-      </c>
+      <c r="AE53" s="3"/>
+      <c r="AF53" s="3"/>
       <c r="AG53" s="3"/>
       <c r="AH53" s="3"/>
       <c r="AI53" s="3"/>
@@ -5438,13 +5349,13 @@
       <c r="AP53" s="4"/>
       <c r="AQ53" s="4"/>
     </row>
-    <row r="54" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>40</v>
@@ -5501,7 +5412,7 @@
         <v>50</v>
       </c>
       <c r="AF54" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="AG54" s="3"/>
       <c r="AH54" s="3"/>
@@ -5520,13 +5431,13 @@
       <c r="AP54" s="4"/>
       <c r="AQ54" s="4"/>
     </row>
-    <row r="55" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>51</v>
@@ -5583,7 +5494,7 @@
         <v>50</v>
       </c>
       <c r="AF55" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
@@ -5602,13 +5513,13 @@
       <c r="AP55" s="4"/>
       <c r="AQ55" s="4"/>
     </row>
-    <row r="56" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>52</v>
@@ -5665,7 +5576,7 @@
         <v>50</v>
       </c>
       <c r="AF56" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
@@ -5684,13 +5595,13 @@
       <c r="AP56" s="4"/>
       <c r="AQ56" s="4"/>
     </row>
-    <row r="57" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>53</v>
@@ -5747,7 +5658,7 @@
         <v>50</v>
       </c>
       <c r="AF57" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="AG57" s="3"/>
       <c r="AH57" s="3"/>
@@ -5766,16 +5677,16 @@
       <c r="AP57" s="4"/>
       <c r="AQ57" s="4"/>
     </row>
-    <row r="58" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>41</v>
@@ -5829,7 +5740,7 @@
         <v>50</v>
       </c>
       <c r="AF58" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="AG58" s="3"/>
       <c r="AH58" s="3"/>
@@ -5848,16 +5759,16 @@
       <c r="AP58" s="4"/>
       <c r="AQ58" s="4"/>
     </row>
-    <row r="59" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>41</v>
@@ -5911,7 +5822,7 @@
         <v>50</v>
       </c>
       <c r="AF59" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="AG59" s="3"/>
       <c r="AH59" s="3"/>
@@ -5930,13 +5841,13 @@
       <c r="AP59" s="4"/>
       <c r="AQ59" s="4"/>
     </row>
-    <row r="60" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>40</v>
@@ -5993,7 +5904,7 @@
         <v>50</v>
       </c>
       <c r="AF60" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="AG60" s="3"/>
       <c r="AH60" s="3"/>
@@ -6012,13 +5923,13 @@
       <c r="AP60" s="4"/>
       <c r="AQ60" s="4"/>
     </row>
-    <row r="61" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>51</v>
@@ -6075,7 +5986,7 @@
         <v>50</v>
       </c>
       <c r="AF61" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="AG61" s="3"/>
       <c r="AH61" s="3"/>
@@ -6094,13 +6005,13 @@
       <c r="AP61" s="4"/>
       <c r="AQ61" s="4"/>
     </row>
-    <row r="62" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>52</v>
@@ -6157,7 +6068,7 @@
         <v>50</v>
       </c>
       <c r="AF62" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="AG62" s="3"/>
       <c r="AH62" s="3"/>
@@ -6176,13 +6087,13 @@
       <c r="AP62" s="4"/>
       <c r="AQ62" s="4"/>
     </row>
-    <row r="63" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>53</v>
@@ -6239,7 +6150,7 @@
         <v>50</v>
       </c>
       <c r="AF63" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="AG63" s="3"/>
       <c r="AH63" s="3"/>
@@ -6258,16 +6169,16 @@
       <c r="AP63" s="4"/>
       <c r="AQ63" s="4"/>
     </row>
-    <row r="64" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>41</v>
@@ -6297,16 +6208,16 @@
         <v>30</v>
       </c>
       <c r="R64" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T64" s="3">
+        <v>1</v>
+      </c>
+      <c r="U64" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S64" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T64" s="3">
-        <v>1</v>
-      </c>
-      <c r="U64" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3"/>
@@ -6331,19 +6242,19 @@
       <c r="AP64" s="4"/>
       <c r="AQ64" s="4"/>
     </row>
-    <row r="65" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>42</v>
@@ -6406,19 +6317,19 @@
       <c r="AP65" s="4"/>
       <c r="AQ65" s="4"/>
     </row>
-    <row r="66" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>42</v>
@@ -6481,19 +6392,19 @@
       <c r="AP66" s="4"/>
       <c r="AQ66" s="4"/>
     </row>
-    <row r="67" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>62</v>
@@ -6520,7 +6431,7 @@
         <v>30</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S67" s="3" t="s">
         <v>48</v>
@@ -6554,19 +6465,19 @@
       <c r="AP67" s="4"/>
       <c r="AQ67" s="4"/>
     </row>
-    <row r="68" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="E68" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>42</v>
@@ -6629,19 +6540,19 @@
       <c r="AP68" s="4"/>
       <c r="AQ68" s="4"/>
     </row>
-    <row r="69" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="E69" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>42</v>
@@ -6704,19 +6615,19 @@
       <c r="AP69" s="4"/>
       <c r="AQ69" s="4"/>
     </row>
-    <row r="70" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>42</v>
@@ -6779,19 +6690,19 @@
       <c r="AP70" s="4"/>
       <c r="AQ70" s="4"/>
     </row>
-    <row r="71" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>42</v>
@@ -6820,7 +6731,7 @@
         <v>96</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S71" s="3" t="s">
         <v>48</v>
@@ -6854,19 +6765,19 @@
       <c r="AP71" s="4"/>
       <c r="AQ71" s="4"/>
     </row>
-    <row r="72" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>42</v>
@@ -6929,19 +6840,19 @@
       <c r="AP72" s="4"/>
       <c r="AQ72" s="4"/>
     </row>
-    <row r="73" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
       <c r="B73" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>42</v>
@@ -6970,7 +6881,7 @@
         <v>96</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S73" s="3" t="s">
         <v>48</v>
@@ -7004,19 +6915,19 @@
       <c r="AP73" s="4"/>
       <c r="AQ73" s="4"/>
     </row>
-    <row r="74" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>42</v>
@@ -7079,19 +6990,19 @@
       <c r="AP74" s="4"/>
       <c r="AQ74" s="4"/>
     </row>
-    <row r="75" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>42</v>
@@ -7120,7 +7031,7 @@
         <v>96</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S75" s="3" t="s">
         <v>48</v>
@@ -7154,19 +7065,19 @@
       <c r="AP75" s="4"/>
       <c r="AQ75" s="4"/>
     </row>
-    <row r="76" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>42</v>
@@ -7217,7 +7128,7 @@
         <v>50</v>
       </c>
       <c r="AF76" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="AG76" s="3"/>
       <c r="AH76" s="3"/>
@@ -7236,19 +7147,19 @@
       <c r="AP76" s="4"/>
       <c r="AQ76" s="4"/>
     </row>
-    <row r="77" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>42</v>
@@ -7299,7 +7210,7 @@
         <v>50</v>
       </c>
       <c r="AF77" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG77" s="3"/>
       <c r="AH77" s="3"/>
@@ -7318,19 +7229,19 @@
       <c r="AP77" s="4"/>
       <c r="AQ77" s="4"/>
     </row>
-    <row r="78" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>62</v>
@@ -7357,7 +7268,7 @@
         <v>30</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S78" s="3" t="s">
         <v>48</v>
@@ -7390,19 +7301,19 @@
       <c r="AP78" s="4"/>
       <c r="AQ78" s="4"/>
     </row>
-    <row r="79" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
       <c r="B79" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C79" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>42</v>
@@ -7453,7 +7364,7 @@
         <v>50</v>
       </c>
       <c r="AF79" s="3" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="AG79" s="3"/>
       <c r="AH79" s="3"/>
@@ -7472,19 +7383,19 @@
       <c r="AP79" s="4"/>
       <c r="AQ79" s="4"/>
     </row>
-    <row r="80" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
       <c r="B80" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C80" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>42</v>
@@ -7535,7 +7446,7 @@
         <v>50</v>
       </c>
       <c r="AF80" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="AG80" s="3"/>
       <c r="AH80" s="3"/>
@@ -7554,19 +7465,19 @@
       <c r="AP80" s="4"/>
       <c r="AQ80" s="4"/>
     </row>
-    <row r="81" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
       <c r="B81" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>42</v>
@@ -7617,7 +7528,7 @@
         <v>50</v>
       </c>
       <c r="AF81" s="3" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="AG81" s="3"/>
       <c r="AH81" s="3"/>
@@ -7636,19 +7547,19 @@
       <c r="AP81" s="4"/>
       <c r="AQ81" s="4"/>
     </row>
-    <row r="82" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>42</v>
@@ -7675,7 +7586,7 @@
         <v>96</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S82" s="3" t="s">
         <v>48</v>
@@ -7699,7 +7610,7 @@
         <v>50</v>
       </c>
       <c r="AF82" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
@@ -7718,19 +7629,19 @@
       <c r="AP82" s="4"/>
       <c r="AQ82" s="4"/>
     </row>
-    <row r="83" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>42</v>
@@ -7781,7 +7692,7 @@
         <v>50</v>
       </c>
       <c r="AF83" s="3" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="AG83" s="3"/>
       <c r="AH83" s="3"/>
@@ -7800,19 +7711,19 @@
       <c r="AP83" s="4"/>
       <c r="AQ83" s="4"/>
     </row>
-    <row r="84" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>42</v>
@@ -7839,7 +7750,7 @@
         <v>96</v>
       </c>
       <c r="R84" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S84" s="3" t="s">
         <v>48</v>
@@ -7863,7 +7774,7 @@
         <v>50</v>
       </c>
       <c r="AF84" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="AG84" s="3"/>
       <c r="AH84" s="3"/>
@@ -7882,19 +7793,19 @@
       <c r="AP84" s="4"/>
       <c r="AQ84" s="4"/>
     </row>
-    <row r="85" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
       <c r="B85" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>42</v>
@@ -7945,7 +7856,7 @@
         <v>50</v>
       </c>
       <c r="AF85" s="3" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="AG85" s="3"/>
       <c r="AH85" s="3"/>
@@ -7964,19 +7875,19 @@
       <c r="AP85" s="4"/>
       <c r="AQ85" s="4"/>
     </row>
-    <row r="86" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>42</v>
@@ -8003,7 +7914,7 @@
         <v>96</v>
       </c>
       <c r="R86" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S86" s="3" t="s">
         <v>48</v>
@@ -8027,7 +7938,7 @@
         <v>50</v>
       </c>
       <c r="AF86" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="AG86" s="3"/>
       <c r="AH86" s="3"/>
@@ -8046,19 +7957,19 @@
       <c r="AP86" s="4"/>
       <c r="AQ86" s="4"/>
     </row>
-    <row r="87" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>42</v>
@@ -8071,7 +7982,7 @@
       </c>
       <c r="K87" s="3"/>
       <c r="L87" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M87" s="3" t="s">
         <v>57</v>
@@ -8087,7 +7998,7 @@
         <v>30</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S87" s="3" t="s">
         <v>48</v>
@@ -8121,19 +8032,19 @@
       <c r="AP87" s="4"/>
       <c r="AQ87" s="4"/>
     </row>
-    <row r="88" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>42</v>
@@ -8146,7 +8057,7 @@
       </c>
       <c r="K88" s="3"/>
       <c r="L88" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="M88" s="3" t="s">
         <v>57</v>
@@ -8162,7 +8073,7 @@
         <v>7</v>
       </c>
       <c r="R88" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S88" s="3" t="s">
         <v>48</v>
@@ -8182,12 +8093,8 @@
       <c r="AB88" s="3"/>
       <c r="AC88" s="3"/>
       <c r="AD88" s="3"/>
-      <c r="AE88" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF88" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="AE88" s="3"/>
+      <c r="AF88" s="3"/>
       <c r="AG88" s="3"/>
       <c r="AH88" s="3"/>
       <c r="AI88" s="3"/>
@@ -8200,19 +8107,19 @@
       <c r="AP88" s="4"/>
       <c r="AQ88" s="4"/>
     </row>
-    <row r="89" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
       <c r="B89" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>42</v>
@@ -8225,7 +8132,7 @@
       </c>
       <c r="K89" s="3"/>
       <c r="L89" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>57</v>
@@ -8241,7 +8148,7 @@
         <v>7</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>48</v>
@@ -8261,12 +8168,8 @@
       <c r="AB89" s="3"/>
       <c r="AC89" s="3"/>
       <c r="AD89" s="3"/>
-      <c r="AE89" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF89" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="AE89" s="3"/>
+      <c r="AF89" s="3"/>
       <c r="AG89" s="3"/>
       <c r="AH89" s="3"/>
       <c r="AI89" s="3"/>
@@ -8279,19 +8182,19 @@
       <c r="AP89" s="4"/>
       <c r="AQ89" s="4"/>
     </row>
-    <row r="90" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>42</v>
@@ -8304,7 +8207,7 @@
       </c>
       <c r="K90" s="3"/>
       <c r="L90" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="M90" s="3" t="s">
         <v>57</v>
@@ -8320,10 +8223,10 @@
         <v>1</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S90" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T90" s="3">
         <v>1</v>
@@ -8340,12 +8243,8 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-      <c r="AE90" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF90" s="3" t="s">
-        <v>173</v>
-      </c>
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
@@ -8358,19 +8257,19 @@
       <c r="AP90" s="4"/>
       <c r="AQ90" s="4"/>
     </row>
-    <row r="91" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>42</v>
@@ -8383,7 +8282,7 @@
       </c>
       <c r="K91" s="3"/>
       <c r="L91" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>57</v>
@@ -8399,10 +8298,10 @@
         <v>1</v>
       </c>
       <c r="R91" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S91" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T91" s="3">
         <v>1</v>
@@ -8419,12 +8318,8 @@
       <c r="AB91" s="3"/>
       <c r="AC91" s="3"/>
       <c r="AD91" s="3"/>
-      <c r="AE91" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF91" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="AE91" s="3"/>
+      <c r="AF91" s="3"/>
       <c r="AG91" s="3"/>
       <c r="AH91" s="3"/>
       <c r="AI91" s="3"/>
@@ -8437,19 +8332,19 @@
       <c r="AP91" s="4"/>
       <c r="AQ91" s="4"/>
     </row>
-    <row r="92" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>42</v>
@@ -8462,7 +8357,7 @@
       </c>
       <c r="K92" s="3"/>
       <c r="L92" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M92" s="3" t="s">
         <v>57</v>
@@ -8478,7 +8373,7 @@
         <v>30</v>
       </c>
       <c r="R92" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S92" s="3" t="s">
         <v>48</v>
@@ -8498,12 +8393,8 @@
       <c r="AB92" s="3"/>
       <c r="AC92" s="3"/>
       <c r="AD92" s="3"/>
-      <c r="AE92" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF92" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="AE92" s="3"/>
+      <c r="AF92" s="3"/>
       <c r="AG92" s="3"/>
       <c r="AH92" s="3"/>
       <c r="AI92" s="3"/>
@@ -8516,19 +8407,19 @@
       <c r="AP92" s="4"/>
       <c r="AQ92" s="4"/>
     </row>
-    <row r="93" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
       <c r="B93" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>42</v>
@@ -8541,7 +8432,7 @@
       </c>
       <c r="K93" s="3"/>
       <c r="L93" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="M93" s="3" t="s">
         <v>57</v>
@@ -8557,7 +8448,7 @@
         <v>7</v>
       </c>
       <c r="R93" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S93" s="3" t="s">
         <v>48</v>
@@ -8577,12 +8468,8 @@
       <c r="AB93" s="3"/>
       <c r="AC93" s="3"/>
       <c r="AD93" s="3"/>
-      <c r="AE93" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF93" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="AE93" s="3"/>
+      <c r="AF93" s="3"/>
       <c r="AG93" s="3"/>
       <c r="AH93" s="3"/>
       <c r="AI93" s="3"/>
@@ -8595,19 +8482,19 @@
       <c r="AP93" s="4"/>
       <c r="AQ93" s="4"/>
     </row>
-    <row r="94" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>42</v>
@@ -8620,7 +8507,7 @@
       </c>
       <c r="K94" s="3"/>
       <c r="L94" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>57</v>
@@ -8636,7 +8523,7 @@
         <v>7</v>
       </c>
       <c r="R94" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>48</v>
@@ -8656,12 +8543,8 @@
       <c r="AB94" s="3"/>
       <c r="AC94" s="3"/>
       <c r="AD94" s="3"/>
-      <c r="AE94" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF94" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="AE94" s="3"/>
+      <c r="AF94" s="3"/>
       <c r="AG94" s="3"/>
       <c r="AH94" s="3"/>
       <c r="AI94" s="3"/>
@@ -8674,19 +8557,19 @@
       <c r="AP94" s="4"/>
       <c r="AQ94" s="4"/>
     </row>
-    <row r="95" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>42</v>
@@ -8699,7 +8582,7 @@
       </c>
       <c r="K95" s="3"/>
       <c r="L95" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="M95" s="3" t="s">
         <v>57</v>
@@ -8715,10 +8598,10 @@
         <v>1</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S95" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T95" s="3">
         <v>1</v>
@@ -8735,12 +8618,8 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-      <c r="AE95" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF95" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
@@ -8753,19 +8632,19 @@
       <c r="AP95" s="4"/>
       <c r="AQ95" s="4"/>
     </row>
-    <row r="96" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>42</v>
@@ -8778,7 +8657,7 @@
       </c>
       <c r="K96" s="3"/>
       <c r="L96" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>57</v>
@@ -8794,16 +8673,16 @@
         <v>1</v>
       </c>
       <c r="R96" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S96" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="T96" s="3">
+        <v>1</v>
+      </c>
+      <c r="U96" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S96" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="T96" s="3">
-        <v>1</v>
-      </c>
-      <c r="U96" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V96" s="3"/>
       <c r="W96" s="3"/>
@@ -8814,12 +8693,8 @@
       <c r="AB96" s="3"/>
       <c r="AC96" s="3"/>
       <c r="AD96" s="3"/>
-      <c r="AE96" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF96" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="AE96" s="3"/>
+      <c r="AF96" s="3"/>
       <c r="AG96" s="3"/>
       <c r="AH96" s="3"/>
       <c r="AI96" s="3"/>
@@ -8832,19 +8707,19 @@
       <c r="AP96" s="4"/>
       <c r="AQ96" s="4"/>
     </row>
-    <row r="97" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
@@ -8855,7 +8730,7 @@
       </c>
       <c r="K97" s="3"/>
       <c r="L97" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="M97" s="3" t="s">
         <v>57</v>
@@ -8865,44 +8740,40 @@
         <v>126</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="Q97" s="3">
         <v>60</v>
       </c>
       <c r="R97" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S97" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="T97" s="3">
+        <v>1</v>
+      </c>
+      <c r="U97" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S97" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="T97" s="3">
-        <v>1</v>
-      </c>
-      <c r="U97" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V97" s="3"/>
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
       <c r="Y97" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="Z97" s="5" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="AA97" s="5" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="AB97" s="3"/>
       <c r="AC97" s="3"/>
       <c r="AD97" s="3"/>
-      <c r="AE97" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF97" s="3" t="s">
-        <v>130</v>
-      </c>
+      <c r="AE97" s="3"/>
+      <c r="AF97" s="3"/>
       <c r="AG97" s="3"/>
       <c r="AH97" s="3"/>
       <c r="AI97" s="3"/>
@@ -8915,19 +8786,19 @@
       <c r="AP97" s="4"/>
       <c r="AQ97" s="4"/>
     </row>
-    <row r="98" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
@@ -8946,22 +8817,22 @@
         <v>630</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="Q98" s="3">
         <v>60</v>
       </c>
       <c r="R98" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S98" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="T98" s="3">
+        <v>1</v>
+      </c>
+      <c r="U98" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S98" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="T98" s="3">
-        <v>1</v>
-      </c>
-      <c r="U98" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V98" s="3"/>
       <c r="W98" s="3"/>
@@ -8986,19 +8857,19 @@
       <c r="AP98" s="4"/>
       <c r="AQ98" s="4"/>
     </row>
-    <row r="99" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C99" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="E99" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>42</v>
@@ -9025,16 +8896,16 @@
         <v>30</v>
       </c>
       <c r="R99" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S99" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T99" s="3">
+        <v>1</v>
+      </c>
+      <c r="U99" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S99" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T99" s="3">
-        <v>1</v>
-      </c>
-      <c r="U99" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V99" s="3"/>
       <c r="W99" s="3"/>
@@ -9059,19 +8930,19 @@
       <c r="AP99" s="4"/>
       <c r="AQ99" s="4"/>
     </row>
-    <row r="100" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
@@ -9090,13 +8961,13 @@
         <v>15</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q100" s="3">
         <v>30</v>
       </c>
       <c r="R100" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>48</v>
@@ -9130,19 +9001,19 @@
       <c r="AP100" s="4"/>
       <c r="AQ100" s="4"/>
     </row>
-    <row r="101" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>42</v>
@@ -9205,19 +9076,19 @@
       <c r="AP101" s="4"/>
       <c r="AQ101" s="4"/>
     </row>
-    <row r="102" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C102" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E102" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>42</v>
@@ -9244,7 +9115,7 @@
         <v>30</v>
       </c>
       <c r="R102" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>48</v>
@@ -9264,12 +9135,8 @@
       <c r="AB102" s="3"/>
       <c r="AC102" s="3"/>
       <c r="AD102" s="3"/>
-      <c r="AE102" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF102" s="3" t="s">
-        <v>167</v>
-      </c>
+      <c r="AE102" s="3"/>
+      <c r="AF102" s="3"/>
       <c r="AG102" s="3"/>
       <c r="AH102" s="3"/>
       <c r="AI102" s="3"/>
@@ -9282,19 +9149,19 @@
       <c r="AP102" s="4"/>
       <c r="AQ102" s="4"/>
     </row>
-    <row r="103" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C103" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E103" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>42</v>
@@ -9357,19 +9224,19 @@
       <c r="AP103" s="4"/>
       <c r="AQ103" s="4"/>
     </row>
-    <row r="104" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>42</v>
@@ -9398,7 +9265,7 @@
         <v>96</v>
       </c>
       <c r="R104" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S104" s="3" t="s">
         <v>48</v>
@@ -9432,19 +9299,19 @@
       <c r="AP104" s="4"/>
       <c r="AQ104" s="4"/>
     </row>
-    <row r="105" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>42</v>
@@ -9473,7 +9340,7 @@
         <v>96</v>
       </c>
       <c r="R105" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S105" s="3" t="s">
         <v>48</v>
@@ -9507,19 +9374,19 @@
       <c r="AP105" s="4"/>
       <c r="AQ105" s="4"/>
     </row>
-    <row r="106" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>42</v>
@@ -9548,7 +9415,7 @@
         <v>96</v>
       </c>
       <c r="R106" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S106" s="3" t="s">
         <v>48</v>
@@ -9582,19 +9449,19 @@
       <c r="AP106" s="4"/>
       <c r="AQ106" s="4"/>
     </row>
-    <row r="107" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>42</v>
@@ -9645,7 +9512,7 @@
         <v>50</v>
       </c>
       <c r="AF107" s="3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG107" s="3"/>
       <c r="AH107" s="3"/>
@@ -9666,19 +9533,19 @@
       <c r="AP107" s="4"/>
       <c r="AQ107" s="4"/>
     </row>
-    <row r="108" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>42</v>
@@ -9729,7 +9596,7 @@
         <v>50</v>
       </c>
       <c r="AF108" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="AG108" s="3"/>
       <c r="AH108" s="3"/>
@@ -9750,19 +9617,19 @@
       <c r="AP108" s="4"/>
       <c r="AQ108" s="4"/>
     </row>
-    <row r="109" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C109" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E109" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>62</v>
@@ -9789,7 +9656,7 @@
         <v>30</v>
       </c>
       <c r="R109" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S109" s="3" t="s">
         <v>48</v>
@@ -9822,19 +9689,19 @@
       <c r="AP109" s="4"/>
       <c r="AQ109" s="4"/>
     </row>
-    <row r="110" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C110" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E110" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>42</v>
@@ -9885,7 +9752,7 @@
         <v>50</v>
       </c>
       <c r="AF110" s="3" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="AG110" s="3"/>
       <c r="AH110" s="3"/>
@@ -9906,19 +9773,19 @@
       <c r="AP110" s="4"/>
       <c r="AQ110" s="4"/>
     </row>
-    <row r="111" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C111" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E111" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>42</v>
@@ -9969,7 +9836,7 @@
         <v>50</v>
       </c>
       <c r="AF111" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="AG111" s="3"/>
       <c r="AH111" s="3"/>
@@ -9990,19 +9857,19 @@
       <c r="AP111" s="4"/>
       <c r="AQ111" s="4"/>
     </row>
-    <row r="112" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>42</v>
@@ -10053,7 +9920,7 @@
         <v>50</v>
       </c>
       <c r="AF112" s="3" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="AG112" s="3"/>
       <c r="AH112" s="3"/>
@@ -10074,19 +9941,19 @@
       <c r="AP112" s="4"/>
       <c r="AQ112" s="4"/>
     </row>
-    <row r="113" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
       <c r="B113" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>42</v>
@@ -10113,7 +9980,7 @@
         <v>96</v>
       </c>
       <c r="R113" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S113" s="3" t="s">
         <v>48</v>
@@ -10137,7 +10004,7 @@
         <v>50</v>
       </c>
       <c r="AF113" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="AG113" s="3"/>
       <c r="AH113" s="3"/>
@@ -10158,19 +10025,19 @@
       <c r="AP113" s="4"/>
       <c r="AQ113" s="4"/>
     </row>
-    <row r="114" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
       <c r="B114" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>42</v>
@@ -10221,7 +10088,7 @@
         <v>50</v>
       </c>
       <c r="AF114" s="3" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="AG114" s="3"/>
       <c r="AH114" s="3"/>
@@ -10242,19 +10109,19 @@
       <c r="AP114" s="4"/>
       <c r="AQ114" s="4"/>
     </row>
-    <row r="115" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>42</v>
@@ -10281,7 +10148,7 @@
         <v>96</v>
       </c>
       <c r="R115" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S115" s="3" t="s">
         <v>48</v>
@@ -10305,7 +10172,7 @@
         <v>50</v>
       </c>
       <c r="AF115" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="AG115" s="3"/>
       <c r="AH115" s="3"/>
@@ -10326,19 +10193,19 @@
       <c r="AP115" s="4"/>
       <c r="AQ115" s="4"/>
     </row>
-    <row r="116" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>42</v>
@@ -10389,7 +10256,7 @@
         <v>50</v>
       </c>
       <c r="AF116" s="3" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="AG116" s="3"/>
       <c r="AH116" s="3"/>
@@ -10410,19 +10277,19 @@
       <c r="AP116" s="4"/>
       <c r="AQ116" s="4"/>
     </row>
-    <row r="117" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
       <c r="B117" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>42</v>
@@ -10449,7 +10316,7 @@
         <v>96</v>
       </c>
       <c r="R117" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S117" s="3" t="s">
         <v>48</v>
@@ -10473,7 +10340,7 @@
         <v>50</v>
       </c>
       <c r="AF117" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="AG117" s="3"/>
       <c r="AH117" s="3"/>
@@ -10494,19 +10361,19 @@
       <c r="AP117" s="4"/>
       <c r="AQ117" s="4"/>
     </row>
-    <row r="118" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
       <c r="B118" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>42</v>
@@ -10557,7 +10424,7 @@
         <v>50</v>
       </c>
       <c r="AF118" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="AG118" s="3"/>
       <c r="AH118" s="3"/>
@@ -10574,19 +10441,19 @@
       <c r="AP118" s="4"/>
       <c r="AQ118" s="4"/>
     </row>
-    <row r="119" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D119" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>42</v>
@@ -10637,7 +10504,7 @@
         <v>50</v>
       </c>
       <c r="AF119" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="AG119" s="3"/>
       <c r="AH119" s="3"/>
@@ -10654,19 +10521,19 @@
       <c r="AP119" s="4"/>
       <c r="AQ119" s="4"/>
     </row>
-    <row r="120" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C120" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E120" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>42</v>
@@ -10693,7 +10560,7 @@
         <v>30</v>
       </c>
       <c r="R120" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S120" s="3" t="s">
         <v>48</v>
@@ -10713,12 +10580,8 @@
       <c r="AB120" s="3"/>
       <c r="AC120" s="3"/>
       <c r="AD120" s="3"/>
-      <c r="AE120" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF120" s="3" t="s">
-        <v>127</v>
-      </c>
+      <c r="AE120" s="3"/>
+      <c r="AF120" s="3"/>
       <c r="AG120" s="3"/>
       <c r="AH120" s="3"/>
       <c r="AI120" s="3"/>
@@ -10730,19 +10593,19 @@
       <c r="AP120" s="4"/>
       <c r="AQ120" s="4"/>
     </row>
-    <row r="121" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C121" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E121" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>42</v>
@@ -10793,7 +10656,7 @@
         <v>50</v>
       </c>
       <c r="AF121" s="3" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="AG121" s="3"/>
       <c r="AH121" s="3"/>
@@ -10808,19 +10671,19 @@
       <c r="AP121" s="4"/>
       <c r="AQ121" s="4"/>
     </row>
-    <row r="122" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C122" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E122" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>42</v>
@@ -10871,7 +10734,7 @@
         <v>50</v>
       </c>
       <c r="AF122" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="AG122" s="3"/>
       <c r="AH122" s="3"/>
@@ -10886,19 +10749,19 @@
       <c r="AP122" s="4"/>
       <c r="AQ122" s="4"/>
     </row>
-    <row r="123" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>42</v>
@@ -10949,7 +10812,7 @@
         <v>50</v>
       </c>
       <c r="AF123" s="3" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="AG123" s="3"/>
       <c r="AH123" s="3"/>
@@ -10964,19 +10827,19 @@
       <c r="AP123" s="4"/>
       <c r="AQ123" s="4"/>
     </row>
-    <row r="124" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>42</v>
@@ -11003,7 +10866,7 @@
         <v>96</v>
       </c>
       <c r="R124" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S124" s="3" t="s">
         <v>48</v>
@@ -11027,7 +10890,7 @@
         <v>50</v>
       </c>
       <c r="AF124" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="AG124" s="3"/>
       <c r="AH124" s="3"/>
@@ -11042,19 +10905,19 @@
       <c r="AP124" s="4"/>
       <c r="AQ124" s="4"/>
     </row>
-    <row r="125" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>42</v>
@@ -11105,7 +10968,7 @@
         <v>50</v>
       </c>
       <c r="AF125" s="3" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="AG125" s="3"/>
       <c r="AH125" s="3"/>
@@ -11120,19 +10983,19 @@
       <c r="AP125" s="4"/>
       <c r="AQ125" s="4"/>
     </row>
-    <row r="126" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>42</v>
@@ -11159,7 +11022,7 @@
         <v>96</v>
       </c>
       <c r="R126" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S126" s="3" t="s">
         <v>48</v>
@@ -11183,7 +11046,7 @@
         <v>50</v>
       </c>
       <c r="AF126" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="AG126" s="3"/>
       <c r="AH126" s="3"/>
@@ -11198,19 +11061,19 @@
       <c r="AP126" s="4"/>
       <c r="AQ126" s="4"/>
     </row>
-    <row r="127" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>42</v>
@@ -11261,7 +11124,7 @@
         <v>50</v>
       </c>
       <c r="AF127" s="3" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="AG127" s="3"/>
       <c r="AH127" s="3"/>
@@ -11276,19 +11139,19 @@
       <c r="AP127" s="4"/>
       <c r="AQ127" s="4"/>
     </row>
-    <row r="128" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>42</v>
@@ -11315,7 +11178,7 @@
         <v>96</v>
       </c>
       <c r="R128" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S128" s="3" t="s">
         <v>48</v>
@@ -11339,7 +11202,7 @@
         <v>50</v>
       </c>
       <c r="AF128" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="AG128" s="3"/>
       <c r="AH128" s="3"/>
@@ -11354,19 +11217,19 @@
       <c r="AP128" s="4"/>
       <c r="AQ128" s="4"/>
     </row>
-    <row r="129" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>42</v>
@@ -11429,19 +11292,19 @@
       <c r="AP129" s="4"/>
       <c r="AQ129" s="4"/>
     </row>
-    <row r="130" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>42</v>
@@ -11504,19 +11367,19 @@
       <c r="AP130" s="4"/>
       <c r="AQ130" s="4"/>
     </row>
-    <row r="131" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C131" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E131" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>62</v>
@@ -11543,7 +11406,7 @@
         <v>30</v>
       </c>
       <c r="R131" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S131" s="3" t="s">
         <v>48</v>
@@ -11577,19 +11440,19 @@
       <c r="AP131" s="4"/>
       <c r="AQ131" s="4"/>
     </row>
-    <row r="132" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C132" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E132" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>42</v>
@@ -11652,19 +11515,19 @@
       <c r="AP132" s="4"/>
       <c r="AQ132" s="4"/>
     </row>
-    <row r="133" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C133" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E133" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E133" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>42</v>
@@ -11727,19 +11590,19 @@
       <c r="AP133" s="4"/>
       <c r="AQ133" s="4"/>
     </row>
-    <row r="134" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C134" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E134" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E134" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>62</v>
@@ -11766,16 +11629,16 @@
         <v>30</v>
       </c>
       <c r="R134" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S134" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T134" s="3">
+        <v>1</v>
+      </c>
+      <c r="U134" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S134" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T134" s="3">
-        <v>1</v>
-      </c>
-      <c r="U134" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V134" s="3"/>
       <c r="W134" s="3"/>
@@ -11800,19 +11663,19 @@
       <c r="AP134" s="4"/>
       <c r="AQ134" s="4"/>
     </row>
-    <row r="135" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>42</v>
@@ -11875,19 +11738,19 @@
       <c r="AP135" s="4"/>
       <c r="AQ135" s="4"/>
     </row>
-    <row r="136" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>42</v>
@@ -11916,7 +11779,7 @@
         <v>96</v>
       </c>
       <c r="R136" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S136" s="3" t="s">
         <v>48</v>
@@ -11950,19 +11813,19 @@
       <c r="AP136" s="4"/>
       <c r="AQ136" s="4"/>
     </row>
-    <row r="137" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
       <c r="B137" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>42</v>
@@ -12025,19 +11888,19 @@
       <c r="AP137" s="4"/>
       <c r="AQ137" s="4"/>
     </row>
-    <row r="138" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
       <c r="B138" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>42</v>
@@ -12066,7 +11929,7 @@
         <v>96</v>
       </c>
       <c r="R138" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S138" s="3" t="s">
         <v>48</v>
@@ -12100,19 +11963,19 @@
       <c r="AP138" s="4"/>
       <c r="AQ138" s="4"/>
     </row>
-    <row r="139" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>42</v>
@@ -12175,19 +12038,19 @@
       <c r="AP139" s="4"/>
       <c r="AQ139" s="4"/>
     </row>
-    <row r="140" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>42</v>
@@ -12216,7 +12079,7 @@
         <v>96</v>
       </c>
       <c r="R140" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S140" s="3" t="s">
         <v>48</v>
@@ -12250,19 +12113,19 @@
       <c r="AP140" s="4"/>
       <c r="AQ140" s="4"/>
     </row>
-    <row r="141" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
       <c r="B141" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C141" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E141" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E141" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>62</v>
@@ -12289,16 +12152,16 @@
         <v>30</v>
       </c>
       <c r="R141" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S141" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T141" s="3">
+        <v>1</v>
+      </c>
+      <c r="U141" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S141" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T141" s="3">
-        <v>1</v>
-      </c>
-      <c r="U141" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V141" s="3"/>
       <c r="W141" s="3"/>
@@ -12323,19 +12186,19 @@
       <c r="AP141" s="4"/>
       <c r="AQ141" s="4"/>
     </row>
-    <row r="142" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
       <c r="B142" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>42</v>
@@ -12386,19 +12249,18 @@
         <v>50</v>
       </c>
       <c r="AF142" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AG142" s="3"/>
       <c r="AH142" s="3"/>
       <c r="AI142" s="3"/>
-      <c r="AJ142" s="3"/>
+      <c r="AJ142" s="3">
+        <v>0.998</v>
+      </c>
       <c r="AK142" s="3">
-        <v>0.998</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="AL142" s="3">
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="AM142" s="3">
         <v>2.2549999999999999</v>
       </c>
       <c r="AN142" s="4"/>
@@ -12406,19 +12268,19 @@
       <c r="AP142" s="4"/>
       <c r="AQ142" s="4"/>
     </row>
-    <row r="143" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D143" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>42</v>
@@ -12469,19 +12331,18 @@
         <v>50</v>
       </c>
       <c r="AF143" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="AG143" s="3"/>
       <c r="AH143" s="3"/>
       <c r="AI143" s="3"/>
-      <c r="AJ143" s="3"/>
+      <c r="AJ143" s="3">
+        <v>0.997</v>
+      </c>
       <c r="AK143" s="3">
-        <v>0.997</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="AL143" s="3">
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="AM143" s="3">
         <v>5.8400000000000001E-2</v>
       </c>
       <c r="AN143" s="4"/>
@@ -12489,19 +12350,19 @@
       <c r="AP143" s="4"/>
       <c r="AQ143" s="4"/>
     </row>
-    <row r="144" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C144" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E144" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E144" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>62</v>
@@ -12528,7 +12389,7 @@
         <v>30</v>
       </c>
       <c r="R144" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S144" s="3" t="s">
         <v>48</v>
@@ -12556,25 +12417,24 @@
       <c r="AJ144" s="3"/>
       <c r="AK144" s="3"/>
       <c r="AL144" s="3"/>
-      <c r="AM144" s="3"/>
       <c r="AN144" s="4"/>
       <c r="AO144" s="4"/>
       <c r="AP144" s="4"/>
       <c r="AQ144" s="4"/>
     </row>
-    <row r="145" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C145" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E145" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>42</v>
@@ -12625,19 +12485,18 @@
         <v>50</v>
       </c>
       <c r="AF145" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="AG145" s="3"/>
       <c r="AH145" s="3"/>
       <c r="AI145" s="3"/>
-      <c r="AJ145" s="3"/>
+      <c r="AJ145" s="3">
+        <v>0.998</v>
+      </c>
       <c r="AK145" s="3">
-        <v>0.998</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="AL145" s="3">
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="AM145" s="3">
         <v>2.2549999999999999</v>
       </c>
       <c r="AN145" s="4"/>
@@ -12645,19 +12504,19 @@
       <c r="AP145" s="4"/>
       <c r="AQ145" s="4"/>
     </row>
-    <row r="146" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
       <c r="B146" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C146" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E146" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>42</v>
@@ -12708,19 +12567,18 @@
         <v>50</v>
       </c>
       <c r="AF146" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="AG146" s="3"/>
       <c r="AH146" s="3"/>
       <c r="AI146" s="3"/>
-      <c r="AJ146" s="3"/>
+      <c r="AJ146" s="3">
+        <v>0.997</v>
+      </c>
       <c r="AK146" s="3">
-        <v>0.997</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="AL146" s="3">
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="AM146" s="3">
         <v>5.8400000000000001E-2</v>
       </c>
       <c r="AN146" s="4"/>
@@ -12728,19 +12586,19 @@
       <c r="AP146" s="4"/>
       <c r="AQ146" s="4"/>
     </row>
-    <row r="147" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C147" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E147" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>62</v>
@@ -12767,16 +12625,16 @@
         <v>30</v>
       </c>
       <c r="R147" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S147" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T147" s="3">
+        <v>1</v>
+      </c>
+      <c r="U147" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S147" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T147" s="3">
-        <v>1</v>
-      </c>
-      <c r="U147" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V147" s="3"/>
       <c r="W147" s="3"/>
@@ -12795,25 +12653,24 @@
       <c r="AJ147" s="3"/>
       <c r="AK147" s="3"/>
       <c r="AL147" s="3"/>
-      <c r="AM147" s="3"/>
       <c r="AN147" s="4"/>
       <c r="AO147" s="4"/>
       <c r="AP147" s="4"/>
       <c r="AQ147" s="4"/>
     </row>
-    <row r="148" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
       <c r="B148" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>42</v>
@@ -12864,19 +12721,18 @@
         <v>50</v>
       </c>
       <c r="AF148" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="AG148" s="3"/>
       <c r="AH148" s="3"/>
       <c r="AI148" s="3"/>
-      <c r="AJ148" s="3"/>
+      <c r="AJ148" s="3">
+        <v>0.998</v>
+      </c>
       <c r="AK148" s="3">
-        <v>0.998</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="AL148" s="3">
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="AM148" s="3">
         <v>2.2549999999999999</v>
       </c>
       <c r="AN148" s="4"/>
@@ -12884,19 +12740,19 @@
       <c r="AP148" s="4"/>
       <c r="AQ148" s="4"/>
     </row>
-    <row r="149" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
       <c r="B149" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>42</v>
@@ -12923,7 +12779,7 @@
         <v>96</v>
       </c>
       <c r="R149" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S149" s="3" t="s">
         <v>48</v>
@@ -12947,19 +12803,18 @@
         <v>50</v>
       </c>
       <c r="AF149" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="AG149" s="3"/>
       <c r="AH149" s="3"/>
       <c r="AI149" s="3"/>
-      <c r="AJ149" s="3"/>
+      <c r="AJ149" s="3">
+        <v>0.997</v>
+      </c>
       <c r="AK149" s="3">
-        <v>0.997</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="AL149" s="3">
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="AM149" s="3">
         <v>5.8400000000000001E-2</v>
       </c>
       <c r="AN149" s="4"/>
@@ -12967,19 +12822,19 @@
       <c r="AP149" s="4"/>
       <c r="AQ149" s="4"/>
     </row>
-    <row r="150" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
       <c r="B150" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>42</v>
@@ -13030,19 +12885,18 @@
         <v>50</v>
       </c>
       <c r="AF150" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="AG150" s="3"/>
       <c r="AH150" s="3"/>
       <c r="AI150" s="3"/>
-      <c r="AJ150" s="3"/>
+      <c r="AJ150" s="3">
+        <v>0.998</v>
+      </c>
       <c r="AK150" s="3">
-        <v>0.998</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="AL150" s="3">
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="AM150" s="3">
         <v>2.2549999999999999</v>
       </c>
       <c r="AN150" s="4"/>
@@ -13050,19 +12904,19 @@
       <c r="AP150" s="4"/>
       <c r="AQ150" s="4"/>
     </row>
-    <row r="151" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
       <c r="B151" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>42</v>
@@ -13089,7 +12943,7 @@
         <v>96</v>
       </c>
       <c r="R151" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S151" s="3" t="s">
         <v>48</v>
@@ -13113,19 +12967,18 @@
         <v>50</v>
       </c>
       <c r="AF151" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="AG151" s="3"/>
       <c r="AH151" s="3"/>
       <c r="AI151" s="3"/>
-      <c r="AJ151" s="3"/>
+      <c r="AJ151" s="3">
+        <v>0.997</v>
+      </c>
       <c r="AK151" s="3">
-        <v>0.997</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="AL151" s="3">
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="AM151" s="3">
         <v>5.8400000000000001E-2</v>
       </c>
       <c r="AN151" s="4"/>
@@ -13133,19 +12986,19 @@
       <c r="AP151" s="4"/>
       <c r="AQ151" s="4"/>
     </row>
-    <row r="152" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
       <c r="B152" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>42</v>
@@ -13196,19 +13049,18 @@
         <v>50</v>
       </c>
       <c r="AF152" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="AG152" s="3"/>
       <c r="AH152" s="3"/>
       <c r="AI152" s="3"/>
-      <c r="AJ152" s="3"/>
+      <c r="AJ152" s="3">
+        <v>0.998</v>
+      </c>
       <c r="AK152" s="3">
-        <v>0.998</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="AL152" s="3">
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="AM152" s="3">
         <v>2.2549999999999999</v>
       </c>
       <c r="AN152" s="4"/>
@@ -13216,19 +13068,19 @@
       <c r="AP152" s="4"/>
       <c r="AQ152" s="4"/>
     </row>
-    <row r="153" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="3"/>
       <c r="B153" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>42</v>
@@ -13255,7 +13107,7 @@
         <v>96</v>
       </c>
       <c r="R153" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S153" s="3" t="s">
         <v>48</v>
@@ -13279,19 +13131,18 @@
         <v>50</v>
       </c>
       <c r="AF153" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="AG153" s="3"/>
       <c r="AH153" s="3"/>
       <c r="AI153" s="3"/>
-      <c r="AJ153" s="3"/>
+      <c r="AJ153" s="3">
+        <v>0.997</v>
+      </c>
       <c r="AK153" s="3">
-        <v>0.997</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="AL153" s="3">
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="AM153" s="3">
         <v>5.8400000000000001E-2</v>
       </c>
       <c r="AN153" s="4"/>
@@ -13299,19 +13150,19 @@
       <c r="AP153" s="4"/>
       <c r="AQ153" s="4"/>
     </row>
-    <row r="154" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="3"/>
       <c r="B154" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C154" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E154" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="D154" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E154" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>62</v>
@@ -13338,16 +13189,16 @@
         <v>30</v>
       </c>
       <c r="R154" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S154" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T154" s="3">
+        <v>1</v>
+      </c>
+      <c r="U154" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S154" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T154" s="3">
-        <v>1</v>
-      </c>
-      <c r="U154" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V154" s="3"/>
       <c r="W154" s="3"/>
@@ -13372,7 +13223,7 @@
       <c r="AP154" s="4"/>
       <c r="AQ154" s="4"/>
     </row>
-    <row r="155" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="3"/>
       <c r="B155" s="3" t="s">
         <v>39</v>
@@ -13384,7 +13235,7 @@
         <v>40</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3"/>
@@ -13405,16 +13256,16 @@
         <v>9</v>
       </c>
       <c r="P155" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q155" s="3">
+        <v>1</v>
+      </c>
+      <c r="R155" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S155" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="Q155" s="3">
-        <v>1</v>
-      </c>
-      <c r="R155" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="S155" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="T155" s="3">
         <v>1</v>
@@ -13445,7 +13296,7 @@
       <c r="AP155" s="4"/>
       <c r="AQ155" s="4"/>
     </row>
-    <row r="156" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="3"/>
       <c r="B156" s="3" t="s">
         <v>39</v>
@@ -13454,10 +13305,10 @@
         <v>64</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F156" s="3"/>
       <c r="G156" s="3"/>
@@ -13478,22 +13329,22 @@
         <v>9</v>
       </c>
       <c r="P156" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q156" s="3">
+        <v>1</v>
+      </c>
+      <c r="R156" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S156" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="Q156" s="3">
-        <v>1</v>
-      </c>
-      <c r="R156" s="3" t="s">
+      <c r="T156" s="3">
+        <v>1</v>
+      </c>
+      <c r="U156" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S156" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="T156" s="3">
-        <v>1</v>
-      </c>
-      <c r="U156" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V156" s="3"/>
       <c r="W156" s="3"/>
@@ -13518,7 +13369,7 @@
       <c r="AP156" s="4"/>
       <c r="AQ156" s="4"/>
     </row>
-    <row r="157" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157" s="3"/>
       <c r="B157" s="3" t="s">
         <v>39</v>
@@ -13527,10 +13378,10 @@
         <v>64</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="3"/>
@@ -13551,16 +13402,16 @@
         <v>9</v>
       </c>
       <c r="P157" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q157" s="3">
+        <v>1</v>
+      </c>
+      <c r="R157" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S157" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="Q157" s="3">
-        <v>1</v>
-      </c>
-      <c r="R157" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="S157" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="T157" s="3">
         <v>1</v>
@@ -13591,7 +13442,7 @@
       <c r="AP157" s="4"/>
       <c r="AQ157" s="4"/>
     </row>
-    <row r="158" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="3"/>
       <c r="B158" s="3" t="s">
         <v>39</v>
@@ -13600,10 +13451,10 @@
         <v>64</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="3"/>
@@ -13624,22 +13475,22 @@
         <v>9</v>
       </c>
       <c r="P158" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q158" s="3">
+        <v>1</v>
+      </c>
+      <c r="R158" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S158" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="Q158" s="3">
-        <v>1</v>
-      </c>
-      <c r="R158" s="3" t="s">
+      <c r="T158" s="3">
+        <v>1</v>
+      </c>
+      <c r="U158" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S158" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="T158" s="3">
-        <v>1</v>
-      </c>
-      <c r="U158" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V158" s="3"/>
       <c r="W158" s="3"/>
@@ -13664,7 +13515,7 @@
       <c r="AP158" s="4"/>
       <c r="AQ158" s="4"/>
     </row>
-    <row r="159" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A159" s="3"/>
       <c r="B159" s="3" t="s">
         <v>39</v>
@@ -13673,10 +13524,10 @@
         <v>64</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F159" s="3"/>
       <c r="G159" s="3"/>
@@ -13697,22 +13548,22 @@
         <v>9</v>
       </c>
       <c r="P159" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q159" s="3">
         <v>30</v>
       </c>
       <c r="R159" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S159" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="T159" s="3">
+        <v>1</v>
+      </c>
+      <c r="U159" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S159" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="T159" s="3">
-        <v>1</v>
-      </c>
-      <c r="U159" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V159" s="3"/>
       <c r="W159" s="3"/>
@@ -13737,7 +13588,7 @@
       <c r="AP159" s="4"/>
       <c r="AQ159" s="4"/>
     </row>
-    <row r="160" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
       <c r="B160" s="3" t="s">
         <v>39</v>
@@ -13746,10 +13597,10 @@
         <v>64</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3"/>
@@ -13770,22 +13621,22 @@
         <v>9</v>
       </c>
       <c r="P160" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q160" s="3">
+        <v>1</v>
+      </c>
+      <c r="R160" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S160" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="Q160" s="3">
-        <v>1</v>
-      </c>
-      <c r="R160" s="3" t="s">
+      <c r="T160" s="3">
+        <v>1</v>
+      </c>
+      <c r="U160" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S160" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="T160" s="3">
-        <v>1</v>
-      </c>
-      <c r="U160" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V160" s="3"/>
       <c r="W160" s="3"/>
@@ -13810,7 +13661,7 @@
       <c r="AP160" s="4"/>
       <c r="AQ160" s="4"/>
     </row>
-    <row r="161" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A161" s="3"/>
       <c r="B161" s="3" t="s">
         <v>39</v>
@@ -13819,10 +13670,10 @@
         <v>64</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="3"/>
@@ -13843,22 +13694,22 @@
         <v>9</v>
       </c>
       <c r="P161" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q161" s="3">
+        <v>1</v>
+      </c>
+      <c r="R161" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S161" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="Q161" s="3">
-        <v>1</v>
-      </c>
-      <c r="R161" s="3" t="s">
+      <c r="T161" s="3">
+        <v>1</v>
+      </c>
+      <c r="U161" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S161" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="T161" s="3">
-        <v>1</v>
-      </c>
-      <c r="U161" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V161" s="3"/>
       <c r="W161" s="3"/>
@@ -13883,7 +13734,7 @@
       <c r="AP161" s="4"/>
       <c r="AQ161" s="4"/>
     </row>
-    <row r="162" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162" s="3"/>
       <c r="B162" s="3" t="s">
         <v>39</v>
@@ -13895,7 +13746,7 @@
         <v>52</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="3"/>
@@ -13916,16 +13767,16 @@
         <v>9</v>
       </c>
       <c r="P162" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q162" s="3">
+        <v>1</v>
+      </c>
+      <c r="R162" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S162" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="Q162" s="3">
-        <v>1</v>
-      </c>
-      <c r="R162" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="S162" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="T162" s="3">
         <v>1</v>
@@ -13956,7 +13807,7 @@
       <c r="AP162" s="4"/>
       <c r="AQ162" s="4"/>
     </row>
-    <row r="163" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A163" s="3"/>
       <c r="B163" s="3" t="s">
         <v>39</v>
@@ -13965,10 +13816,10 @@
         <v>64</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="3"/>
@@ -13989,22 +13840,22 @@
         <v>9</v>
       </c>
       <c r="P163" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q163" s="3">
+        <v>1</v>
+      </c>
+      <c r="R163" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S163" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="Q163" s="3">
-        <v>1</v>
-      </c>
-      <c r="R163" s="3" t="s">
+      <c r="T163" s="3">
+        <v>1</v>
+      </c>
+      <c r="U163" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S163" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="T163" s="3">
-        <v>1</v>
-      </c>
-      <c r="U163" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V163" s="3"/>
       <c r="W163" s="3"/>
@@ -14029,7 +13880,7 @@
       <c r="AP163" s="4"/>
       <c r="AQ163" s="4"/>
     </row>
-    <row r="164" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164" s="3"/>
       <c r="B164" s="3" t="s">
         <v>39</v>
@@ -14038,10 +13889,10 @@
         <v>64</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3"/>
@@ -14062,22 +13913,22 @@
         <v>9</v>
       </c>
       <c r="P164" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q164" s="3">
+        <v>1</v>
+      </c>
+      <c r="R164" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S164" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="Q164" s="3">
-        <v>1</v>
-      </c>
-      <c r="R164" s="3" t="s">
+      <c r="T164" s="3">
+        <v>1</v>
+      </c>
+      <c r="U164" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S164" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="T164" s="3">
-        <v>1</v>
-      </c>
-      <c r="U164" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V164" s="3"/>
       <c r="W164" s="3"/>
@@ -14102,7 +13953,7 @@
       <c r="AP164" s="4"/>
       <c r="AQ164" s="4"/>
     </row>
-    <row r="165" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A165" s="3"/>
       <c r="B165" s="3" t="s">
         <v>39</v>
@@ -14114,7 +13965,7 @@
         <v>53</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="3"/>
@@ -14135,16 +13986,16 @@
         <v>9</v>
       </c>
       <c r="P165" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q165" s="3">
+        <v>1</v>
+      </c>
+      <c r="R165" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S165" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="Q165" s="3">
-        <v>1</v>
-      </c>
-      <c r="R165" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="S165" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="T165" s="3">
         <v>1</v>
@@ -14175,7 +14026,7 @@
       <c r="AP165" s="4"/>
       <c r="AQ165" s="4"/>
     </row>
-    <row r="166" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166" s="3"/>
       <c r="B166" s="3" t="s">
         <v>39</v>
@@ -14184,10 +14035,10 @@
         <v>64</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3"/>
@@ -14208,22 +14059,22 @@
         <v>9</v>
       </c>
       <c r="P166" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q166" s="3">
+        <v>1</v>
+      </c>
+      <c r="R166" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S166" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="Q166" s="3">
-        <v>1</v>
-      </c>
-      <c r="R166" s="3" t="s">
+      <c r="T166" s="3">
+        <v>1</v>
+      </c>
+      <c r="U166" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S166" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="T166" s="3">
-        <v>1</v>
-      </c>
-      <c r="U166" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V166" s="3"/>
       <c r="W166" s="3"/>
@@ -14248,7 +14099,7 @@
       <c r="AP166" s="4"/>
       <c r="AQ166" s="4"/>
     </row>
-    <row r="167" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="3"/>
       <c r="B167" s="3" t="s">
         <v>39</v>
@@ -14260,7 +14111,7 @@
         <v>51</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="3"/>
@@ -14281,16 +14132,16 @@
         <v>9</v>
       </c>
       <c r="P167" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q167" s="3">
+        <v>1</v>
+      </c>
+      <c r="R167" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S167" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="Q167" s="3">
-        <v>1</v>
-      </c>
-      <c r="R167" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="S167" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="T167" s="3">
         <v>1</v>
@@ -14321,7 +14172,7 @@
       <c r="AP167" s="4"/>
       <c r="AQ167" s="4"/>
     </row>
-    <row r="168" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168" s="3"/>
       <c r="B168" s="3" t="s">
         <v>39</v>
@@ -14330,10 +14181,10 @@
         <v>64</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3"/>
@@ -14354,22 +14205,22 @@
         <v>9</v>
       </c>
       <c r="P168" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q168" s="3">
         <v>30</v>
       </c>
       <c r="R168" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S168" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="T168" s="3">
+        <v>1</v>
+      </c>
+      <c r="U168" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S168" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="T168" s="3">
-        <v>1</v>
-      </c>
-      <c r="U168" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V168" s="3"/>
       <c r="W168" s="3"/>
@@ -14394,19 +14245,19 @@
       <c r="AP168" s="4"/>
       <c r="AQ168" s="4"/>
     </row>
-    <row r="169" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A169" s="3"/>
       <c r="B169" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="3"/>
@@ -14425,13 +14276,13 @@
         <v>5</v>
       </c>
       <c r="P169" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q169" s="3">
         <v>30</v>
       </c>
       <c r="R169" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S169" s="3" t="s">
         <v>48</v>
@@ -14465,19 +14316,19 @@
       <c r="AP169" s="4"/>
       <c r="AQ169" s="4"/>
     </row>
-    <row r="170" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170" s="3"/>
       <c r="B170" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>62</v>
@@ -14526,12 +14377,8 @@
       <c r="AB170" s="3"/>
       <c r="AC170" s="3"/>
       <c r="AD170" s="3"/>
-      <c r="AE170" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF170" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="AE170" s="3"/>
+      <c r="AF170" s="3"/>
       <c r="AG170" s="3"/>
       <c r="AH170" s="3"/>
       <c r="AI170" s="3"/>
@@ -14544,19 +14391,19 @@
       <c r="AP170" s="4"/>
       <c r="AQ170" s="4"/>
     </row>
-    <row r="171" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A171" s="3"/>
       <c r="B171" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D171" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>62</v>
@@ -14585,7 +14432,7 @@
         <v>96</v>
       </c>
       <c r="R171" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S171" s="3" t="s">
         <v>48</v>
@@ -14605,12 +14452,8 @@
       <c r="AB171" s="3"/>
       <c r="AC171" s="3"/>
       <c r="AD171" s="3"/>
-      <c r="AE171" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF171" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="AE171" s="3"/>
+      <c r="AF171" s="3"/>
       <c r="AG171" s="3"/>
       <c r="AH171" s="3"/>
       <c r="AI171" s="3"/>
@@ -14623,19 +14466,19 @@
       <c r="AP171" s="4"/>
       <c r="AQ171" s="4"/>
     </row>
-    <row r="172" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A172" s="3"/>
       <c r="B172" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C172" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E172" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="D172" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E172" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>62</v>
@@ -14662,7 +14505,7 @@
         <v>30</v>
       </c>
       <c r="R172" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S172" s="3" t="s">
         <v>48</v>
@@ -14696,19 +14539,19 @@
       <c r="AP172" s="4"/>
       <c r="AQ172" s="4"/>
     </row>
-    <row r="173" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173" s="3"/>
       <c r="B173" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C173" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E173" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="D173" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E173" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>62</v>
@@ -14757,12 +14600,8 @@
       <c r="AB173" s="3"/>
       <c r="AC173" s="3"/>
       <c r="AD173" s="3"/>
-      <c r="AE173" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF173" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="AE173" s="3"/>
+      <c r="AF173" s="3"/>
       <c r="AG173" s="3"/>
       <c r="AH173" s="3"/>
       <c r="AI173" s="3"/>
@@ -14775,19 +14614,19 @@
       <c r="AP173" s="4"/>
       <c r="AQ173" s="4"/>
     </row>
-    <row r="174" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A174" s="3"/>
       <c r="B174" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C174" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E174" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="D174" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E174" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>62</v>
@@ -14816,7 +14655,7 @@
         <v>96</v>
       </c>
       <c r="R174" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S174" s="3" t="s">
         <v>48</v>
@@ -14836,12 +14675,8 @@
       <c r="AB174" s="3"/>
       <c r="AC174" s="3"/>
       <c r="AD174" s="3"/>
-      <c r="AE174" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF174" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="AE174" s="3"/>
+      <c r="AF174" s="3"/>
       <c r="AG174" s="3"/>
       <c r="AH174" s="3"/>
       <c r="AI174" s="3"/>
@@ -14854,19 +14689,19 @@
       <c r="AP174" s="4"/>
       <c r="AQ174" s="4"/>
     </row>
-    <row r="175" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A175" s="3"/>
       <c r="B175" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C175" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E175" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="D175" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E175" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>62</v>
@@ -14893,16 +14728,16 @@
         <v>30</v>
       </c>
       <c r="R175" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S175" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T175" s="3">
+        <v>1</v>
+      </c>
+      <c r="U175" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S175" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T175" s="3">
-        <v>1</v>
-      </c>
-      <c r="U175" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V175" s="3"/>
       <c r="W175" s="3"/>
@@ -14927,19 +14762,19 @@
       <c r="AP175" s="4"/>
       <c r="AQ175" s="4"/>
     </row>
-    <row r="176" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
       <c r="B176" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>62</v>
@@ -14988,12 +14823,8 @@
       <c r="AB176" s="3"/>
       <c r="AC176" s="3"/>
       <c r="AD176" s="3"/>
-      <c r="AE176" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF176" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="AE176" s="3"/>
+      <c r="AF176" s="3"/>
       <c r="AG176" s="3"/>
       <c r="AH176" s="3"/>
       <c r="AI176" s="3"/>
@@ -15006,19 +14837,19 @@
       <c r="AP176" s="4"/>
       <c r="AQ176" s="4"/>
     </row>
-    <row r="177" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A177" s="3"/>
       <c r="B177" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>62</v>
@@ -15047,7 +14878,7 @@
         <v>96</v>
       </c>
       <c r="R177" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S177" s="3" t="s">
         <v>48</v>
@@ -15067,12 +14898,8 @@
       <c r="AB177" s="3"/>
       <c r="AC177" s="3"/>
       <c r="AD177" s="3"/>
-      <c r="AE177" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF177" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="AE177" s="3"/>
+      <c r="AF177" s="3"/>
       <c r="AG177" s="3"/>
       <c r="AH177" s="3"/>
       <c r="AI177" s="3"/>
@@ -15085,19 +14912,19 @@
       <c r="AP177" s="4"/>
       <c r="AQ177" s="4"/>
     </row>
-    <row r="178" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A178" s="3"/>
       <c r="B178" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D178" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>62</v>
@@ -15146,12 +14973,8 @@
       <c r="AB178" s="3"/>
       <c r="AC178" s="3"/>
       <c r="AD178" s="3"/>
-      <c r="AE178" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF178" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="AE178" s="3"/>
+      <c r="AF178" s="3"/>
       <c r="AG178" s="3"/>
       <c r="AH178" s="3"/>
       <c r="AI178" s="3"/>
@@ -15164,19 +14987,19 @@
       <c r="AP178" s="4"/>
       <c r="AQ178" s="4"/>
     </row>
-    <row r="179" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
       <c r="B179" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>62</v>
@@ -15205,7 +15028,7 @@
         <v>96</v>
       </c>
       <c r="R179" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S179" s="3" t="s">
         <v>48</v>
@@ -15225,12 +15048,8 @@
       <c r="AB179" s="3"/>
       <c r="AC179" s="3"/>
       <c r="AD179" s="3"/>
-      <c r="AE179" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF179" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="AE179" s="3"/>
+      <c r="AF179" s="3"/>
       <c r="AG179" s="3"/>
       <c r="AH179" s="3"/>
       <c r="AI179" s="3"/>
@@ -15243,19 +15062,19 @@
       <c r="AP179" s="4"/>
       <c r="AQ179" s="4"/>
     </row>
-    <row r="180" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
       <c r="B180" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D180" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>62</v>
@@ -15304,12 +15123,8 @@
       <c r="AB180" s="3"/>
       <c r="AC180" s="3"/>
       <c r="AD180" s="3"/>
-      <c r="AE180" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF180" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="AE180" s="3"/>
+      <c r="AF180" s="3"/>
       <c r="AG180" s="3"/>
       <c r="AH180" s="3"/>
       <c r="AI180" s="3"/>
@@ -15322,19 +15137,19 @@
       <c r="AP180" s="4"/>
       <c r="AQ180" s="4"/>
     </row>
-    <row r="181" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181" s="3"/>
       <c r="B181" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>62</v>
@@ -15363,7 +15178,7 @@
         <v>96</v>
       </c>
       <c r="R181" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S181" s="3" t="s">
         <v>48</v>
@@ -15383,12 +15198,8 @@
       <c r="AB181" s="3"/>
       <c r="AC181" s="3"/>
       <c r="AD181" s="3"/>
-      <c r="AE181" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF181" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="AE181" s="3"/>
+      <c r="AF181" s="3"/>
       <c r="AG181" s="3"/>
       <c r="AH181" s="3"/>
       <c r="AI181" s="3"/>
@@ -15401,19 +15212,19 @@
       <c r="AP181" s="4"/>
       <c r="AQ181" s="4"/>
     </row>
-    <row r="182" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A182" s="3"/>
       <c r="B182" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C182" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E182" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="D182" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E182" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>62</v>
@@ -15440,16 +15251,16 @@
         <v>30</v>
       </c>
       <c r="R182" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S182" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T182" s="3">
+        <v>1</v>
+      </c>
+      <c r="U182" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S182" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T182" s="3">
-        <v>1</v>
-      </c>
-      <c r="U182" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V182" s="3"/>
       <c r="W182" s="3"/>
@@ -15474,19 +15285,19 @@
       <c r="AP182" s="4"/>
       <c r="AQ182" s="4"/>
     </row>
-    <row r="183" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
       <c r="B183" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>42</v>
@@ -15534,10 +15345,10 @@
       <c r="AC183" s="3"/>
       <c r="AD183" s="3"/>
       <c r="AE183" s="3" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="AF183" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="AG183" s="3"/>
       <c r="AH183" s="3"/>
@@ -15556,19 +15367,19 @@
       <c r="AP183" s="4"/>
       <c r="AQ183" s="4"/>
     </row>
-    <row r="184" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
       <c r="B184" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>42</v>
@@ -15595,7 +15406,7 @@
         <v>30</v>
       </c>
       <c r="R184" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S184" s="3" t="s">
         <v>48</v>
@@ -15628,19 +15439,19 @@
       <c r="AP184" s="4"/>
       <c r="AQ184" s="4"/>
     </row>
-    <row r="185" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A185" s="3"/>
       <c r="B185" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>42</v>
@@ -15691,7 +15502,7 @@
         <v>50</v>
       </c>
       <c r="AF185" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG185" s="3"/>
       <c r="AH185" s="3"/>
@@ -15710,19 +15521,19 @@
       <c r="AP185" s="4"/>
       <c r="AQ185" s="4"/>
     </row>
-    <row r="186" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A186" s="3"/>
       <c r="B186" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D186" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>42</v>
@@ -15773,7 +15584,7 @@
         <v>50</v>
       </c>
       <c r="AF186" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG186" s="3"/>
       <c r="AH186" s="3"/>
@@ -15792,19 +15603,19 @@
       <c r="AP186" s="4"/>
       <c r="AQ186" s="4"/>
     </row>
-    <row r="187" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A187" s="3"/>
       <c r="B187" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D187" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>42</v>
@@ -15855,7 +15666,7 @@
         <v>50</v>
       </c>
       <c r="AF187" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG187" s="3"/>
       <c r="AH187" s="3"/>
@@ -15874,19 +15685,19 @@
       <c r="AP187" s="4"/>
       <c r="AQ187" s="4"/>
     </row>
-    <row r="188" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188" s="3"/>
       <c r="B188" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D188" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>42</v>
@@ -15937,7 +15748,7 @@
         <v>50</v>
       </c>
       <c r="AF188" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG188" s="3"/>
       <c r="AH188" s="3"/>
@@ -15956,19 +15767,19 @@
       <c r="AP188" s="4"/>
       <c r="AQ188" s="4"/>
     </row>
-    <row r="189" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A189" s="3"/>
       <c r="B189" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D189" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F189" s="3"/>
       <c r="G189" s="3"/>
@@ -15985,16 +15796,16 @@
       <c r="N189" s="3"/>
       <c r="O189" s="3"/>
       <c r="P189" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q189" s="3">
         <v>1</v>
       </c>
       <c r="R189" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S189" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T189" s="3">
         <v>1</v>
@@ -16011,12 +15822,8 @@
       <c r="AB189" s="3"/>
       <c r="AC189" s="3"/>
       <c r="AD189" s="3"/>
-      <c r="AE189" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF189" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="AE189" s="3"/>
+      <c r="AF189" s="3"/>
       <c r="AG189" s="3"/>
       <c r="AH189" s="3"/>
       <c r="AI189" s="3"/>
@@ -16029,19 +15836,19 @@
       <c r="AP189" s="4"/>
       <c r="AQ189" s="4"/>
     </row>
-    <row r="190" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A190" s="3"/>
       <c r="B190" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D190" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="3"/>
@@ -16060,7 +15867,7 @@
         <v>20</v>
       </c>
       <c r="P190" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q190" s="3">
         <v>2</v>
@@ -16100,19 +15907,19 @@
       <c r="AP190" s="4"/>
       <c r="AQ190" s="4"/>
     </row>
-    <row r="191" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A191" s="3"/>
       <c r="B191" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D191" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="3"/>
@@ -16129,16 +15936,16 @@
       <c r="N191" s="3"/>
       <c r="O191" s="3"/>
       <c r="P191" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q191" s="3">
         <v>1</v>
       </c>
       <c r="R191" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S191" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T191" s="3">
         <v>1</v>
@@ -16155,12 +15962,8 @@
       <c r="AB191" s="3"/>
       <c r="AC191" s="3"/>
       <c r="AD191" s="3"/>
-      <c r="AE191" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF191" s="3" t="s">
-        <v>134</v>
-      </c>
+      <c r="AE191" s="3"/>
+      <c r="AF191" s="3"/>
       <c r="AG191" s="3"/>
       <c r="AH191" s="3"/>
       <c r="AI191" s="3"/>
@@ -16173,19 +15976,19 @@
       <c r="AP191" s="4"/>
       <c r="AQ191" s="4"/>
     </row>
-    <row r="192" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192" s="3"/>
       <c r="B192" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="3"/>
@@ -16204,7 +16007,7 @@
         <v>30</v>
       </c>
       <c r="P192" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q192" s="3">
         <v>2</v>
@@ -16244,19 +16047,19 @@
       <c r="AP192" s="4"/>
       <c r="AQ192" s="4"/>
     </row>
-    <row r="193" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A193" s="3"/>
       <c r="B193" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>62</v>
@@ -16283,7 +16086,7 @@
         <v>30</v>
       </c>
       <c r="R193" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S193" s="3" t="s">
         <v>48</v>
@@ -16317,19 +16120,19 @@
       <c r="AP193" s="4"/>
       <c r="AQ193" s="4"/>
     </row>
-    <row r="194" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A194" s="3"/>
       <c r="B194" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>62</v>
@@ -16356,16 +16159,16 @@
         <v>30</v>
       </c>
       <c r="R194" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S194" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T194" s="3">
+        <v>1</v>
+      </c>
+      <c r="U194" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S194" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T194" s="3">
-        <v>1</v>
-      </c>
-      <c r="U194" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V194" s="3"/>
       <c r="W194" s="3"/>
@@ -16390,19 +16193,19 @@
       <c r="AP194" s="4"/>
       <c r="AQ194" s="4"/>
     </row>
-    <row r="195" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A195" s="3"/>
       <c r="B195" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>62</v>
@@ -16429,16 +16232,16 @@
         <v>30</v>
       </c>
       <c r="R195" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S195" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T195" s="3">
+        <v>1</v>
+      </c>
+      <c r="U195" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S195" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T195" s="3">
-        <v>1</v>
-      </c>
-      <c r="U195" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V195" s="3"/>
       <c r="W195" s="3"/>
@@ -16463,19 +16266,19 @@
       <c r="AP195" s="4"/>
       <c r="AQ195" s="4"/>
     </row>
-    <row r="196" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A196" s="3"/>
       <c r="B196" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="3"/>
@@ -16500,7 +16303,7 @@
         <v>30</v>
       </c>
       <c r="R196" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S196" s="3" t="s">
         <v>48</v>
@@ -16534,19 +16337,19 @@
       <c r="AP196" s="4"/>
       <c r="AQ196" s="4"/>
     </row>
-    <row r="197" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A197" s="3"/>
       <c r="B197" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>42</v>
@@ -16597,7 +16400,7 @@
         <v>50</v>
       </c>
       <c r="AF197" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="AG197" s="3"/>
       <c r="AH197" s="3"/>
@@ -16616,19 +16419,19 @@
       <c r="AP197" s="4"/>
       <c r="AQ197" s="4"/>
     </row>
-    <row r="198" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A198" s="3"/>
       <c r="B198" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>42</v>
@@ -16679,7 +16482,7 @@
         <v>50</v>
       </c>
       <c r="AF198" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="AG198" s="3"/>
       <c r="AH198" s="3"/>
@@ -16698,19 +16501,19 @@
       <c r="AP198" s="4"/>
       <c r="AQ198" s="4"/>
     </row>
-    <row r="199" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A199" s="3"/>
       <c r="B199" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>62</v>
@@ -16737,7 +16540,7 @@
         <v>30</v>
       </c>
       <c r="R199" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S199" s="3" t="s">
         <v>48</v>
@@ -16770,19 +16573,19 @@
       <c r="AP199" s="4"/>
       <c r="AQ199" s="4"/>
     </row>
-    <row r="200" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A200" s="3"/>
       <c r="B200" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>42</v>
@@ -16833,7 +16636,7 @@
         <v>50</v>
       </c>
       <c r="AF200" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="AG200" s="3"/>
       <c r="AH200" s="3"/>
@@ -16852,19 +16655,19 @@
       <c r="AP200" s="4"/>
       <c r="AQ200" s="4"/>
     </row>
-    <row r="201" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A201" s="3"/>
       <c r="B201" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>42</v>
@@ -16891,7 +16694,7 @@
         <v>96</v>
       </c>
       <c r="R201" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S201" s="3" t="s">
         <v>48</v>
@@ -16915,7 +16718,7 @@
         <v>50</v>
       </c>
       <c r="AF201" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="AG201" s="3"/>
       <c r="AH201" s="3"/>
@@ -16934,19 +16737,19 @@
       <c r="AP201" s="4"/>
       <c r="AQ201" s="4"/>
     </row>
-    <row r="202" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A202" s="3"/>
       <c r="B202" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>62</v>
@@ -16973,16 +16776,16 @@
         <v>30</v>
       </c>
       <c r="R202" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S202" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T202" s="3">
+        <v>1</v>
+      </c>
+      <c r="U202" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S202" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T202" s="3">
-        <v>1</v>
-      </c>
-      <c r="U202" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V202" s="3"/>
       <c r="W202" s="3"/>
@@ -17006,19 +16809,19 @@
       <c r="AP202" s="4"/>
       <c r="AQ202" s="4"/>
     </row>
-    <row r="203" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A203" s="3"/>
       <c r="B203" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D203" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>42</v>
@@ -17069,7 +16872,7 @@
         <v>50</v>
       </c>
       <c r="AF203" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="AG203" s="3"/>
       <c r="AH203" s="3"/>
@@ -17088,19 +16891,19 @@
       <c r="AP203" s="4"/>
       <c r="AQ203" s="4"/>
     </row>
-    <row r="204" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A204" s="3"/>
       <c r="B204" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D204" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>42</v>
@@ -17127,7 +16930,7 @@
         <v>96</v>
       </c>
       <c r="R204" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S204" s="3" t="s">
         <v>48</v>
@@ -17151,7 +16954,7 @@
         <v>50</v>
       </c>
       <c r="AF204" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="AG204" s="3"/>
       <c r="AH204" s="3"/>
@@ -17170,19 +16973,19 @@
       <c r="AP204" s="4"/>
       <c r="AQ204" s="4"/>
     </row>
-    <row r="205" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A205" s="3"/>
       <c r="B205" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D205" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>42</v>
@@ -17233,7 +17036,7 @@
         <v>50</v>
       </c>
       <c r="AF205" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="AG205" s="3"/>
       <c r="AH205" s="3"/>
@@ -17252,19 +17055,19 @@
       <c r="AP205" s="4"/>
       <c r="AQ205" s="4"/>
     </row>
-    <row r="206" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A206" s="3"/>
       <c r="B206" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>42</v>
@@ -17291,7 +17094,7 @@
         <v>96</v>
       </c>
       <c r="R206" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S206" s="3" t="s">
         <v>48</v>
@@ -17315,7 +17118,7 @@
         <v>50</v>
       </c>
       <c r="AF206" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="AG206" s="3"/>
       <c r="AH206" s="3"/>
@@ -17334,19 +17137,19 @@
       <c r="AP206" s="4"/>
       <c r="AQ206" s="4"/>
     </row>
-    <row r="207" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A207" s="3"/>
       <c r="B207" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D207" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>42</v>
@@ -17397,7 +17200,7 @@
         <v>50</v>
       </c>
       <c r="AF207" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="AG207" s="3"/>
       <c r="AH207" s="3"/>
@@ -17416,19 +17219,19 @@
       <c r="AP207" s="4"/>
       <c r="AQ207" s="4"/>
     </row>
-    <row r="208" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A208" s="3"/>
       <c r="B208" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D208" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>42</v>
@@ -17455,7 +17258,7 @@
         <v>96</v>
       </c>
       <c r="R208" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S208" s="3" t="s">
         <v>48</v>
@@ -17479,7 +17282,7 @@
         <v>50</v>
       </c>
       <c r="AF208" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="AG208" s="3"/>
       <c r="AH208" s="3"/>
@@ -17498,19 +17301,19 @@
       <c r="AP208" s="4"/>
       <c r="AQ208" s="4"/>
     </row>
-    <row r="209" spans="1:43" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:43" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A209" s="3"/>
       <c r="B209" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>62</v>
@@ -17537,16 +17340,16 @@
         <v>30</v>
       </c>
       <c r="R209" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S209" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T209" s="3">
+        <v>1</v>
+      </c>
+      <c r="U209" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="S209" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T209" s="3">
-        <v>1</v>
-      </c>
-      <c r="U209" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="V209" s="3"/>
       <c r="W209" s="3"/>
